--- a/doc/excel/apipf-process-design.xlsx
+++ b/doc/excel/apipf-process-design.xlsx
@@ -8943,7 +8943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9025,7 +9025,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>全量確認の起点（定期側）。ここから 全量-03（対象一覧取得）→ 全量-04（fan-out）→ 認証実装チェック-01〜08 が動く。認証構成情報に変化がなくても動く**唯一の経路**であり、コンソール直変更のような資材に現れない変化を最大 24 時間で捕捉する（18 §18.1.1）。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -9111,7 +9115,13 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>日次 EventBridge Scheduler・実行ロールが作成済み（WBS A15-i）
+Scheduler 用 DLQ（SQS 標準キュー）が作成済み。**EventBridge Scheduler は On-failure Destination に非対応**のため、Lambda 側（全量-04 / 認証実装チェック）とは異なり DLQ を使う（2026-09-14 確定）
+巡回（対象検索-01）の実行時間帯と重ならないこと</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -9151,402 +9161,795 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>スケジュール式</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>cron</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Scheduler 定義（IaC）</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>**cron は 6 フィールド必須**（分 時 日 月 曜 年）。日と曜の両方に * は指定できず、片方は ? にする</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>ScheduleExpressionTimezone</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IANA TZ</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>JST 運用なら Asia/Tokyo を明示する。未指定だと UTC 解釈になり、意図した時間帯からずれる</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>FlexibleTimeWindow</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>OFF / FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>**Mode は指定必須**。全量確認は時刻の厳密性を要さないため FLEXIBLE（例 15 分）を推奨。起動を分散でき、同時刻に集中する他ジョブとの競合を避けられる（M-Q-PD-15）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>target payload</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>{"mode":"full"} のみ。対象の決定は 全量-03 が台帳から行う</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>RetryPolicy / DeadLetterConfig</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>対象検索-01 と同じ方針（M-Q-PD-1 で実装値を確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>3. 出力（O）</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>出力先</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>説明・例</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック Lambda の起動</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>非同期 Invoke</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック Lambda</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>payload = {mode:'full'}</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>AWS/Scheduler メトリクス</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>共通基盤アカウント</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>InvocationAttemptCount / TargetErrorCount / InvocationDroppedCount ほか</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>処理内容</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>補足・参照</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
+    <row r="32">
+      <c r="A32" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】実行時刻帯（M-Q-18-3）と、巡回（対象検索-01）と時間帯が重ならない配慮を明記する</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>日次 cron で起動する</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>起動精度は 60 秒。FLEXIBLE を設定した場合はウィンドウ内で分散される</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>巡回（毎正時付近）と重ならない時刻帯を選ぶ</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>同時に走ると台帳への書き込み（対象検索-09）と読み取り（全量-03）が交錯し、巡回の途中状態を全量が読む可能性がある。実害は小さいが避けられる競合は避ける（実行時刻帯は M-Q-18-3）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>payload {"mode":"full"} を渡して認証実装チェック Lambda を起動する</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>**手動起動（全量-02）と payload が同一**であり、実装上の分岐はない。トリガが Scheduler か人かだけの違い（18 §18.3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>起動失敗は RetryPolicy に従い再試行し、枯渇したら DLQ へ配信する</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Scheduler は Destination 非対応のため DLQ（SQS 標準キュー）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>EventBridge Scheduler -&gt; 認証実装チェック Lambda : Invoke(Event, {mode:'full'})
 【シーケンス図の所在】18 §18.1 実行モード図・§18.3 / 10 §10.1.7 F2</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-    </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>前日の全量確認がまだ終わっていない</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Lambda の同時実行</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>二重に走るが、検査は読み取り専用で冪等のため無害。ただし同時実行数とメトリクスを二重消費する</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>長時間化が続くなら Duration アラームで顕在化</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.3 / M-Q-PD-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック Lambda のスロットリング</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>TargetErrorThrottledCount</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>RetryPolicy に従い再試行</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>リトライ成功なら通知なし</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>§10 上限・制約</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>リトライ枯渇</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>InvocationDroppedCount / InvocationsSentToDeadLetterCount</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>DLQ へ退避（運用-02 で再処理）</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>MM-2 → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>全量確認が丸ごと動かない（スケジュール無効化等）</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>**巡回（MM-1）のような専用のハートビートを持たない**ため、気づくのが遅れる</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>再実行時の振る舞い</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>同じ日に複数回起動しても、検査は読み取り専用で冪等のため結果は変わらない（18 §18.5.2）。</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>状態更新のタイミング</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>本処理は状態を持たない。台帳の更新も行わない（全量確認は**読むだけ**で、台帳を書くのは巡回の責務）。</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>8. 権限・エンドポイント</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>権限 / エンドポイント</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Scheduler 実行ロール / lambda:InvokeFunction</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>認証方式・補足</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Scheduler 実行ロールの信頼ポリシーは aws:SourceAccount + aws:SourceArn（**スケジュールグループ単位**）を条件に付ける
+権限は lambda:InvokeFunction（対象関数に限定）+ sqs:SendMessage（DLQ に限定）</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>全量確認開始（定期）</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>実行 ID / 起動時刻 / トリガ種別=scheduled</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>手動起動と区別できるようトリガ種別を記録する</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>メトリクス</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>AWS/Scheduler（標準）</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>上記</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>ディメンション ScheduleGroup</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="n"/>
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="10" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>想定件数 / 所要時間</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>1 日 1 回 = 約 30 回/月。Scheduler の無料枠内で費用は実質ゼロ（RC-4）</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>上限・制約</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>起動精度 60 秒 / FLEXIBLE 指定時は最大 1440 分までウィンドウ設定可 / 単一スケジュールへの操作は 10 TPS</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-18-3</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>全量確認の実行時刻帯（巡回と重ならない時間）と、手動実行の権限範囲</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>運用 / 設計担当</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-15</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>FlexibleTimeWindow を FLEXIBLE にするか OFF にするか。全量確認は時刻厳密性を要さないため FLEXIBLE を推奨するが、「毎日 X 時に走る」ことを運用が前提にするなら OFF の方が説明しやすい</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>運用 / 設計担当</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-17</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>全量確認そのものが止まったことをどう検知するか。巡回には MM-1（DiscoveryLastSuccess の欠損）があるが、全量確認には対応するハートビートが無い。案: 全量確認の完了時に FullScanLastSuccess を emit し、**36 時間欠損で発報**（MM-1 と同じく検知の遅れは許容）</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>設計担当（18 §18.5.1 に MM-6 として追加するか要判断）</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n"/>
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A30:E30"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="B68:E68"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="B55:E55"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A39:E43"/>
+    <mergeCell ref="B54:E54"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="A71:E71"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="A38:E38"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B69:E69"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
+    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9559,7 +9962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9641,7 +10044,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>全量確認の起点（手動側）。**実装は 全量-01（定期）と完全に同一**で、起動元が人である点だけが異なる（18 §18.3）。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -9727,7 +10134,12 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>実行者が lambda:InvokeFunction の権限を持つこと（範囲は M-Q-18-3）
+Runbook「全量確認の手動実行手順」が整備されていること（WBS W4-1 ②）</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -9767,18 +10179,58 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>全件: {"mode":"full"} / 特定アプリのみ: {"mode":"full","appId":"…","env":"…"}</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>実行理由</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>監査前 / 大きな変更後 / インシデント後など。**payload には含めず、Runbook の実施記録に残す**</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n"/>
@@ -9817,16 +10269,48 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック Lambda の起動</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>非同期 Invoke</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック Lambda</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>定期起動と同一 payload</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>実行の監査証跡</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>CloudTrail</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>共通基盤アカウント</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>**誰がいつ実行したか**。手動操作の追跡はここに依存する</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n"/>
@@ -9859,40 +10343,79 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】実行権限を持つ者の範囲（共通基盤チームのみか、アプリチームも可か。M-Q-18-3）を確定する</t>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>**非同期（InvocationType=Event）で invoke する**</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>同期にすると全量確認の完了まで応答を待つことになり、CLI 側がタイムアウトする。また同期呼び出しの応答上限 6MB に対して結果が大きくなりうる</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>appId / env を指定した場合は **全量-04 の fan-out を行わず、その 1 アプリだけを検査する**</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>対象が 1 件しかない状態で自己 invoke するのは無駄な往復になるため。**この分岐は 全量-03 で対象を 1 件に絞ることで自然に実現する**（実装上の特別扱いを増やさない）</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>実行者・日時・理由を Runbook の実施記録に残す</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>payload に理由を入れても検査側は使わない。運用記録として別に残す方が確実（W4-1 ②）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>定期実行と同時刻に重ならないよう配慮する</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>重なっても無害だが、同時実行数とメトリクスを二重消費する</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>運用者 -&gt; 認証実装チェック Lambda : Invoke(Event, {mode:'full'})
 ※ 特定アプリのみ: {mode:'full', appId, env}
@@ -9900,270 +10423,435 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37"/>
     <row r="38"/>
     <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40"/>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
     <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>権限不足</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>AccessDenied</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>実行できない（正常な拒否）</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-18-3</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>同期 invoke してしまった</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>CLI タイムアウト</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Lambda 側は実行を継続する（呼び出し側が切れただけ）。結果はメトリクスと通知で確認する</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Runbook に非同期指定を明記（W4-1 ②）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>定期実行と同時に走った</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Lambda の同時実行</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>二重に検査されるが冪等のため無害</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.2</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>誤って連続実行した</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>検査は読み取り専用のため実害はないが、対象アプリへ短時間に複数回の検査リクエストが飛ぶ。**WAF のレートベースルールに抵触する可能性**があるため Runbook で注意喚起する</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>WAF ブロックは認証実装チェック-06 で WARN に分類</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>11 §11.2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="n"/>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>再実行時の振る舞い</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>状態更新のタイミング</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>8. 権限・エンドポイント</t>
-        </is>
-      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>何度実行しても検査結果は変わらない（読み取り専用）。ただし短時間の連続実行は対象アプリへの負荷になるため運用上は避ける。</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>権限 / エンドポイント</t>
+          <t>状態更新のタイミング</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>lambda:InvokeFunction（実行者の IAM）</t>
+          <t>状態を更新しない。</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>8. 権限・エンドポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>lambda:InvokeFunction（実行者の IAM）</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>認証方式・補足</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>実行者の IAM に lambda:InvokeFunction（対象関数に限定）。**実行の記録は CloudTrail に依存する**ため、共通基盤アカウントの CloudTrail が有効であることが前提
+実行権限を広く配ると「誰でも本番へ検査リクエストを流せる」状態になるため、範囲は明示的に決める（M-Q-18-3）</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-    </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>10. 性能・上限</t>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>全量確認開始（手動）</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>実行 ID / トリガ種別=manual / appId・env 指定の有無</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>定期起動と区別できるようにする</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>想定件数 / 所要時間</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>監査ログ</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>CloudTrail Invoke</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>実行者の ARN / 時刻 / 関数名</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>手動操作の追跡</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>上限・制約</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
+      <c r="A62" s="10" t="n"/>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
+          <t>10. 性能・上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>想定件数 / 所要時間</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>随時。頻度は運用次第（監査前・障害後など）</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>上限・制約</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>定期実行と同じ経路のため上限も同じ</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-18-3</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>手動実行の権限範囲（共通基盤チームのみか、アプリチームが自アプリを実行できるか）。後者を許す場合は appId を自分のアプリに限定する仕組みが要る</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>運用 / セキュリティ</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="n"/>
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="B65:E65"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B55:E55"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="A54:E54"/>
     <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A36:E40"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="B66:E66"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="B56:E56"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A42:E42"/>
     <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B53:E53"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A68:E68"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11031,9 +11719,9 @@
           <t>全量-01_全量確認処理開始（定期）</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -11083,9 +11771,9 @@
           <t>全量-02_全量確認処理開始（手動）</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -11135,9 +11823,9 @@
           <t>全量-03_監視対象一覧取得</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -11187,9 +11875,9 @@
           <t>全量-04_アプリ単位確認依頼</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -12025,7 +12713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12107,7 +12795,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>mode=full の本体の入口。全量-01 / 全量-02 のどちらから起動されても同じ処理を行い、検査対象の一覧を作る。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -12193,7 +12885,12 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>台帳（registry/）が存在すること
+配置バケットへの s3:ListBucket / GetObject 権限があること</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -12233,18 +12930,58 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>registry/ プレフィックス</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>S3 キー</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>規約</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>registry/{appId}/{env}.json</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>appId / env</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>payload（全量-02 の手動指定時のみ）</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>指定時は対象を 1 件に絞る</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n"/>
@@ -12283,16 +13020,48 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>検査対象リスト</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>[{appId, env}]</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>全量-04（メモリ内）</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>enabled=true のレコードのみ</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>除外件数</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>ログ</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>enabled=false で除外した件数。監視されていないアプリ数の把握に使う</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n"/>
@@ -12325,40 +13094,109 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】enabled=false のレコードを除外すること、List のページングを明記する</t>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>registry/ プレフィックスを List する。**1 リクエスト最大 1,000 キー**のためページングする</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>ContinuationToken で繰り返す。Phase 1 は数十件で 1 ページに収まる</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>各レコードを GetObject して enabled を確認する</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>**enabled=false のレコードを除外する**</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>中央が意図的に監視を止めたアプリと、**不備で取り込みを拒否したアプリ（拒否レコード）**の両方が除外される。後者は enabled=false + lastRejectedVersions を持つ（対象検索-09）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="A32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>appId / env の指定があればその 1 件に絞る</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>手動での部分実行（全量-02）。**ここで絞ることで 全量-04 の fan-out が自然に 1 件になり、実装上の分岐を増やさずに済む**</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>対象が 0 件なら異常として通知し、以降を実行しない</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>台帳が空 = 監視対象ゼロは通常あり得ない。権限不足や台帳の消失を黙って正常終了させない</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>【重要】全量確認は**台帳と API 仕様に載っている endpoint しか見ない**</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>認証構成情報のアップロード忘れがあると、新設した endpoint は台帳にも仕様にも現れないため検査対象に入らない。これは全量確認でも埋められない穴であり、責任分界（原則アプリ責任、M-Q-17-7）と staleness 検知（対象検索-13）で受ける（17 §17.2.2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>認証実装チェック Lambda -&gt; 配置バケット : List(registry/) -&gt; GetObject（各件）
 配置バケット --&gt; 認証実装チェック Lambda : 台帳 JSON 群
@@ -12366,270 +13204,427 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>List 失敗（AccessDenied 等）</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>API 例外</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>全量確認を中断する</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>MM-4 → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.1</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>一部レコードの Get 失敗</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>API 例外</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>その 1 件を落として継続（他のアプリは検査する）</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>件数をログに残し、多発時は MM-4 で顕在化</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>レコードの JSON が壊れている</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>パース例外</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>その 1 件を落として継続</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>対象 0 件</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>中断して通知</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>MM-4 → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>enabled=false が大半を占める</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>検査は実施するが、**除外件数をログに残して棚卸しの材料にする**</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>対象検索-13 の棚卸しと連動</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>再実行時の振る舞い</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>読み取りのみで副作用なし。同じ台帳なら常に同じ対象リストが得られる。</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>状態更新のタイミング</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>8. 権限・エンドポイント</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>権限 / エンドポイント</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>s3:ListBucket / s3:GetObject</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>認証方式・補足</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>共通基盤アカウント内の読み取り。クロスアカウント権限は不要</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>対象一覧取得</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>総レコード数 / 対象件数 / enabled=false 除外件数 / ページ数</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>想定件数 / 所要時間</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1 は数十レコード（3 アプリ × 2 環境）。将来 30 アプリ × 2 環境 = 60 レコードでも 1 ページ・1 秒未満</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>上限・制約</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>S3 List は 1 リクエスト最大 1,000 キー。数千レコード規模になったら並列 Get を検討（現時点では不要）</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="72">
+      <c r="A72" s="10" t="n"/>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="10" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n"/>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A38:E42"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="B68:E68"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B55:E55"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="B54:E54"/>
     <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A37:E37"/>
     <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="A66:E66"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B58:E58"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B53:E53"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12642,7 +13637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12724,7 +13719,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>全量確認の出口。対象アプリごとに**自分自身を非同期で呼び直し**、「1 実行 = 1 アプリ」に分割する。これにより全量を 1 実行に詰め込まずに済み、アプリ数が増えても Lambda の 15 分制限に構造的に当たらない（18 §18.5.3）。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -12810,7 +13809,12 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>全量-03 で検査対象リストを取得済み
+認証実装チェック Lambda に On-failure Destination（送信先 SQS）が設定済み（WBS A5）</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -12850,11 +13854,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>検査対象リスト</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>[{appId, env}]</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>全量-03</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>enabled=true のみ</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n"/>
@@ -12863,47 +13887,78 @@
       <c r="D18" s="10" t="n"/>
       <c r="E18" s="10" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>3. 出力（O）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>3. 出力（O）</t>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>出力先</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>説明・例</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>出力先</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>説明・例</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>子の起動</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>非同期 Invoke（自分自身）</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック Lambda</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>payload = {mode:'delta', appId, env, origin:'full'}</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>invoke 失敗件数</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>ログ / メトリクス</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>1 件の失敗で全量を止めないため、件数として集計する</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n"/>
@@ -12911,341 +13966,614 @@
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>4. 処理手順</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>4. 処理手順</t>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>補足・参照</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>処理内容</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>補足・参照</t>
+      <c r="A28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>対象ごとに**自分自身を非同期（InvocationType=Event）で invoke する**</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>1 実行 = 1 アプリ。親は検査そのものを行わず、割り振りに徹する（責務分離）</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】同時実行数の上限・スロットリング時の扱いを明記する</t>
+      <c r="A29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>payload に **origin:'full'** を付けて起点を記録する</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>検査側は origin を判定に使わず**ログにだけ出す**。これにより『巡回起点の検査』と『全量起点の検査』を後からログで区別できる。判定ロジックを分岐させないことで、モード1/モード2 で同一実装という原則を保つ</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>【重要】**Lambda の再帰ループ検出に抵触しないことを確認する**</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>AWS は同一リクエストチェーン内で約 16 回の呼び出しを検出すると次の起動を自動停止する（既定 ON・無料・X-Ray のトレースヘッダで計数）。本設計のチェーンは**親（mode=full）→ 子（1 アプリ）の深さ 2 で終わり**、子はさらに自分自身を呼ばないため閾値に達しない。ただし将来 fan-out を多段化する場合は要注意。停止された場合は RecursiveInvocationsDropped メトリクスに現れる</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>invoke の失敗は記録して次の対象へ進む</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>1 アプリの起動失敗で全量確認を止めない（18 §18.5.2）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="A32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>親は子の完了を待たない</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>非同期のため即座に返る。結果はメトリクス（認証実装チェック-07）と通知（認証実装チェック-08）で収束する</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>全対象の invoke が終わったら親は終了する</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>親自身は検査結果を集計しない（集計はメトリクス側の役割）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>認証実装チェック Lambda(mode=full) -&gt; 認証実装チェック Lambda(1 アプリ分) : アプリ数分 Invoke(Event)
 【シーケンス図の所在】18 §18.1 実行モード図・§18.3 / 10 §10.1.7 F2</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38"/>
     <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40"/>
+    <row r="41"/>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
     <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>同時実行数の上限に当たる（429）</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>API 例外</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>**AWS 仕様では 429 / 5xx はイベントがキューに戻り、最大 6 時間・指数バックオフ（最大 5 分間隔）で再試行される**。呼び出し側は受理されなかった分のみ失敗として記録する</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>長期化すれば MM-4 → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>AWS 公式（invocation-async-error-handling）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>子が関数エラーで失敗</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Lambda 側</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>既定 2 回リトライ（1 分後・2 分後）。枯渇で On-failure Destination へ</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>MM-4（Destination 滞留 ≥ 1）→ P2 Platform</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.1</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>再帰ループ検出で停止された</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>RecursiveInvocationsDropped メトリクス</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>**本設計では発生しない想定**（深さ 2）。発生したら多段 fan-out の混入を疑う</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>MM-4 相当として P2 Platform</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>AWS 公式（invocation-recursion）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>同一アプリが巡回起点の検査と重なる</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>二重に検査されるが読み取り専用のため無害。origin でログ上は区別できる</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>対象が 1 件のみ（手動の部分実行）</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>全量-03 の出力</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>1 回だけ invoke する（特別扱いはしない）</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>全量-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>再実行時の振る舞い</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>状態更新のタイミング</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>8. 権限・エンドポイント</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>権限 / エンドポイント</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>lambda:InvokeFunction（自身）/ lambda.{region}.amazonaws.com</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>認証方式・補足</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
+          <t>再実行時の振る舞い</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>**at-least-once**。同じアプリへ複数回の検査依頼が飛びうるが、検査は読み取り専用で冪等のため無害。AWS 公式も非同期キューが結果整合性であり同一イベントが複数回届きうると明記している（18 §18.5.2）。</t>
+        </is>
+      </c>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
     </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>9. ログ・メトリクス</t>
-        </is>
-      </c>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>状態更新のタイミング</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。**全量確認は台帳を書かない**（台帳を書くのは巡回の責務）。したがって lastArtifactVersions は全量確認では変化せず、巡回の差分判定に影響を与えない。</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>名称・項目</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>8. 権限・エンドポイント</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>lambda:InvokeFunction（自身）/ lambda.{region}.amazonaws.com</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>認証方式・補足</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>lambda:InvokeFunction（**自分自身の関数 ARN**）。共通基盤アカウント内のため AssumeRole は不要
+非同期のペイロード上限は 1 MB（同期の 6 MB とは別）。本 payload は数十バイトで問題にならない</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
+          <t>9. ログ・メトリクス</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>名称・項目</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>fan-out 実行</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>対象件数 / invoke 成功件数 / 失敗件数 / 所要 ms</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>子の起動</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>appId / env / origin=full / 相関 ID</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>親の実行 ID を引き回して親子を紐づける</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>想定件数 / 所要時間</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>対象アプリ数 × 1 invoke。Phase 1 は 6 件（3 アプリ × 2 環境）、将来 30 アプリでも 60 件で数秒</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>上限・制約</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>**同時実行数（既定 1,000）を対象件数分消費する**。アプリ単位の並列は別ドメインへのアクセスのため1 アプリに負荷が集中することはないが、件数が増えたら並列度の上限設定を検討する（M-Q-PD-18）。Lambda のスケーリングは 1 関数あたり 10 秒で 1,000 実行環境まで</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-18</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>fan-out の並列度に上限を設けるか。アプリ単位の並列は別ドメインへのアクセスなので負荷は分散するが、アプリ数が増えると同時実行数を一気に消費し、巡回起点の検査（対象検索-11）を圧迫する可能性がある。案: 予約同時実行の割り当て、またはバッチ分割して時間をずらす</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-19</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>payload に origin を追加することの確認（検査側は判定に使わずログ出力のみ）。code-samples/README §2 のイベント形式に追記が必要</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="n"/>
+      <c r="B74" s="10" t="n"/>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="B68:E68"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="B54:E54"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="A37:E41"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B67:E67"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/doc/excel/apipf-process-design.xlsx
+++ b/doc/excel/apipf-process-design.xlsx
@@ -28,24 +28,25 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全量-02_全量確認処理開始（手動）" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全量-03_監視対象一覧取得" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全量-04_アプリ単位確認依頼" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-01_認証構成情報参照" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-02_API仕様取得" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-03_正常系確認用トークン取得" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-04_未認証アクセス確認" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-05_正常系アクセス確認" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-06_確認結果判定" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-07_確認結果メトリクス送信" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-08_検知結果通知依頼" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知-01_通知先解決" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知-02_重要度別通知送信" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知-03_メトリクス閾値通知" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="運用-01_監視機構稼働監視通知" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="運用-02_処理失敗退避・再処理" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="運用-03_監視設定手動更新" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="連携-01_認証構成情報配置" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全量-05_全量確認結果メトリクス送信" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-01_認証構成情報参照" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-02_API仕様取得" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-03_正常系確認用トークン取得" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-04_未認証アクセス確認" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-05_正常系アクセス確認" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-06_確認結果判定" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-07_確認結果メトリクス送信" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証実装チェック-08_検知結果通知依頼" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知-01_通知先解決" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知-02_重要度別通知送信" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知-03_メトリクス閾値通知" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="運用-01_監視機構稼働監視通知" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="運用-02_処理失敗退避・再処理" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="運用-03_監視設定手動更新" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="連携-01_認証構成情報配置" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_処理一覧'!$A$4:$J$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_処理一覧'!$A$4:$J$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9222,7 +9223,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>OFF / FLEXIBLE</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -9237,7 +9238,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>**Mode は指定必須**。全量確認は時刻の厳密性を要さないため FLEXIBLE（例 15 分）を推奨。起動を分散でき、同時刻に集中する他ジョブとの競合を避けられる（M-Q-PD-15）</t>
+          <t>**Mode は指定必須**。本設計は **OFF で確定**（2026-09-15）。FLEXIBLE の効果は「起動の分散によるスロットリング回避」だが、本設計はスケジュールが 2 本（巡回・全量）しかなく集中しないため効果がない。OFF なら『毎日 X 時に走る』と運用に説明でき、障害調査時も実行時刻が読める（起動精度は 60 秒）</t>
         </is>
       </c>
     </row>
@@ -9612,22 +9613,22 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FullScanLastSuccess の 48 時間欠損（MM-6）</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>**巡回（MM-1）のような専用のハートビートを持たない**ため、気づくのが遅れる</t>
+          <t>—（検知のみ）</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MM-6 → P2 Platform</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>M-Q-PD-17</t>
+          <t>全量-05 / 18 §18.5.1</t>
         </is>
       </c>
     </row>
@@ -9884,12 +9885,12 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>FlexibleTimeWindow を FLEXIBLE にするか OFF にするか。全量確認は時刻厳密性を要さないため FLEXIBLE を推奨するが、「毎日 X 時に走る」ことを運用が前提にするなら OFF の方が説明しやすい</t>
+          <t>【解決・2026-09-15】**OFF で確定**。FLEXIBLE の効果（起動の分散によるスロットリング回避）はスケジュールが 2 本しかない本設計では得られず、実行時刻が読めなくなる不利益の方が大きいため</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>運用 / 設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr"/>
@@ -9902,12 +9903,12 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>全量確認そのものが止まったことをどう検知するか。巡回には MM-1（DiscoveryLastSuccess の欠損）があるが、全量確認には対応するハートビートが無い。案: 全量確認の完了時に FullScanLastSuccess を emit し、**36 時間欠損で発報**（MM-1 と同じく検知の遅れは許容）</t>
+          <t>【解決・2026-09-15】全量確認の停止検知を **MM-6** として新設。**全量-05 が FullScanLastSuccess を emit し、48 時間欠損で発報**（日次実行に対し 2 回分の余裕）。18 §18.5.1 / WBS B10-i・B1-i に反映済み</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>設計担当（18 §18.5.1 に MM-6 として追加するか要判断）</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr"/>
@@ -10864,7 +10865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11884,22 +11885,22 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック-01</t>
+          <t>全量-05</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>認証構成情報参照</t>
+          <t>全量確認結果メトリクス送信</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック（1 アプリの確認・共通）</t>
+          <t>全量（全量確認 固有）</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>共通（対象検索・全量とも）</t>
+          <t>全量（日次・手動）</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -11909,7 +11910,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>認証構成情報配置バケット（registry/）</t>
+          <t>CloudWatch</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -11919,29 +11920,29 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>確認対象アプリの設定値（検査先 URL・認証方式・トークン設定）を台帳から取得する。</t>
+          <t>全量確認の fan-out が完了したことを示すハートビートを送信する。これが止まることが MM-6（全量確認の停止）の検知トリガーになる。</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>認証実装チェック-01_認証構成情報参照</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+          <t>全量-05_全量確認結果メトリクス送信</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック-02</t>
+          <t>認証実装チェック-01</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>API 仕様取得</t>
+          <t>認証構成情報参照</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11961,7 +11962,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>認証構成情報配置バケット（openapi/）</t>
+          <t>認証構成情報配置バケット（registry/）</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -11971,12 +11972,12 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>確認対象の endpoint 一覧と公開明示（MON-1）を取得する。</t>
+          <t>確認対象アプリの設定値（検査先 URL・認証方式・トークン設定）を台帳から取得する。</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>認証実装チェック-02_API仕様取得</t>
+          <t>認証実装チェック-01_認証構成情報参照</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -11988,12 +11989,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック-03</t>
+          <t>認証実装チェック-02</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>正常系確認用トークン取得</t>
+          <t>API 仕様取得</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -12013,7 +12014,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Secrets Manager → 認証基盤 /token</t>
+          <t>認証構成情報配置バケット（openapi/）</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -12023,12 +12024,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>正常系アクセス確認で使う短命トークンを取得する。</t>
+          <t>確認対象の endpoint 一覧と公開明示（MON-1）を取得する。</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>認証実装チェック-03_正常系確認用トークン取得</t>
+          <t>認証実装チェック-02_API仕様取得</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -12040,12 +12041,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック-04</t>
+          <t>認証実装チェック-03</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>未認証アクセス確認</t>
+          <t>正常系確認用トークン取得</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -12065,7 +12066,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>CloudFront → WAF → API GW / ALB</t>
+          <t>Secrets Manager → 認証基盤 /token</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -12075,29 +12076,29 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>認証情報なしでリクエストし、正しく拒否されるか（401/403、Cookie 系は 302）を確認する。2xx なら認証実装漏れ。</t>
+          <t>正常系アクセス確認で使う短命トークンを取得する。</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>認証実装チェック-04_未認証アクセス確認</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>○ 記入済</t>
+          <t>認証実装チェック-03_正常系確認用トークン取得</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>記入待ち</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック-05</t>
+          <t>認証実装チェック-04</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>正常系アクセス確認</t>
+          <t>未認証アクセス確認</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -12127,29 +12128,29 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>有効なトークン付きでリクエストし、200 が返ることで API 稼働と確認処理自体の健全性を確かめる。</t>
+          <t>認証情報なしでリクエストし、正しく拒否されるか（401/403、Cookie 系は 302）を確認する。2xx なら認証実装漏れ。</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>認証実装チェック-05_正常系アクセス確認</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+          <t>認証実装チェック-04_未認証アクセス確認</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック-06</t>
+          <t>認証実装チェック-05</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>確認結果判定（4×4）</t>
+          <t>正常系アクセス確認</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12164,27 +12165,27 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック Lambda（内部）</t>
+          <t>認証実装チェック Lambda</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CloudFront → WAF → API GW / ALB</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>同期</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>未認証アクセス確認と正常系アクセス確認の結果の組み合わせから、重要度（CRITICAL / WARN / INFO / OK）を判定する。</t>
+          <t>有効なトークン付きでリクエストし、200 が返ることで API 稼働と確認処理自体の健全性を確かめる。</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>認証実装チェック-06_確認結果判定</t>
+          <t>認証実装チェック-05_正常系アクセス確認</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -12196,12 +12197,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック-07</t>
+          <t>認証実装チェック-06</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>確認結果メトリクス送信</t>
+          <t>確認結果判定（4×4）</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12216,27 +12217,27 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック Lambda</t>
+          <t>認証実装チェック Lambda（内部）</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>CloudWatch</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>同期</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>確認結果をメトリクス化し、保険系アラーム（AuthCheckCritical &gt; 0）の入力とする。</t>
+          <t>未認証アクセス確認と正常系アクセス確認の結果の組み合わせから、重要度（CRITICAL / WARN / INFO / OK）を判定する。</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>認証実装チェック-07_確認結果メトリクス送信</t>
+          <t>認証実装チェック-06_確認結果判定</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -12248,12 +12249,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック-08</t>
+          <t>認証実装チェック-07</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>検知結果通知依頼</t>
+          <t>確認結果メトリクス送信</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -12273,22 +12274,22 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>アラート検知 Lambda</t>
+          <t>CloudWatch</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>非同期</t>
+          <t>同期</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>判定済みの検知結果を、通知の振り分けを行うアラート検知 Lambda へ引き渡す。</t>
+          <t>確認結果をメトリクス化し、保険系アラーム（AuthCheckCritical &gt; 0）の入力とする。</t>
         </is>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>認証実装チェック-08_検知結果通知依頼</t>
+          <t>認証実装チェック-07_確認結果メトリクス送信</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -12300,47 +12301,47 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>通知-01</t>
+          <t>認証実装チェック-08</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>通知先解決</t>
+          <t>検知結果通知依頼</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>通知（アラート通知）</t>
+          <t>認証実装チェック（1 アプリの確認・共通）</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>共通（検知時）</t>
+          <t>共通（対象検索・全量とも）</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
+          <t>認証実装チェック Lambda</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
           <t>アラート検知 Lambda</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>認証構成情報配置バケット（registry/）</t>
-        </is>
-      </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>同期</t>
+          <t>非同期</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>台帳の通知先設定から送信先を解決する。未設定時は全社デフォルトを使う。</t>
+          <t>判定済みの検知結果を、通知の振り分けを行うアラート検知 Lambda へ引き渡す。</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>通知-01_通知先解決</t>
+          <t>認証実装チェック-08_検知結果通知依頼</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -12352,12 +12353,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>通知-02</t>
+          <t>通知-01</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>重要度別通知送信</t>
+          <t>通知先解決</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12377,7 +12378,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>SNS（P1 Security / P2 Platform / P3 App）</t>
+          <t>認証構成情報配置バケット（registry/）</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -12387,12 +12388,12 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>重要度に応じた宛先へ通知を送信する。</t>
+          <t>台帳の通知先設定から送信先を解決する。未設定時は全社デフォルトを使う。</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>通知-02_重要度別通知送信</t>
+          <t>通知-01_通知先解決</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -12404,12 +12405,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>通知-03</t>
+          <t>通知-02</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>メトリクス閾値通知（保険系）</t>
+          <t>重要度別通知送信</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -12419,32 +12420,32 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>共通（閾値超過時）</t>
+          <t>共通（検知時）</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>CloudWatch Alarm</t>
+          <t>アラート検知 Lambda</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SNS（P1 Security / P2 Platform / P3 App）</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>非同期</t>
+          <t>同期</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>アラート検知 Lambda の経路とは独立に、メトリクス閾値からも発報する（発報 2 系統の保険側）。</t>
+          <t>重要度に応じた宛先へ通知を送信する。</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>通知-03_メトリクス閾値通知</t>
+          <t>通知-02_重要度別通知送信</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -12456,22 +12457,22 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>運用-01</t>
+          <t>通知-03</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>監視機構稼働監視通知（MM-1〜5）</t>
+          <t>メトリクス閾値通知（保険系）</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>運用（運用・異常系）</t>
+          <t>通知（アラート通知）</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>随時（異常時）</t>
+          <t>共通（閾値超過時）</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -12481,7 +12482,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>SNS（P2 Platform）</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -12491,12 +12492,12 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>監視機構そのものの停止・失敗を検知して発報する（監視の空白＝検知の空白を防ぐ）。</t>
+          <t>アラート検知 Lambda の経路とは独立に、メトリクス閾値からも発報する（発報 2 系統の保険側）。</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>運用-01_監視機構稼働監視通知</t>
+          <t>通知-03_メトリクス閾値通知</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -12508,12 +12509,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>運用-02</t>
+          <t>運用-01</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>処理失敗退避・再処理（DLQ）</t>
+          <t>監視機構稼働監視通知（MM-1〜5）</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -12528,12 +12529,12 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>各 Lambda（非同期実行の失敗）</t>
+          <t>CloudWatch Alarm</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>SQS DLQ → 運用者</t>
+          <t>SNS（P2 Platform）</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -12543,12 +12544,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>非同期呼び出しがリトライ後も失敗した場合に退避し、後から再処理・原因調査できるようにする。</t>
+          <t>監視機構そのものの停止・失敗を検知して発報する（監視の空白＝検知の空白を防ぐ）。</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>運用-02_処理失敗退避・再処理</t>
+          <t>運用-01_監視機構稼働監視通知</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -12560,12 +12561,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>運用-03</t>
+          <t>運用-02</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>監視設定手動更新</t>
+          <t>処理失敗退避・再処理（DLQ）</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -12575,32 +12576,32 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>随時（運用操作）</t>
+          <t>随時（異常時）</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>運用者</t>
+          <t>各 Lambda（非同期実行の失敗）</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>認証構成情報配置バケット（registry/）</t>
+          <t>SQS DLQ → 運用者</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>同期</t>
+          <t>非同期</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>監視の有効・無効の切替や通知先の設定など、中央管理項目を運用者が更新する。</t>
+          <t>非同期呼び出しがリトライ後も失敗した場合に退避し、後から再処理・原因調査できるようにする。</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>運用-03_監視設定手動更新</t>
+          <t>運用-02_処理失敗退避・再処理</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -12612,57 +12613,109 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
+          <t>運用-03</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>監視設定手動更新</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>運用（運用・異常系）</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>随時（運用操作）</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>運用者</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>認証構成情報配置バケット（registry/）</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>同期</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>監視の有効・無効の切替や通知先の設定など、中央管理項目を運用者が更新する。</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>運用-03_監視設定手動更新</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>記入待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
           <t>連携-01</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>認証構成情報配置（アプリ側）</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>連携（アプリ接点）</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>随時（デプロイのたび）</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>ベンダー CI（デプロイパイプライン最終段）</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>認証構成情報連携バケット（App アカウント）</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>同期</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>デプロイ成功後に認証構成情報を配置する。本監視の入口であり、アプリ（ベンダー）側の責務。</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>連携-01_認証構成情報配置</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>記入待ち</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J37"/>
+  <autoFilter ref="A4:J38"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -12686,21 +12739,22 @@
     <hyperlink ref="I20" location="'全量-02_全量確認処理開始（手動）'!A1"/>
     <hyperlink ref="I21" location="'全量-03_監視対象一覧取得'!A1"/>
     <hyperlink ref="I22" location="'全量-04_アプリ単位確認依頼'!A1"/>
-    <hyperlink ref="I23" location="'認証実装チェック-01_認証構成情報参照'!A1"/>
-    <hyperlink ref="I24" location="'認証実装チェック-02_API仕様取得'!A1"/>
-    <hyperlink ref="I25" location="'認証実装チェック-03_正常系確認用トークン取得'!A1"/>
-    <hyperlink ref="I26" location="'認証実装チェック-04_未認証アクセス確認'!A1"/>
-    <hyperlink ref="I27" location="'認証実装チェック-05_正常系アクセス確認'!A1"/>
-    <hyperlink ref="I28" location="'認証実装チェック-06_確認結果判定'!A1"/>
-    <hyperlink ref="I29" location="'認証実装チェック-07_確認結果メトリクス送信'!A1"/>
-    <hyperlink ref="I30" location="'認証実装チェック-08_検知結果通知依頼'!A1"/>
-    <hyperlink ref="I31" location="'通知-01_通知先解決'!A1"/>
-    <hyperlink ref="I32" location="'通知-02_重要度別通知送信'!A1"/>
-    <hyperlink ref="I33" location="'通知-03_メトリクス閾値通知'!A1"/>
-    <hyperlink ref="I34" location="'運用-01_監視機構稼働監視通知'!A1"/>
-    <hyperlink ref="I35" location="'運用-02_処理失敗退避・再処理'!A1"/>
-    <hyperlink ref="I36" location="'運用-03_監視設定手動更新'!A1"/>
-    <hyperlink ref="I37" location="'連携-01_認証構成情報配置'!A1"/>
+    <hyperlink ref="I23" location="'全量-05_全量確認結果メトリクス送信'!A1"/>
+    <hyperlink ref="I24" location="'認証実装チェック-01_認証構成情報参照'!A1"/>
+    <hyperlink ref="I25" location="'認証実装チェック-02_API仕様取得'!A1"/>
+    <hyperlink ref="I26" location="'認証実装チェック-03_正常系確認用トークン取得'!A1"/>
+    <hyperlink ref="I27" location="'認証実装チェック-04_未認証アクセス確認'!A1"/>
+    <hyperlink ref="I28" location="'認証実装チェック-05_正常系アクセス確認'!A1"/>
+    <hyperlink ref="I29" location="'認証実装チェック-06_確認結果判定'!A1"/>
+    <hyperlink ref="I30" location="'認証実装チェック-07_確認結果メトリクス送信'!A1"/>
+    <hyperlink ref="I31" location="'認証実装チェック-08_検知結果通知依頼'!A1"/>
+    <hyperlink ref="I32" location="'通知-01_通知先解決'!A1"/>
+    <hyperlink ref="I33" location="'通知-02_重要度別通知送信'!A1"/>
+    <hyperlink ref="I34" location="'通知-03_メトリクス閾値通知'!A1"/>
+    <hyperlink ref="I35" location="'運用-01_監視機構稼働監視通知'!A1"/>
+    <hyperlink ref="I36" location="'運用-02_処理失敗退避・再処理'!A1"/>
+    <hyperlink ref="I37" location="'運用-03_監視設定手動更新'!A1"/>
+    <hyperlink ref="I38" location="'連携-01_認証構成情報配置'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13637,7 +13691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14011,12 +14065,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>payload に **origin:'full'** を付けて起点を記録する</t>
+          <t>**同時に走らせる子の数を 10 件までに制限する**（2026-09-15 確定）</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>検査側は origin を判定に使わず**ログにだけ出す**。これにより『巡回起点の検査』と『全量起点の検査』を後からログで区別できる。判定ロジックを分岐させないことで、モード1/モード2 で同一実装という原則を保つ</t>
+          <t>対象が 10 件を超える場合は 10 件ずつに区切って invoke する。同時実行数を一気に消費して巡回起点の検査（対象検索-11）を圧迫するのを防ぐ。Phase 1 の規模（3 アプリ × 2 環境 = 6 件）では実質的に制限に当たらず、将来 30 アプリでも 6 バッチで収まる</t>
         </is>
       </c>
     </row>
@@ -14026,12 +14080,12 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>【重要】**Lambda の再帰ループ検出に抵触しないことを確認する**</t>
+          <t>payload に **origin:'full'** を付けて起点を記録する</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>AWS は同一リクエストチェーン内で約 16 回の呼び出しを検出すると次の起動を自動停止する（既定 ON・無料・X-Ray のトレースヘッダで計数）。本設計のチェーンは**親（mode=full）→ 子（1 アプリ）の深さ 2 で終わり**、子はさらに自分自身を呼ばないため閾値に達しない。ただし将来 fan-out を多段化する場合は要注意。停止された場合は RecursiveInvocationsDropped メトリクスに現れる</t>
+          <t>検査側は origin を判定に使わず**ログにだけ出す**。これにより『巡回起点の検査』と『全量起点の検査』を後からログで区別できる。判定ロジックを分岐させないことで、モード1/モード2 で同一実装という原則を保つ</t>
         </is>
       </c>
     </row>
@@ -14041,12 +14095,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>invoke の失敗は記録して次の対象へ進む</t>
+          <t>【重要】**Lambda の再帰ループ検出に抵触しないことを確認する**</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>1 アプリの起動失敗で全量確認を止めない（18 §18.5.2）</t>
+          <t>AWS は同一リクエストチェーン内で約 16 回の呼び出しを検出すると次の起動を自動停止する（既定 ON・無料・X-Ray のトレースヘッダで計数）。本設計のチェーンは**親（mode=full）→ 子（1 アプリ）の深さ 2 で終わり**、子はさらに自分自身を呼ばないため閾値に達しない。ただし将来 fan-out を多段化する場合は要注意。停止された場合は RecursiveInvocationsDropped メトリクスに現れる</t>
         </is>
       </c>
     </row>
@@ -14056,12 +14110,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>親は子の完了を待たない</t>
+          <t>invoke の失敗は記録して次の対象へ進む</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>非同期のため即座に返る。結果はメトリクス（認証実装チェック-07）と通知（認証実装チェック-08）で収束する</t>
+          <t>1 アプリの起動失敗で全量確認を止めない（18 §18.5.2）</t>
         </is>
       </c>
     </row>
@@ -14071,338 +14125,331 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
+          <t>親は子の完了を待たない</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>非同期のため即座に返る。結果はメトリクス（認証実装チェック-07）と通知（認証実装チェック-08）で収束する</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
           <t>全対象の invoke が終わったら親は終了する</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>親自身は検査結果を集計しない（集計はメトリクス側の役割）</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>認証実装チェック Lambda(mode=full) -&gt; 認証実装チェック Lambda(1 アプリ分) : アプリ数分 Invoke(Event)
 【シーケンス図の所在】18 §18.1 実行モード図・§18.3 / 10 §10.1.7 F2</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39"/>
     <row r="40"/>
     <row r="41"/>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="42"/>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>参照</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>同時実行数の上限に当たる（429）</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>API 例外</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>**AWS 仕様では 429 / 5xx はイベントがキューに戻り、最大 6 時間・指数バックオフ（最大 5 分間隔）で再試行される**。呼び出し側は受理されなかった分のみ失敗として記録する</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>長期化すれば MM-4 → P2 Platform</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>AWS 公式（invocation-async-error-handling）</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>子が関数エラーで失敗</t>
+          <t>同時実行数の上限に当たる（429）</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Lambda 側</t>
+          <t>API 例外</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>既定 2 回リトライ（1 分後・2 分後）。枯渇で On-failure Destination へ</t>
+          <t>**AWS 仕様では 429 / 5xx はイベントがキューに戻り、最大 6 時間・指数バックオフ（最大 5 分間隔）で再試行される**。呼び出し側は受理されなかった分のみ失敗として記録する</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>MM-4（Destination 滞留 ≥ 1）→ P2 Platform</t>
+          <t>長期化すれば MM-4 → P2 Platform</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>18 §18.5.1</t>
+          <t>AWS 公式（invocation-async-error-handling）</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>再帰ループ検出で停止された</t>
+          <t>子が関数エラーで失敗</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>RecursiveInvocationsDropped メトリクス</t>
+          <t>Lambda 側</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>**本設計では発生しない想定**（深さ 2）。発生したら多段 fan-out の混入を疑う</t>
+          <t>既定 2 回リトライ（1 分後・2 分後）。枯渇で On-failure Destination へ</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>MM-4 相当として P2 Platform</t>
+          <t>MM-4（Destination 滞留 ≥ 1）→ P2 Platform</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>AWS 公式（invocation-recursion）</t>
+          <t>18 §18.5.1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>同一アプリが巡回起点の検査と重なる</t>
+          <t>再帰ループ検出で停止された</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RecursiveInvocationsDropped メトリクス</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>二重に検査されるが読み取り専用のため無害。origin でログ上は区別できる</t>
+          <t>**本設計では発生しない想定**（深さ 2）。発生したら多段 fan-out の混入を疑う</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MM-4 相当として P2 Platform</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>18 §18.5.2</t>
+          <t>AWS 公式（invocation-recursion）</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
+          <t>同一アプリが巡回起点の検査と重なる</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>二重に検査されるが読み取り専用のため無害。origin でログ上は区別できる</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
           <t>対象が 1 件のみ（手動の部分実行）</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>全量-03 の出力</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>1 回だけ invoke する（特別扱いはしない）</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>全量-02</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="10" t="n"/>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>再実行時の振る舞い</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>**at-least-once**。同じアプリへ複数回の検査依頼が飛びうるが、検査は読み取り専用で冪等のため無害。AWS 公式も非同期キューが結果整合性であり同一イベントが複数回届きうると明記している（18 §18.5.2）。</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>状態更新のタイミング</t>
+          <t>再実行時の振る舞い</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>状態を更新しない。**全量確認は台帳を書かない**（台帳を書くのは巡回の責務）。したがって lastArtifactVersions は全量確認では変化せず、巡回の差分判定に影響を与えない。</t>
+          <t>**at-least-once**。同じアプリへ複数回の検査依頼が飛びうるが、検査は読み取り専用で冪等のため無害。AWS 公式も非同期キューが結果整合性であり同一イベントが複数回届きうると明記している（18 §18.5.2）。</t>
         </is>
       </c>
       <c r="C54" s="4" t="n"/>
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="n"/>
     </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>状態更新のタイミング</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。**全量確認は台帳を書かない**（台帳を書くのは巡回の責務）。したがって lastArtifactVersions は全量確認では変化せず、巡回の差分判定に影響を与えない。</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>8. 権限・エンドポイント</t>
         </is>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>権限 / エンドポイント</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>lambda:InvokeFunction（自身）/ lambda.{region}.amazonaws.com</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>認証方式・補足</t>
+          <t>権限 / エンドポイント</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>lambda:InvokeFunction（**自分自身の関数 ARN**）。共通基盤アカウント内のため AssumeRole は不要
-非同期のペイロード上限は 1 MB（同期の 6 MB とは別）。本 payload は数十バイトで問題にならない</t>
+          <t>lambda:InvokeFunction（自身）/ lambda.{region}.amazonaws.com</t>
         </is>
       </c>
       <c r="C58" s="4" t="n"/>
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="n"/>
     </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>認証方式・補足</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>lambda:InvokeFunction（**自分自身の関数 ARN**）。共通基盤アカウント内のため AssumeRole は不要
+非同期のペイロード上限は 1 MB（同期の 6 MB とは別）。本 payload は数十バイトで問題にならない</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>アプリログ</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>fan-out 実行</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>対象件数 / invoke 成功件数 / 失敗件数 / 所要 ms</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -14414,166 +14461,188 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
+          <t>fan-out 実行</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>対象件数 / invoke 成功件数 / 失敗件数 / 所要 ms</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
           <t>子の起動</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>appId / env / origin=full / 相関 ID</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>親の実行 ID を引き回して親子を紐づける</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="10" t="n"/>
-      <c r="B64" s="10" t="n"/>
-      <c r="C64" s="10" t="n"/>
-      <c r="D64" s="10" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="10" t="n"/>
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="10" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>想定件数 / 所要時間</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>対象アプリ数 × 1 invoke。Phase 1 は 6 件（3 アプリ × 2 環境）、将来 30 アプリでも 60 件で数秒</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>上限・制約</t>
+          <t>想定件数 / 所要時間</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>**同時実行数（既定 1,000）を対象件数分消費する**。アプリ単位の並列は別ドメインへのアクセスのため1 アプリに負荷が集中することはないが、件数が増えたら並列度の上限設定を検討する（M-Q-PD-18）。Lambda のスケーリングは 1 関数あたり 10 秒で 1,000 実行環境まで</t>
+          <t>対象アプリ数 × 1 invoke。Phase 1 は 6 件（3 アプリ × 2 環境）、将来 30 アプリでも 60 件で数秒</t>
         </is>
       </c>
       <c r="C68" s="4" t="n"/>
       <c r="D68" s="4" t="n"/>
       <c r="E68" s="4" t="n"/>
     </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>上限・制約</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>**同時実行は 10 件までに制限する**（2026-09-15 確定）。既定の同時実行数 1,000 に対して十分小さく、巡回起点の検査（対象検索-11）と競合しない。アプリ単位の並列は別ドメインへのアクセスのため 1 アプリに負荷は集中しない。Lambda のスケーリングは 1 関数あたり 10 秒で 1,000 実行環境まで</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="7" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>M-Q-PD-18</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>fan-out の並列度に上限を設けるか。アプリ単位の並列は別ドメインへのアクセスなので負荷は分散するが、アプリ数が増えると同時実行数を一気に消費し、巡回起点の検査（対象検索-11）を圧迫する可能性がある。案: 予約同時実行の割り当て、またはバッチ分割して時間をずらす</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>設計担当</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
+          <t>M-Q-PD-18</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>【解決・2026-09-15】**同時実行の上限を 10 件**とする。10 件ずつのバッチで invoke し、巡回起点の検査を圧迫しないようにする。アプリ数の見込み（数〜30 程度）に対して十分で、Phase 1 では制限に当たらない</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>—（解決済み）</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
           <t>M-Q-PD-19</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>payload に origin を追加することの確認（検査側は判定に使わずログ出力のみ）。code-samples/README §2 のイベント形式に追記が必要</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>設計担当</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="n"/>
-      <c r="B74" s="10" t="n"/>
-      <c r="C74" s="10" t="n"/>
-      <c r="D74" s="10" t="n"/>
+      <c r="D74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="n"/>
+      <c r="B75" s="10" t="n"/>
+      <c r="C75" s="10" t="n"/>
+      <c r="D75" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A38:E42"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
     <mergeCell ref="B68:E68"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B55:E55"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A61:E61"/>
     <mergeCell ref="B54:E54"/>
     <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A37:E37"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="B59:E59"/>
     <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B58:E58"/>
-    <mergeCell ref="A37:E41"/>
+    <mergeCell ref="A71:E71"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="A52:E52"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="B10:E10"/>
+    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14582,11 +14651,11 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00C6E0B4"/>
+    <tabColor rgb="009DC3E6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14599,7 +14668,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>認証実装チェック-01  認証構成情報参照</t>
+          <t>全量-05  全量確認結果メトリクス送信</t>
         </is>
       </c>
     </row>
@@ -14618,7 +14687,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>確認対象アプリの設定値（検査先 URL・認証方式・トークン設定）を台帳から取得する。</t>
+          <t>全量確認の fan-out が完了したことを示すハートビートを送信する。これが止まることが MM-6（全量確認の停止）の検知トリガーになる。</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -14640,7 +14709,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック（1 アプリの確認・共通）</t>
+          <t>全量（全量確認 固有）</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -14655,7 +14724,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>共通（対象検索・全量とも）</t>
+          <t>全量（日次・手動）</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -14668,7 +14737,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>全量確認の最終処理（親側）。**巡回における 対象検索-14 と対になる**。子（1 アプリの検査）の結果は 認証実装チェック-07 が別途メトリクス化するため、本処理は「親が完走したか」だけを扱う。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -14696,7 +14769,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>認証構成情報配置バケット（registry/）</t>
+          <t>CloudWatch</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -14741,7 +14814,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>アプリごとに 1 回</t>
+          <t>全量確認ごとに 1 回</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -14754,7 +14827,11 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>全量-03 / 全量-04 が完了していること（一部アプリの invoke 失敗は許容）</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -14794,11 +14871,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>全量確認サマリ</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>{対象件数, invoke 成功件数, invoke 失敗件数, 除外件数}</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>全量-03 / 全量-04</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n"/>
@@ -14807,53 +14904,100 @@
       <c r="D18" s="10" t="n"/>
       <c r="E18" s="10" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>3. 出力（O）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>3. 出力（O）</t>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>出力先</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>説明・例</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>出力先</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>説明・例</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>FullScanLastSuccess</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Count=1</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch（共通基盤）</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>**全量確認が完走したこと**を示すハートビート。MM-6 の入力（2026-09-15 新設）</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>FullScanTargets</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Count=N</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch（共通基盤）</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>検査対象としたアプリ×環境の件数。増減の傾向把握に使う</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>FullScanInvokeErrors</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Count=N</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch（共通基盤）</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>fan-out の invoke に失敗した件数</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n"/>
@@ -14886,151 +15030,269 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】台帳が取得できない場合（削除・権限不足）の扱いを明記する</t>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>fan-out が完了したら FullScanLastSuccess = 1 を PutMetricData する</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>【重要】**「子の検査が終わったこと」ではなく「親が割り振りを終えたこと」を示す**。親は非同期のため子の完了を待たない（全量-04）。子の失敗は MM-4 が別に受け持つ</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>一部アプリの invoke に失敗していても FullScanLastSuccess は 1 を出す</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>対象検索-14 と同じ考え方。部分失敗は FullScanInvokeErrors（および MM-4）が受け持ち、MM-6 は『全量確認そのものが動いていない』ことだけを見る。役割を混ぜない</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>対象件数・invoke 失敗件数もあわせて送信する</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>0 件でも 0 を出す。値を出さないと欠損と区別できない</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="A32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>ディメンションは最小限にする</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>メトリクスはディメンションの組合せごとに課金される（RC-7 が最大費目）。アプリ次元は持たせない</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>PutMetricData の失敗は記録して握り潰す</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>メトリクス送信の失敗で全量確認の結果を覆さない</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>認証実装チェック Lambda -&gt; 配置バケット : GetObject(registry/{appId}/{env}.json)
-配置バケット --&gt; 認証実装チェック Lambda : 台帳 JSON
-【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37"/>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック Lambda -&gt; CloudWatch : PutMetricData(FullScanLastSuccess, FullScanTargets, FullScanInvokeErrors)
+【シーケンス図の所在】18 §18.1 実行モード図・§18.3 / 10 §10.1.7 F2</t>
+        </is>
+      </c>
+    </row>
     <row r="38"/>
     <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40"/>
+    <row r="41"/>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
     <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>全量確認が異常終了（例外で落ちた）</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>FullScanLastSuccess を出さない → 48 時間欠損で MM-6 発報</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>MM-6 → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>対象 0 件で中断した（全量-03）</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>**FullScanLastSuccess を出さない**（完走していないため）</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>MM-4 → P2 + 48 時間後に MM-6</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>全量-03</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>7. 冪等性・リトライ</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>一部の invoke に失敗</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>全量-04</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>FullScanLastSuccess は 1、FullScanInvokeErrors は N</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>MM-4 → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.1</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>再実行時の振る舞い</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>PutMetricData 失敗</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>API 例外</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>記録して継続</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>結果として MM-6 が誤発報しうる</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>48 時間の猶予があるため、単発の失敗では発報に至らない</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>状態更新のタイミング</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
+      <c r="A49" s="10" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>8. 権限・エンドポイント</t>
+          <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>権限 / エンドポイント</t>
+          <t>再実行時の振る舞い</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>s3:GetObject</t>
+          <t>同じ全量確認で複数回送っても CloudWatch 側は同一タイムスタンプの値として扱う。実害はないが 1 回に留める。</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
@@ -15040,10 +15302,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>認証方式・補足</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
+          <t>状態更新のタイミング</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。**全量確認は台帳を書かない**（書くのは巡回の責務）。</t>
+        </is>
+      </c>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
@@ -15051,146 +15317,229 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
+          <t>8. 権限・エンドポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>cloudwatch:PutMetricData / monitoring.{region}.amazonaws.com</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>認証方式・補足</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>cloudwatch:PutMetricData。共通基盤アカウント内のため AssumeRole は不要</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>全量確認完了サマリ</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>対象件数 / invoke 成功・失敗件数 / 除外件数 / 総所要 ms / トリガ種別</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>運用ダッシュボードの元データ（WBS W4-3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>メトリクス</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>FullScanLastSuccess / FullScanTargets / FullScanInvokeErrors</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>上記</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>名前空間・ディメンションは監視設計書（WBS B0-d）で確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="n"/>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>想定件数 / 所要時間</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>1 日 1 回（+手動実行分）。カスタムメトリクス 3 種で月 $1 未満（RC-7 の一部）</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>上限・制約</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>PutMetricData は 1 リクエスト 1 MB / 1,000 メトリクス / 30 ディメンションまで。本用途では上限に当たらない</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="71">
+      <c r="A71" s="10" t="n"/>
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="10" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="n"/>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A59:E59"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A65:E65"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B66:E66"/>
     <mergeCell ref="A55:E55"/>
+    <mergeCell ref="B56:E56"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A37:E41"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B67:E67"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B57:E57"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15216,7 +15565,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>認証実装チェック-02  API 仕様取得</t>
+          <t>認証実装チェック-01  認証構成情報参照</t>
         </is>
       </c>
     </row>
@@ -15235,7 +15584,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>確認対象の endpoint 一覧と公開明示（MON-1）を取得する。</t>
+          <t>確認対象アプリの設定値（検査先 URL・認証方式・トークン設定）を台帳から取得する。</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -15313,7 +15662,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>認証構成情報配置バケット（openapi/）</t>
+          <t>認証構成情報配置バケット（registry/）</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -15509,7 +15858,7 @@
       <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>【設計時の要記載】API 仕様が存在しない場合（モノリスの endpoint 列挙方式）の分岐を明記する</t>
+          <t>【設計時の要記載】台帳が取得できない場合（削除・権限不足）の扱いを明記する</t>
         </is>
       </c>
     </row>
@@ -15538,8 +15887,8 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック Lambda -&gt; 配置バケット : GetObject(openApiS3Key)
-配置バケット --&gt; 認証実装チェック Lambda : API 仕様
+          <t>認証実装チェック Lambda -&gt; 配置バケット : GetObject(registry/{appId}/{env}.json)
+配置バケット --&gt; 認証実装チェック Lambda : 台帳 JSON
 【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
         </is>
       </c>
@@ -15833,7 +16182,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>認証実装チェック-03  正常系確認用トークン取得</t>
+          <t>認証実装チェック-02  API 仕様取得</t>
         </is>
       </c>
     </row>
@@ -15852,7 +16201,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>正常系アクセス確認で使う短命トークンを取得する。</t>
+          <t>確認対象の endpoint 一覧と公開明示（MON-1）を取得する。</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -15930,7 +16279,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Secrets Manager → 認証基盤 /token</t>
+          <t>認証構成情報配置バケット（openapi/）</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -15975,7 +16324,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>確認ごとに 1 回</t>
+          <t>アプリごとに 1 回</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -16126,7 +16475,7 @@
       <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>【設計時の要記載】トークンのキャッシュ有無・失効時の再取得・ログへのマスク（トークンを出力しない）を明記する</t>
+          <t>【設計時の要記載】API 仕様が存在しない場合（モノリスの endpoint 列挙方式）の分岐を明記する</t>
         </is>
       </c>
     </row>
@@ -16155,9 +16504,8 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック Lambda -&gt; Secrets Manager : GetSecretValue
-認証実装チェック Lambda -&gt; 認証基盤 /token : client_credentials
-認証基盤 --&gt; 認証実装チェック Lambda : access_token（短命）
+          <t>認証実装チェック Lambda -&gt; 配置バケット : GetObject(openApiS3Key)
+配置バケット --&gt; 認証実装チェック Lambda : API 仕様
 【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
         </is>
       </c>
@@ -16265,7 +16613,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>secretsmanager:GetSecretValue / 認証基盤の公開 /token（インターネット経由・OAuth client_credentials）</t>
+          <t>s3:GetObject</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
@@ -16438,6 +16786,624 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>認証実装チェック-03  正常系確認用トークン取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>0. 概要</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>概要</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>正常系アクセス確認で使う短命トークンを取得する。</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>1. 基本情報</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>系統</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック（1 アプリの確認・共通）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>実行契機</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>共通（対象検索・全量とも）</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>フロー内の位置</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>起動元</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック Lambda</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>起動先</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Secrets Manager → 認証基盤 /token</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>呼び出し方式</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>同期</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>実行主体</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック Lambda</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>頻度・タイミング</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>確認ごとに 1 回</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>前提条件・事前状態</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2. 入力（I）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>取得元</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>説明・例</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>3. 出力（O）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>出力先</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>説明・例</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>4. 処理手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>補足・参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr"/>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>【設計時の要記載】トークンのキャッシュ有無・失効時の再取得・ログへのマスク（トークンを出力しない）を明記する</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック Lambda -&gt; Secrets Manager : GetSecretValue
+認証実装チェック Lambda -&gt; 認証基盤 /token : client_credentials
+認証基盤 --&gt; 認証実装チェック Lambda : access_token（短命）
+【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>6. 例外・異常系</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>ケース</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>検知方法</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>動作</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>7. 冪等性・リトライ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>再実行時の振る舞い</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>状態更新のタイミング</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>8. 権限・エンドポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>secretsmanager:GetSecretValue / 認証基盤の公開 /token（インターネット経由・OAuth client_credentials）</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>認証方式・補足</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>9. ログ・メトリクス</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>名称・項目</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n"/>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>10. 性能・上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>想定件数 / 所要時間</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>上限・制約</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr"/>
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>11. 未決事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>確認先</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n"/>
+      <c r="B66" s="10" t="n"/>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="10" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="n"/>
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="A35:E39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C6E0B4"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -17701,623 +18667,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00C6E0B4"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E67"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>認証実装チェック-05  正常系アクセス確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>0. 概要</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>概要</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>有効なトークン付きでリクエストし、200 が返ることで API 稼働と確認処理自体の健全性を確かめる。</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>1. 基本情報</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>系統</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>認証実装チェック（1 アプリの確認・共通）</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>実行契機</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>共通（対象検索・全量とも）</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>フロー内の位置</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>起動元</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>認証実装チェック Lambda</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>起動先</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>CloudFront → WAF → API GW / ALB</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>呼び出し方式</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>同期</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>実行主体</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>認証実装チェック Lambda</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>頻度・タイミング</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>endpoint ごとに 1 回</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>前提条件・事前状態</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>2. 入力（I）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>取得元</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>説明・例</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>3. 出力（O）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>出力先</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>説明・例</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>4. 処理手順</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>処理内容</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>補足・参照</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】参照系のみ実行すること（更新系を叩かない）、対象 endpoint の選定規則を明記する</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>認証実装チェック Lambda -&gt; CloudFront : GET（Authorization: Bearer …, X-Auth-Probe）
-API GW --&gt; 認証実装チェック Lambda : ステータスコード
-【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>6. 例外・異常系</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>ケース</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>検知方法</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>動作</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>通知</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>参照</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>7. 冪等性・リトライ</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>再実行時の振る舞い</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>状態更新のタイミング</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>8. 権限・エンドポイント</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>権限 / エンドポイント</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Bearer（認証実装チェック-03 のトークン）/ HTTPS 443 / X-Auth-Probe ヘッダ付与</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>認証方式・補足</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>9. ログ・メトリクス</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>名称・項目</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>10. 性能・上限</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>想定件数 / 所要時間</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>上限・制約</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>11. 未決事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>確認先</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>期限</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -18338,7 +18687,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>認証実装チェック-06  確認結果判定（4×4）</t>
+          <t>認証実装チェック-05  正常系アクセス確認</t>
         </is>
       </c>
     </row>
@@ -18357,7 +18706,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>未認証アクセス確認と正常系アクセス確認の結果の組み合わせから、重要度（CRITICAL / WARN / INFO / OK）を判定する。</t>
+          <t>有効なトークン付きでリクエストし、200 が返ることで API 稼働と確認処理自体の健全性を確かめる。</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -18420,7 +18769,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック Lambda（内部）</t>
+          <t>認証実装チェック Lambda</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -18435,7 +18784,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CloudFront → WAF → API GW / ALB</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -18450,7 +18799,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>同期</t>
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -18631,7 +18980,7 @@
       <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>【設計時の要記載】4×4 の全組み合わせと重要度の対応表を貼る（code-samples/README §2 が正）</t>
+          <t>【設計時の要記載】参照系のみ実行すること（更新系を叩かない）、対象 endpoint の選定規則を明記する</t>
         </is>
       </c>
     </row>
@@ -18660,8 +19009,8 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック Lambda : (未認証結果, 正常系結果) -&gt; 4×4 真偽値表 -&gt; 重要度決定
-WAF 起因の 403 は WARN（構成）に分類
+          <t>認証実装チェック Lambda -&gt; CloudFront : GET（Authorization: Bearer …, X-Auth-Probe）
+API GW --&gt; 認証実装チェック Lambda : ステータスコード
 【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
         </is>
       </c>
@@ -18769,7 +19118,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>—（AWS 呼び出しなし）</t>
+          <t>Bearer（認証実装チェック-03 のトークン）/ HTTPS 443 / X-Auth-Probe ヘッダ付与</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
@@ -18955,7 +19304,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>認証実装チェック-07  確認結果メトリクス送信</t>
+          <t>認証実装チェック-06  確認結果判定（4×4）</t>
         </is>
       </c>
     </row>
@@ -18974,7 +19323,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>確認結果をメトリクス化し、保険系アラーム（AuthCheckCritical &gt; 0）の入力とする。</t>
+          <t>未認証アクセス確認と正常系アクセス確認の結果の組み合わせから、重要度（CRITICAL / WARN / INFO / OK）を判定する。</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -19037,7 +19386,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック Lambda</t>
+          <t>認証実装チェック Lambda（内部）</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -19052,7 +19401,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>CloudWatch</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -19067,7 +19416,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>同期</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -19097,7 +19446,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>確認ごとに 1 回</t>
+          <t>endpoint ごとに 1 回</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -19248,7 +19597,7 @@
       <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>【設計時の要記載】ディメンション設計（アプリ数比例でメトリクス課金が増える点に注意）を明記する</t>
+          <t>【設計時の要記載】4×4 の全組み合わせと重要度の対応表を貼る（code-samples/README §2 が正）</t>
         </is>
       </c>
     </row>
@@ -19277,7 +19626,8 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック Lambda -&gt; CloudWatch : PutMetricData(AuthCheckCritical ほか, ディメンション=appId/env)
+          <t>認証実装チェック Lambda : (未認証結果, 正常系結果) -&gt; 4×4 真偽値表 -&gt; 重要度決定
+WAF 起因の 403 は WARN（構成）に分類
 【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
         </is>
       </c>
@@ -19385,7 +19735,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>cloudwatch:PutMetricData / monitoring.{region}.amazonaws.com</t>
+          <t>—（AWS 呼び出しなし）</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
@@ -19571,7 +19921,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>認証実装チェック-08  検知結果通知依頼</t>
+          <t>認証実装チェック-07  確認結果メトリクス送信</t>
         </is>
       </c>
     </row>
@@ -19590,7 +19940,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>判定済みの検知結果を、通知の振り分けを行うアラート検知 Lambda へ引き渡す。</t>
+          <t>確認結果をメトリクス化し、保険系アラーム（AuthCheckCritical &gt; 0）の入力とする。</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -19668,7 +20018,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>アラート検知 Lambda</t>
+          <t>CloudWatch</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -19683,7 +20033,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>非同期</t>
+          <t>同期</t>
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -19713,7 +20063,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>重要度≠OK 時</t>
+          <t>確認ごとに 1 回</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -19864,7 +20214,7 @@
       <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>【設計時の要記載】イベント形式（README §2.6）と、配列でのバッチ送付の可否を明記する</t>
+          <t>【設計時の要記載】ディメンション設計（アプリ数比例でメトリクス課金が増える点に注意）を明記する</t>
         </is>
       </c>
     </row>
@@ -19893,7 +20243,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック Lambda -&gt; アラート検知 Lambda : Invoke(Event, 4×4 判定済みイベント)
+          <t>認証実装チェック Lambda -&gt; CloudWatch : PutMetricData(AuthCheckCritical ほか, ディメンション=appId/env)
 【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
         </is>
       </c>
@@ -20001,7 +20351,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>lambda:InvokeFunction（InvocationType=Event）</t>
+          <t>cloudwatch:PutMetricData / monitoring.{region}.amazonaws.com</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
@@ -20634,7 +20984,7 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00F4B183"/>
+    <tabColor rgb="00C6E0B4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -20651,7 +21001,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>通知-01  通知先解決</t>
+          <t>認証実装チェック-08  検知結果通知依頼</t>
         </is>
       </c>
     </row>
@@ -20670,7 +21020,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>台帳の通知先設定から送信先を解決する。未設定時は全社デフォルトを使う。</t>
+          <t>判定済みの検知結果を、通知の振り分けを行うアラート検知 Lambda へ引き渡す。</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -20692,7 +21042,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>通知（アラート通知）</t>
+          <t>認証実装チェック（1 アプリの確認・共通）</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -20707,7 +21057,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>共通（検知時）</t>
+          <t>共通（対象検索・全量とも）</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -20733,7 +21083,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>アラート検知 Lambda</t>
+          <t>認証実装チェック Lambda</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -20748,7 +21098,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>認証構成情報配置バケット（registry/）</t>
+          <t>アラート検知 Lambda</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -20763,7 +21113,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>同期</t>
+          <t>非同期</t>
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -20778,7 +21128,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>アラート検知 Lambda</t>
+          <t>認証実装チェック Lambda</t>
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -20793,7 +21143,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>イベントごとに 1 回</t>
+          <t>重要度≠OK 時</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -20944,7 +21294,7 @@
       <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>【設計時の要記載】2 段解決（アプリ個別 → 全社デフォルト）の順序と、未解決時に throw する仕様を明記する</t>
+          <t>【設計時の要記載】イベント形式（README §2.6）と、配列でのバッチ送付の可否を明記する</t>
         </is>
       </c>
     </row>
@@ -20973,9 +21323,8 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>アラート検知 Lambda -&gt; 配置バケット : GetObject（alertRouting 参照）
-未設定 -&gt; 全社デフォルト ARN
-【シーケンス図の所在】15 §15.1 振り分けフロー / 10 §10.1.7 F3</t>
+          <t>認証実装チェック Lambda -&gt; アラート検知 Lambda : Invoke(Event, 4×4 判定済みイベント)
+【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
         </is>
       </c>
     </row>
@@ -21082,7 +21431,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>s3:GetObject</t>
+          <t>lambda:InvokeFunction（InvocationType=Event）</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
@@ -21268,7 +21617,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>通知-02  重要度別通知送信</t>
+          <t>通知-01  通知先解決</t>
         </is>
       </c>
     </row>
@@ -21287,7 +21636,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>重要度に応じた宛先へ通知を送信する。</t>
+          <t>台帳の通知先設定から送信先を解決する。未設定時は全社デフォルトを使う。</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -21365,7 +21714,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>SNS（P1 Security / P2 Platform / P3 App）</t>
+          <t>認証構成情報配置バケット（registry/）</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -21561,7 +21910,7 @@
       <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>【設計時の要記載】通知本文のテンプレートと、1 件でも失敗したら throw（DLQ 発火）する仕様を明記する</t>
+          <t>【設計時の要記載】2 段解決（アプリ個別 → 全社デフォルト）の順序と、未解決時に throw する仕様を明記する</t>
         </is>
       </c>
     </row>
@@ -21590,7 +21939,8 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>アラート検知 Lambda -&gt; SNS(P1|P2|P3) : Publish（件名・本文・appId・endpoint・判定根拠）
+          <t>アラート検知 Lambda -&gt; 配置バケット : GetObject（alertRouting 参照）
+未設定 -&gt; 全社デフォルト ARN
 【シーケンス図の所在】15 §15.1 振り分けフロー / 10 §10.1.7 F3</t>
         </is>
       </c>
@@ -21698,7 +22048,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>sns:Publish / sns.{region}.amazonaws.com</t>
+          <t>s3:GetObject</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
@@ -21884,7 +22234,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>通知-03  メトリクス閾値通知（保険系）</t>
+          <t>通知-02  重要度別通知送信</t>
         </is>
       </c>
     </row>
@@ -21903,7 +22253,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>アラート検知 Lambda の経路とは独立に、メトリクス閾値からも発報する（発報 2 系統の保険側）。</t>
+          <t>重要度に応じた宛先へ通知を送信する。</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -21940,7 +22290,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>共通（閾値超過時）</t>
+          <t>共通（検知時）</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -21966,7 +22316,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>CloudWatch Alarm</t>
+          <t>アラート検知 Lambda</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -21981,7 +22331,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SNS（P1 Security / P2 Platform / P3 App）</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -21996,7 +22346,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>非同期</t>
+          <t>同期</t>
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -22011,7 +22361,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>CloudWatch</t>
+          <t>アラート検知 Lambda</t>
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -22026,7 +22376,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>閾値超過時</t>
+          <t>イベントごとに 1 回</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -22177,7 +22527,7 @@
       <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>【設計時の要記載】即時系（アラート検知 Lambda）と保険系の重複通知の扱いを明記する</t>
+          <t>【設計時の要記載】通知本文のテンプレートと、1 件でも失敗したら throw（DLQ 発火）する仕様を明記する</t>
         </is>
       </c>
     </row>
@@ -22206,7 +22556,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CloudWatch Alarm(AuthCheckCritical &gt; 0) -&gt; SNS : 通知
+          <t>アラート検知 Lambda -&gt; SNS(P1|P2|P3) : Publish（件名・本文・appId・endpoint・判定根拠）
 【シーケンス図の所在】15 §15.1 振り分けフロー / 10 §10.1.7 F3</t>
         </is>
       </c>
@@ -22314,7 +22664,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CloudWatch Alarm → SNS（アラームアクション）</t>
+          <t>sns:Publish / sns.{region}.amazonaws.com</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
@@ -22483,7 +22833,7 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00C9C9C9"/>
+    <tabColor rgb="00F4B183"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -22500,7 +22850,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>運用-01  監視機構稼働監視通知（MM-1〜5）</t>
+          <t>通知-03  メトリクス閾値通知（保険系）</t>
         </is>
       </c>
     </row>
@@ -22519,7 +22869,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>監視機構そのものの停止・失敗を検知して発報する（監視の空白＝検知の空白を防ぐ）。</t>
+          <t>アラート検知 Lambda の経路とは独立に、メトリクス閾値からも発報する（発報 2 系統の保険側）。</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -22541,7 +22891,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>運用（運用・異常系）</t>
+          <t>通知（アラート通知）</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -22556,7 +22906,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>随時（異常時）</t>
+          <t>共通（閾値超過時）</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -22597,7 +22947,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>SNS（P2 Platform）</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -22793,7 +23143,7 @@
       <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>【設計時の要記載】MM-1〜5 の各アラーム定義（対象メトリクス・閾値・評価期間）を一覧化する</t>
+          <t>【設計時の要記載】即時系（アラート検知 Lambda）と保険系の重複通知の扱いを明記する</t>
         </is>
       </c>
     </row>
@@ -22822,8 +23172,8 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Alarm(DiscoveryLastSuccess 2h 欠損 / Lambda Errors / DLQ 滞留) -&gt; SNS(P2)
-【シーケンス図の所在】18 §18.5 運用設計 / 10 §10.1.7 F3</t>
+          <t>CloudWatch Alarm(AuthCheckCritical &gt; 0) -&gt; SNS : 通知
+【シーケンス図の所在】15 §15.1 振り分けフロー / 10 §10.1.7 F3</t>
         </is>
       </c>
     </row>
@@ -22930,7 +23280,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CloudWatch Alarm → SNS</t>
+          <t>CloudWatch Alarm → SNS（アラームアクション）</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
@@ -23116,7 +23466,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>運用-02  処理失敗退避・再処理（DLQ）</t>
+          <t>運用-01  監視機構稼働監視通知（MM-1〜5）</t>
         </is>
       </c>
     </row>
@@ -23135,7 +23485,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>非同期呼び出しがリトライ後も失敗した場合に退避し、後から再処理・原因調査できるようにする。</t>
+          <t>監視機構そのものの停止・失敗を検知して発報する（監視の空白＝検知の空白を防ぐ）。</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -23198,7 +23548,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>各 Lambda（非同期実行の失敗）</t>
+          <t>CloudWatch Alarm</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -23213,7 +23563,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>SQS DLQ → 運用者</t>
+          <t>SNS（P2 Platform）</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -23243,7 +23593,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Lambda / 運用者</t>
+          <t>CloudWatch</t>
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -23258,7 +23608,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>失敗時</t>
+          <t>閾値超過時</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -23409,7 +23759,7 @@
       <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>【設計時の要記載】DLQ の保持期間・再処理手順（Runbook 化）・滞留アラーム（MM-4/5）を明記する</t>
+          <t>【設計時の要記載】MM-1〜5 の各アラーム定義（対象メトリクス・閾値・評価期間）を一覧化する</t>
         </is>
       </c>
     </row>
@@ -23438,8 +23788,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Lambda(失敗) -&gt; 自動リトライ(2 回) -&gt; SQS DLQ
-運用者 -&gt; DLQ : 内容確認 -&gt; 再実行
+          <t>Alarm(DiscoveryLastSuccess 2h 欠損 / Lambda Errors / DLQ 滞留) -&gt; SNS(P2)
 【シーケンス図の所在】18 §18.5 運用設計 / 10 §10.1.7 F3</t>
         </is>
       </c>
@@ -23547,7 +23896,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Lambda 非同期呼び出しの DLQ 設定 / sqs:ReceiveMessage・DeleteMessage（運用者）</t>
+          <t>CloudWatch Alarm → SNS</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
@@ -23733,7 +24082,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>運用-03  監視設定手動更新</t>
+          <t>運用-02  処理失敗退避・再処理（DLQ）</t>
         </is>
       </c>
     </row>
@@ -23752,7 +24101,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>監視の有効・無効の切替や通知先の設定など、中央管理項目を運用者が更新する。</t>
+          <t>非同期呼び出しがリトライ後も失敗した場合に退避し、後から再処理・原因調査できるようにする。</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -23789,7 +24138,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>随時（運用操作）</t>
+          <t>随時（異常時）</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -23815,7 +24164,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>運用者</t>
+          <t>各 Lambda（非同期実行の失敗）</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -23830,7 +24179,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>認証構成情報配置バケット（registry/）</t>
+          <t>SQS DLQ → 運用者</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -23845,7 +24194,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>同期</t>
+          <t>非同期</t>
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -23860,7 +24209,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>運用者</t>
+          <t>Lambda / 運用者</t>
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -23875,7 +24224,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>失敗時</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -24026,7 +24375,7 @@
       <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>【設計時の要記載】巡回（対象検索-09）との競合手順、変更履歴の追跡（Versioning）、承認フローの要否を明記する</t>
+          <t>【設計時の要記載】DLQ の保持期間・再処理手順（Runbook 化）・滞留アラーム（MM-4/5）を明記する</t>
         </is>
       </c>
     </row>
@@ -24055,8 +24404,8 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>運用者 -&gt; 配置バケット : GetObject -&gt; 編集 -&gt; PutObject（If-Match）
-巡回と競合した場合は 412 -&gt; 再取得
+          <t>Lambda(失敗) -&gt; 自動リトライ(2 回) -&gt; SQS DLQ
+運用者 -&gt; DLQ : 内容確認 -&gt; 再実行
 【シーケンス図の所在】18 §18.5 運用設計 / 10 §10.1.7 F3</t>
         </is>
       </c>
@@ -24164,7 +24513,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>s3:GetObject / s3:PutObject（ETag 条件付き）</t>
+          <t>Lambda 非同期呼び出しの DLQ 設定 / sqs:ReceiveMessage・DeleteMessage（運用者）</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
@@ -24331,6 +24680,623 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9C9C9"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>運用-03  監視設定手動更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>0. 概要</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>概要</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>監視の有効・無効の切替や通知先の設定など、中央管理項目を運用者が更新する。</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>1. 基本情報</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>系統</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>運用（運用・異常系）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>実行契機</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>随時（運用操作）</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>フロー内の位置</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>起動元</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>運用者</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>起動先</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>認証構成情報配置バケット（registry/）</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>呼び出し方式</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>同期</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>実行主体</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>運用者</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>頻度・タイミング</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>前提条件・事前状態</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2. 入力（I）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>取得元</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>説明・例</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>3. 出力（O）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>出力先</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>説明・例</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>4. 処理手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>補足・参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr"/>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>【設計時の要記載】巡回（対象検索-09）との競合手順、変更履歴の追跡（Versioning）、承認フローの要否を明記する</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>運用者 -&gt; 配置バケット : GetObject -&gt; 編集 -&gt; PutObject（If-Match）
+巡回と競合した場合は 412 -&gt; 再取得
+【シーケンス図の所在】18 §18.5 運用設計 / 10 §10.1.7 F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>6. 例外・異常系</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>ケース</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>検知方法</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>動作</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>7. 冪等性・リトライ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>再実行時の振る舞い</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>状態更新のタイミング</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>8. 権限・エンドポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>s3:GetObject / s3:PutObject（ETag 条件付き）</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>認証方式・補足</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>9. ログ・メトリクス</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>名称・項目</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n"/>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>10. 性能・上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>想定件数 / 所要時間</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>上限・制約</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr"/>
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>11. 未決事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>確認先</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n"/>
+      <c r="B66" s="10" t="n"/>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="10" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="n"/>
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="A35:E39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00D9B3E6"/>

--- a/doc/excel/apipf-process-design.xlsx
+++ b/doc/excel/apipf-process-design.xlsx
@@ -11980,9 +11980,9 @@
           <t>認証実装チェック-01_認証構成情報参照</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -12032,9 +12032,9 @@
           <t>認証実装チェック-02_API仕様取得</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -12188,9 +12188,9 @@
           <t>認証実装チェック-05_正常系アクセス確認</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -12240,9 +12240,9 @@
           <t>認証実装チェック-06_確認結果判定</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -12292,9 +12292,9 @@
           <t>認証実装チェック-07_確認結果メトリクス送信</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -12344,9 +12344,9 @@
           <t>認証実装チェック-08_検知結果通知依頼</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15634,7 +15634,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>1 アプリの検査の入口。巡回起点（対象検索-11）でも全量起点（全量-04）でも、ここから同じ処理が始まる。**payload の origin は判定に使わずログにのみ出す**ため、以降の処理は起点を意識しない（18 §18.3）。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -15720,7 +15724,12 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>payload に mode / appId / env が渡されていること（README §2.6）
+配置バケットへの s3:GetObject 権限があること</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -15760,18 +15769,58 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>appId / env</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>payload（対象検索-11 / 全量-04）</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>検査対象の単位</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>origin</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>delta（巡回起点）/ full（全量起点）。**ログ出力のみで判定には使わない**</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n"/>
@@ -15810,10 +15859,26 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>台帳レコード</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-02〜08（メモリ内）</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>baseUrl / authPattern / openApiS3Key / testTokenSecret / alertRouting / enabled</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n"/>
@@ -15821,56 +15886,89 @@
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>4. 処理手順</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>4. 処理手順</t>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>補足・参照</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>処理内容</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>補足・参照</t>
+      <c r="A28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>registry/{appId}/{env}.json を GetObject する</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>巡回が同期した実行用ビュー。検査側は台帳だけを見る</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】台帳が取得できない場合（削除・権限不足）の扱いを明記する</t>
+      <c r="A29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>enabled=false なら**検査せずに終了する**</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>中央が意図的に監視を止めたアプリ、または不備で取り込みを拒否したアプリ（対象検索-09 の拒否レコード）。全量起点では 全量-03 が既に除外しているが、巡回起点や手動 invoke では到達しうるため**ここでも必ず確認する**</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>baseUrl / authPattern / openApiS3Key を取り出す</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>**baseUrl は検査先そのもの**。台帳に入っている時点で 対象検索-08 のドメイン検証を通過している（2026-09-14 確定）</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>alertRouting は読むだけで解決はしない</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>通知先の解決はアラート検知 Lambda の責務（通知-01）。検査側で解決すると解決ロジックが 2 か所になる</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n"/>
@@ -15932,228 +16030,358 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>台帳が存在しない（削除された / appId 誤り）</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>NoSuchKey</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>検査せず終了し、エラーとして記録する</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>MM-4（Destination 滞留）→ P2 Platform</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>enabled=false</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>台帳値</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>検査せず正常終了（エラーではない）</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>通知なし</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>12 章 中央管理項目</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>JSON が壊れている</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>パース例外</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>検査せず終了しエラー記録</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>MM-4 → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>AccessDenied</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>API 例外</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>16 §16.3</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="10" t="n"/>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>再実行時の振る舞い</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>読み取りのみ。同じ台帳なら常に同じ結果。</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>状態更新のタイミング</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。**検査は台帳を一切書き換えない**（書くのは巡回の責務）。</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>8. 権限・エンドポイント</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>権限 / エンドポイント</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>s3:GetObject</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>認証方式・補足</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>s3:GetObject（配置バケット）。共通基盤アカウント内のため AssumeRole は不要</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>検査開始</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>appId / env / mode / origin / 相関 ID</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>origin により巡回起点か全量起点かを後から追える</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="10" t="n"/>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>想定件数 / 所要時間</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>1 アプリにつき 1 回の GetObject。台帳は KB オーダー</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>上限・制約</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>S3 GET は 5,500 req/s（プレフィックス単位）</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="68">
+      <c r="A68" s="10" t="n"/>
+      <c r="B68" s="10" t="n"/>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="10" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="n"/>
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="B64:E64"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B55:E55"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B50:E50"/>
     <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B54:E54"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A66:E66"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="A62:E62"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="A35:E39"/>
@@ -16169,7 +16397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16251,7 +16479,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-01 の直後。ここで「何を検査するか」= endpoint のリストが確定する。**本処理の抽出漏れはそのまま検査漏れになる**ため、解釈規則を厳密に定める。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -16337,7 +16569,12 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-01 で openApiS3Key を取得済み
+配置バケットへの s3:GetObject 権限</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -16377,18 +16614,58 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>openApiS3Key</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-01</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>openapi/{accountId}/{appId}/openapi.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>endpoint 列挙（代替）</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>台帳（monitoring.yaml 由来）</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>API 仕様が無いモノリス等で使う。17 §17.4</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n"/>
@@ -16427,10 +16704,26 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>endpoint 記述子リスト</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>[{method, path, rawPath, skipAuthCheck, positiveTest, pathParams, authMode, expectedRedirect}]</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-04〜06（メモリ内）</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>1 endpoint = 1 記述子。**認証実装チェック-04 の入力そのもの**</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n"/>
@@ -16438,71 +16731,164 @@
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>4. 処理手順</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>4. 処理手順</t>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>補足・参照</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>処理内容</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>補足・参照</t>
+      <c r="A28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>openApiS3Key で API 仕様を GetObject する</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>中央に複写された「デプロイされた版の写し」（対象検索-10）</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】API 仕様が存在しない場合（モノリスの endpoint 列挙方式）の分岐を明記する</t>
+      <c r="A29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>paths 配下を走査し、**HTTP メソッドのキーだけ**を endpoint として抽出する</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>【重要】paths 配下には `parameters` / `summary` / `description` / `servers` / `$ref` など**メソッドではないキーが同居しうる**。これらをメソッドと誤認すると存在しない endpoint を検査してしまう。抽出は get / put / post / delete / options / head / patch / trace の**許可リスト方式**にする</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>**公開明示（x-synthetics-skip-auth-check）を解釈する。未記載は false（＝認証必須）**</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>MON-1 の default-deny（13 §13.3.0）。ここを「未記載＝スキップ」にすると、うっかり公開した endpoint を永久に検知できなくなる。本機構の安全性の根幹</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>path parameter を x-canary-path-params の dummy 値で解決し、path と rawPath の 2 つを作る</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>path = 実際に叩く URL（/api/users/1）、rawPath = テンプレート（/api/users/{id}）。**rawPath はログ・アラートの識別子**に使う。dummy 値が無い場合の扱いは下記の例外参照</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="A32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>x-canary-positive-test を解釈し、正常系確認の対象かを決める</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>既定 false。pre-prod-only は本番では対象外（11 §11.5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>x-canary-auth-mode / x-canary-expected-redirect を解釈する（Cookie モノリス用）</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>302 が期待値になるケースの判定材料（認証実装チェック-06 へ渡す）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>**仕様側の servers は無視し、検査先は台帳の baseUrl を使う**</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>servers には開発用 URL や API GW の直 URL が書かれていることがあり、これに従うとCloudFront を経由しない検査になってしまう（実 UX と条件がずれ、Origin Protection も破る）。宛先を台帳の baseUrl に固定することが宛先 allowlist の担保にもなる（10 §10.1.6）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>API 仕様が無い場合は台帳の endpoint 列挙を使う</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>ALB 直モノリス等（17 §17.4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>認証実装チェック Lambda -&gt; 配置バケット : GetObject(openApiS3Key)
 配置バケット --&gt; 認証実装チェック Lambda : API 仕様
@@ -16510,223 +16896,335 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-    </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>7. 冪等性・リトライ</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>API 仕様が存在しない</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>NoSuchKey</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>台帳の endpoint 列挙にフォールバック。それも無ければ検査対象なしとして終了し記録する</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>列挙も無い場合はメタ不足として P2</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>17 §17.4</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>再実行時の振る舞い</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>paths が空 / 0 endpoint</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>解析結果</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>検査対象なしとして終了し記録する</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>メタ不足アラート → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>状態更新のタイミング</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>path parameter があるのに x-canary-path-params が無い</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>解析結果</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>**その endpoint をスキップせず、既定の dummy 値（例 1）で解決して検査する**。スキップすると認証漏れを見逃すため。404 になっても認証レイヤーの手前で弾かれるかは観測できる</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>メソッド以外のキー（parameters / summary 等）</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>解析</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>endpoint として抽出しない（許可リスト方式）</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.x 仕様</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>8. 権限・エンドポイント</t>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>$ref による外部参照</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>解析</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>**解決せず、その endpoint をスキップして記録する**。外部ファイルは中央に複写されていないため解決できない</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>メタ不足アラート → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-21</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>権限 / エンドポイント</t>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>仕様が巨大（数千 endpoint）</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>s3:GetObject</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>件数に上限を設け、超過分は検査せず記録する（Lambda の 15 分制限に当たらないため）</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>メタ不足アラート → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-22</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>認証方式・補足</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
+      <c r="A53" s="10" t="n"/>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>9. ログ・メトリクス</t>
+          <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>名称・項目</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>再実行時の振る舞い</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>読み取りと解析のみ。同じ仕様なら常に同じ endpoint リストが得られる。</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>状態更新のタイミング</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>8. 権限・エンドポイント</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>10. 性能・上限</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>s3:GetObject</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>想定件数 / 所要時間</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr"/>
+          <t>認証方式・補足</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>s3:GetObject（配置バケット）。共通基盤アカウント内</t>
+        </is>
+      </c>
       <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="n"/>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>上限・制約</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>9. ログ・メトリクス</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>11. 未決事項</t>
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>名称・項目</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>確認先</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>期限</t>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>endpoint 抽出</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>appId / env / 抽出件数 / 公開明示件数 / スキップ件数と理由</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>**パス一覧の全件出力はしない**（件数と代表値のみ）</t>
         </is>
       </c>
     </row>
@@ -16736,44 +17234,164 @@
       <c r="C66" s="10" t="n"/>
       <c r="D66" s="10" t="n"/>
     </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>10. 性能・上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>想定件数 / 所要時間</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>1 アプリにつき 1 回の GetObject と解析。数十〜数百 endpoint</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>上限・制約</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>仕様サイズは 対象検索-07 のサイズ上限で制御済み（M-Q-PD-6）。endpoint 件数上限は M-Q-PD-22</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" s="4" t="n"/>
+      <c r="E70" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>11. 未決事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>確認先</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-20</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>path parameter の dummy 値が未指定のときの既定値。案: 数値パラメータは 1、文字列は canary-test。実在しない ID になるため 404 が返りやすいが、**認証が効いていれば 404 より先に 401/403 が返る**ため検査は成立する</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-21</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>$ref による外部ファイル参照を解決するか。解決するなら参照先も認証構成情報として連携バケットに置いてもらう必要があり、アプリ側の作業が増える。案: 単一ファイルに bundle してからアップロードすることを規約にする（vendor-guide に追記）</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-22</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>1 アプリあたりの endpoint 件数上限（Lambda 15 分制限との兼ね合い）。W3-5 の性能実測で 1 endpoint あたりの所要時間を確定してから決める</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>設計担当（W3-5 と連動）</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="n"/>
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A59:E59"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="A39:E43"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A27:E27"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A55:E55"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B70:E70"/>
     <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B60:E60"/>
     <mergeCell ref="B61:E61"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A72:E72"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A63:E63"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18674,7 +19292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18756,7 +19374,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-04（未認証）の直後、同じ endpoint に対して実行する。**この確認があることで「検査自体が壊れている」ことを検知できる**（未認証だけだと、アプリが全面ダウンして全部 403 を返している状態を『認証が効いている』と誤認する）。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -18842,7 +19464,13 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-03 で短命トークンを取得済み
+対象 endpoint が x-canary-positive-test の対象であること（既定は対象外）
+本番では GET のみが対象（11 §11.5）</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -18882,132 +19510,320 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>access_token</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>string（機微）</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-03</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>**ログ・例外メッセージに出さない**（06 章 OBS-3）</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>ep.method / ep.path</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-02</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>ep.positiveTest</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>true / false / pre-prod-only</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-02</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>既定 false（対象外）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-01</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>pre-prod-only の判定に使う</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>3. 出力（O）</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>出力先</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>説明・例</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-    </row>
     <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>posStatus</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>number / null</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-06（メモリ内）</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>対象外の場合は null</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>処理内容</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>補足・参照</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
+    <row r="30">
+      <c r="A30" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】参照系のみ実行すること（更新系を叩かない）、対象 endpoint の選定規則を明記する</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>positiveTest が false なら本処理をスキップし posStatus = null を返す</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>既定は対象外。全 endpoint で正常系確認を回すとトークン発行と負荷が増えるため、明示指定された endpoint に限る</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>pre-prod-only かつ env が本番ならスキップする</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>11 §11.5</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="A32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>**本番では GET 以外をスキップする**</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>副作用回避の鉄則。POST 等は認証が効いていれば通らないが、**通ってしまったら本番データを更新する**。検証は stg 側で行う（11 §11.5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;token&gt; と X-Auth-Probe を付けてリクエストする</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>宛先・経路は 認証実装チェック-04 と同一（CloudFront 経由・Origin Protection は CloudFront が付与）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>応答ステータスを回収し、本文は読み捨てる</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>**本文には実データが含まれうる**ため保持しない。メモリ確保も避ける（OBS-3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>401/403 が返った場合もエラーとせず観測値として返す</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>トークン失効・スコープ不足の可能性があり、判定は 認証実装チェック-06 の責務。**未認証側が正常なら WARN 止まり**（認証は効いているため P1 ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>接続不能・タイムアウトは観測不能として記録し次へ進む</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>1 endpoint の失敗で残りを打ち切らない（18 §18.5.2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>認証実装チェック Lambda -&gt; CloudFront : GET（Authorization: Bearer …, X-Auth-Probe）
 API GW --&gt; 認証実装チェック Lambda : ステータスコード
@@ -19015,182 +19831,268 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>positiveTest 対象外</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>アノテーション</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>スキップして null を返す</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>通知なし</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>README §2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>本番の更新系メソッド</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>env + method</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>スキップ</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>通知なし</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>11 §11.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>401/403（トークン失効・スコープ不足）</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>観測値として返す</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-06 で WARN → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>README §2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>観測値として返す</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-06 で WARN（構成）→ P2</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>README §2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>観測値として返す</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-06 で INFO（Backend バグ）→ P3 App team</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>README §2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>接続不能 / タイムアウト</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>例外捕捉</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>観測不能として次の endpoint へ</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-06 で WARN</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>再実行時の振る舞い</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>**本番では GET のみ**を実行するため副作用がなく冪等。stg では更新系も対象になりうるが、その場合は x-canary-cleanup による後処理を伴う（README §2.3）。</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>状態更新のタイミング</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>8. 権限・エンドポイント</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>権限 / エンドポイント</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Bearer（認証実装チェック-03 のトークン）/ HTTPS 443 / X-Auth-Probe ヘッダ付与</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>認証方式・補足</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>9. ログ・メトリクス</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>名称・項目</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。観測値はメモリ上で 認証実装チェック-06 へ渡すのみ。</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>10. 性能・上限</t>
+          <t>8. 権限・エンドポイント</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>想定件数 / 所要時間</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr"/>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Bearer（認証実装チェック-03 のトークン）/ HTTPS 443 / X-Auth-Probe ヘッダ付与</t>
+        </is>
+      </c>
       <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="n"/>
@@ -19198,10 +20100,16 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>上限・制約</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr"/>
+          <t>認証方式・補足</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer（認証実装チェック-03 の短命トークン）。**トークンはログ・アラート本文・例外メッセージに出さない**（OBS-3）
+トークンのスコープは読み取り専用・最小権限（Phase 1 はスコープ A、目標は B。11 §11.3.1 / M-Q-11-4）
+AWS API の呼び出しは伴わない。通信はインターネット向け HTTPS 443 のみ</t>
+        </is>
+      </c>
       <c r="C62" s="4" t="n"/>
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="n"/>
@@ -19209,37 +20117,53 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>11. 未決事項</t>
+          <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>種別</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
+          <t>名称・項目</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>確認先</t>
-        </is>
-      </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>期限</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>正常系確認</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>appId / env / method / rawPath / posStatus / 所要 ms / 相関 ID</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>**トークンと応答本文は出力しない**</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="n"/>
@@ -19247,38 +20171,132 @@
       <c r="C67" s="10" t="n"/>
       <c r="D67" s="10" t="n"/>
     </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>10. 性能・上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>想定件数 / 所要時間</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>対象 endpoint ごとに 1 リクエスト。既定では対象が限られるため未認証確認より件数は少ない</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" s="4" t="n"/>
+      <c r="E70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>上限・制約</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>タイムアウト値は 認証実装チェック-04 と共通（W3-5 で本決め）</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n"/>
+      <c r="D71" s="4" t="n"/>
+      <c r="E71" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>11. 未決事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>確認先</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-11-4</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Positive のスコープを B（canary 専用テナント / 合成データのみ）へ移行する時期。Phase 1 は A（全 API 横断の読み取り専用）で開始</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>認証基盤チーム</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>調整中</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n"/>
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="10" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A73:E73"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A40:E44"/>
+    <mergeCell ref="A69:E69"/>
     <mergeCell ref="B62:E62"/>
     <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A46:E46"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="B71:E71"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B70:E70"/>
     <mergeCell ref="B11:E11"/>
+    <mergeCell ref="A23:E23"/>
     <mergeCell ref="B61:E61"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B57:E57"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19291,7 +20309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19373,7 +20391,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-04（未認証）と 認証実装チェック-05（正常系）の観測値を突き合わせ、重要度を決める。**観測と判定を分けている**のが設計の要点で、04/05 は観測に徹し、判定ロジックはここに 1 本化する。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -19459,7 +20481,13 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-04 で negStatus / wafBlocked / 観測不能フラグを取得済み
+認証実装チェック-05 で posStatus を取得済み（対象外なら null）
+認証実装チェック-01 で authPattern を取得済み（期待値の分岐に使う）</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -19499,132 +20527,357 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>negStatus</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>number / null</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-04</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>null は公開明示によるスキップ</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>posStatus</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>number / null</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-05</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>null は正常系確認の対象外</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>wafBlocked</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-04</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>WAF 由来の 403 かどうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>authPattern</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>enum（6 値）</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-01</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>期待する拒否ステータスの分岐</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>3. 出力（O）</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>出力先</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>説明・例</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-    </row>
     <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>enum(OK / INFO / WARN / CRITICAL)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-07 / 08</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>4×4 真偽値表（README §2.5）に基づく</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>判定根拠</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-08（通知本文）</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>どの組合せで何と判定したか。受け手が再現できる粒度で残す</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>処理内容</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>補足・参照</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
+    <row r="31">
+      <c r="A31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】4×4 の全組み合わせと重要度の対応表を貼る（code-samples/README §2 が正）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>**WAF 由来の 403（wafBlocked=true）を最優先で切り分ける**</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>【最重要】WAF の 403 を「認証が効いている」と解釈すると、**認証漏れを OK と誤判定する（偽陰性）**。本機構が最も避けるべき誤りであり、WARN（境界でブロック）として別分類する（11 §11.2.4）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="A32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>公開明示によるスキップ（negStatus=null）は OK とする</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>MON-1 で public と宣言された endpoint。posStatus が 200 なら「OK（public + health）」</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>authPattern に応じた期待値で negStatus を評価する</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>api-gw-* 系は 401/403、Cookie 系（alb-cookie-monolith / bff-cookie-session）は **302** が期待値。302 を「異常」と判定するとモノリスで誤検知が多発する（11 §11.3）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>**negStatus が 2xx なら CRITICAL（認証実装漏れ）と判定する**</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>posStatus に関わらず CRITICAL。posStatus も 200 なら「認証 missing」、401/403 なら「認証逆転」（トークンありで弾かれ、なしで通る = 設定が反転している）。いずれも P1 Security 即時（README §2.5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>negStatus が期待どおりでも posStatus が異常なら WARN / INFO に落とす</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>401/403 × 401/403 = WARN（トークン失効）、401/403 × 404 = WARN（構成）、401/403 × 500 = INFO（Backend バグ）。**認証は効いているので P1 ではない**という切り分け</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>negStatus が 404 なら WARN（構成ミス）とする</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>検査先に endpoint が無い。仕様と実態のずれ（アップロード忘れ・未デプロイ）の可能性</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>観測不能（接続不能・タイムアウト）は WARN（構成）とする</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>「認証が効いている」とは言えないため OK にしない。かといって認証漏れでもないため CRITICAL にもしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>判定根拠を文字列で組み立てる</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>「未認証で 200 が返った（期待 401/403）」のように、**受け手が状況を再現できる粒度**で残す。P1 を受け取った担当が最初に見る情報になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>認証実装チェック Lambda : (未認証結果, 正常系結果) -&gt; 4×4 真偽値表 -&gt; 重要度決定
 WAF 起因の 403 は WARN（構成）に分類
@@ -19632,270 +20885,484 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>WAF 由来の 403</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>wafBlocked=true</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>WARN（境界でブロック）→ P2 Platform</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>**OK にも CRITICAL にもしない**</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>11 §11.2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>negStatus=2xx（認証実装漏れ）</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL → P1 Security 即時</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>最優先で通知</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>README §2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Cookie 系で 302 が返った</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>authPattern + ステータス</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>OK（期待どおり）</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>通知なし</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>11 §11.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Cookie 系で 302 だが expected-redirect と不一致</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>リダイレクト先</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>WARN（構成）→ P2 Platform</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>観測不能（接続不能・タイムアウト）</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-04 のフラグ</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>WARN（構成）→ P2 Platform</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>4×4 表に無い組合せ</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>ステータスの組合せ</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>**WARN（未分類）として通知する**。判定不能を OK にしない</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>P2 Platform</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n"/>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>再実行時の振る舞い</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>純粋な判定処理で副作用なし。同じ観測値なら常に同じ severity になる。</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>状態更新のタイミング</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>8. 権限・エンドポイント</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>権限 / エンドポイント</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>—（AWS 呼び出しなし）</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>認証方式・補足</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>AWS API の呼び出しを伴わない内部処理。</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>判定結果</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>appId / env / rawPath / method / negStatus / posStatus / wafBlocked / severity / 判定根拠</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>**この 1 行が障害調査の起点**になるため、判定に使った全入力を残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="n"/>
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="10" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>想定件数 / 所要時間</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>endpoint ごとにメモリ内で判定。実質ゼロコスト</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>上限・制約</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="4" t="n"/>
+      <c r="E73" s="4" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-23</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Cookie 系でリダイレクト先が期待値と異なる場合の扱い（WARN にするか、リダイレクト先は見ないか）。厳密に見ると誤検知が増える可能性がある</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-24</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>4×4 表に無い組合せ（例: negStatus=500）の既定分類。案: WARN（未分類）として通知し、頻出するものは表に追加していく</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="n"/>
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A58:E58"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="B64:E64"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B63:E63"/>
     <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
     <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="A75:E75"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="A66:E66"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A71:E71"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A42:E46"/>
+    <mergeCell ref="B73:E73"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19908,7 +21375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19990,7 +21457,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>1 アプリの全 endpoint を検査し終えた後に 1 回だけ実行する。**発報 2 系統のうち「保険系」の入口**であり、即時系（認証実装チェック-08）とは独立して動く。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -20076,7 +21547,11 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-06 で全 endpoint の判定が完了していること</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -20116,18 +21591,58 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>判定結果の集計</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>{CRITICAL 件数, WARN 件数, INFO 件数, OK 件数, 観測不能件数}</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-06</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>appId / env</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-01</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>ディメンションに使う</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n"/>
@@ -20166,16 +21681,48 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>AuthCheckCritical</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Count=N</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch（共通基盤）</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>**保険系アラーム（&gt; 0 で P1）の入力**。即時系が壊れていても、これで検知できる（18 §18.4）</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>AuthCheckWarn / AuthCheckInfo</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Count=N</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch（共通基盤）</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>傾向把握・ダッシュボード用</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n"/>
@@ -20208,310 +21755,467 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】ディメンション設計（アプリ数比例でメトリクス課金が増える点に注意）を明記する</t>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>endpoint ごとの判定を severity 別に集計する</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>1 アプリ 1 回の送信にまとめ、endpoint 単位では送らない</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>AuthCheckCritical を PutMetricData する。**0 件でも 0 を送る**</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>値を送らないと「検査していない」と「異常なし」が区別できない。アラームは &gt; 0 で発報するため、0 の送信はアラーム動作に影響しない</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>ディメンションは appId / env に限定する</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>【注意】**メトリクスはディメンションの組合せごとに課金される**（RC-7 が最大費目）。endpoint 単位のディメンションを付けると endpoint 数 × アプリ数で急増するため付けない。endpoint 単位の情報は 認証実装チェック-06 のログ（CloudWatch Logs Insights）で追う</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="A32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>**この送信は即時系（認証実装チェック-08）と独立して行う**</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>アラート検知 Lambda が壊れていても保険系アラームが鳴るようにするため。両方そろって初めて検知網が閉じる（18 §18.5.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>PutMetricData の失敗は記録して握り潰す</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>メトリクス送信の失敗で検査結果を覆さない</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>認証実装チェック Lambda -&gt; CloudWatch : PutMetricData(AuthCheckCritical ほか, ディメンション=appId/env)
 【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38"/>
     <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40"/>
+    <row r="41"/>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
     <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL が 1 件以上</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>集計</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>AuthCheckCritical = N を送信</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>保険系アラーム &gt; 0 → P1 Security</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>全 endpoint が観測不能</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>集計</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL は 0 だが WARN が全件になる。**アプリ全面ダウンの可能性**</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>WARN 経由で P2 Platform</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-06</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>PutMetricData 失敗</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>API 例外</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>記録して継続。**即時系（認証実装チェック-08）は独立して動くため通知は届く**</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>発報 2 系統の利点</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="n"/>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>再実行時の振る舞い</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>状態更新のタイミング</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>8. 権限・エンドポイント</t>
-        </is>
-      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>同じ検査で複数回送っても CloudWatch 側は同一タイムスタンプの値として扱う。1 回に留める。</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>権限 / エンドポイント</t>
+          <t>状態更新のタイミング</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>cloudwatch:PutMetricData / monitoring.{region}.amazonaws.com</t>
+          <t>状態を更新しない。</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>8. 権限・エンドポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>cloudwatch:PutMetricData / monitoring.{region}.amazonaws.com</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>認証方式・補足</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>cloudwatch:PutMetricData。共通基盤アカウント内</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-    </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>メトリクス</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>AuthCheckCritical / AuthCheckWarn / AuthCheckInfo</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>severity 別件数</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>ディメンションは appId / env のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="n"/>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>想定件数 / 所要時間</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>1 アプリにつき 1 回。カスタムメトリクスはアプリ数 × env 数 × 種類数で増える</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>上限・制約</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>**PutMetricData は 1 リクエスト 1 MB / 1,000 メトリクス / 30 ディメンションまで**。アプリ数比例でメトリクス課金が増える点は費用見積 RC-7 に織り込み済み</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="69">
+      <c r="A69" s="10" t="n"/>
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="10" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="n"/>
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="B65:E65"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="B64:E64"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B55:E55"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="A54:E54"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="B56:E56"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A37:E41"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A63:E63"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
+    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20988,7 +22692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21070,7 +22774,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>1 アプリの検査の出口。**発報 2 系統のうち「即時系」**で、判定結果をアラート検知 Lambda へ渡す。保険系（認証実装チェック-07 のメトリクス → アラーム）とは独立して動く。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -21156,7 +22864,12 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-06 で判定が完了していること
+アラート検知 Lambda に On-failure Destination（送信先 SQS）が設定済み（WBS A5）</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -21196,11 +22909,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>検知イベント</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>[{appId, env, method, rawPath, negStatus, posStatus, severity, 判定根拠}]</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-06</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>severity ≠ OK のものだけ</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n"/>
@@ -21209,47 +22942,78 @@
       <c r="D18" s="10" t="n"/>
       <c r="E18" s="10" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>3. 出力（O）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>3. 出力（O）</t>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>出力先</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>説明・例</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>出力先</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>説明・例</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>検知イベント送付</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>非同期 Invoke</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>アラート検知 Lambda</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>README §2.7 形式</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>失敗時の呼び出し記録</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>SQS メッセージ（JSON）</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>アラート検知用 On-failure Destination</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>MM-5 の入力</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n"/>
@@ -21257,341 +23021,596 @@
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>4. 処理手順</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>4. 処理手順</t>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>補足・参照</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>処理内容</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>補足・参照</t>
+      <c r="A28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>severity = OK の endpoint は送らない</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>通知すべき事象がないため。OK の記録はメトリクスとログに残る</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】イベント形式（README §2.6）と、配列でのバッチ送付の可否を明記する</t>
+      <c r="A29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>**同一アプリの検知を 1 回の invoke にまとめて送る（配列）**</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>endpoint ごとに invoke すると、1 アプリで大量の認証漏れがあったときに通知が溢れる。アラート検知 Lambda 側は「配列でも処理する」設計になっている（15 章）</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>**非同期（InvocationType=Event）で invoke する**</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>通知の失敗・遅延が検査本体を巻き込まないようにする。非同期のペイロード上限は 1 MB（同期の 6 MB とは別）</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>判定根拠を本文に含める</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>受け手（Security オンコール）が最初に見る情報。「未認証で 200 が返った（期待 401/403）」のように状況が再現できる粒度にする</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="A32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>**通知先の解決はここでは行わない**</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>alertRouting の解決はアラート検知 Lambda の責務（通知-01）。検査側で解決すると解決ロジックが 2 か所になり、全社デフォルトへのフォールバック規則も二重管理になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>invoke の失敗は記録して継続する</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>**保険系（認証実装チェック-07 のメトリクス → アラーム）が独立して動くため、通知経路が壊れても検知は失われない**</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>認証実装チェック Lambda -&gt; アラート検知 Lambda : Invoke(Event, 4×4 判定済みイベント)
 【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38"/>
     <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40"/>
+    <row r="41"/>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
     <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>severity が全て OK</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>判定結果</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>invoke しない（正常系）</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>通知なし</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>invoke がスロットリング（429）</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>API 例外</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>イベントはキューに戻り最大 6 時間・指数バックオフで再試行される</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>長期化すれば MM-5 → P2</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>AWS 公式</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>アラート検知 Lambda が失敗</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Lambda 側</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>既定 2 回リトライ（1 分後・2 分後）→ On-failure Destination へ</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>MM-5（Destination 滞留 ≥ 1）→ P2 Platform</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>ペイロードが 1 MB を超える（検知が大量）</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>サイズ</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>分割して複数回 invoke する。**1 件も落とさない**</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>invoke 自体が失敗</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>API 例外</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>記録して継続。保険系アラームで検知は担保される</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>AuthCheckCritical &gt; 0 → P1</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>再実行時の振る舞い</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>状態更新のタイミング</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>8. 権限・エンドポイント</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>権限 / エンドポイント</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>lambda:InvokeFunction（InvocationType=Event）</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>認証方式・補足</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
+          <t>再実行時の振る舞い</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>**at-least-once**。同じ検知が複数回通知されうる（非同期キューの結果整合性）。重複通知は運用上のノイズになるが、**通知が届かないより安全**という判断（18 §18.5.2）。同一問題が解消するまで巡回・全量のたびに再通知される点は dedup の要否として未決（M-Q-15-3）。</t>
+        </is>
+      </c>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
     </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>9. ログ・メトリクス</t>
-        </is>
-      </c>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>状態更新のタイミング</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。通知の送信記録はログとメトリクスに残る。</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>名称・項目</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>8. 権限・エンドポイント</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>lambda:InvokeFunction（InvocationType=Event）</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>認証方式・補足</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>lambda:InvokeFunction（アラート検知 Lambda に限定）。共通基盤アカウント内
+イベント本文に**トークン・応答本文・機微データを含めない**（OBS-3）。含めるのはステータスとパスと判定根拠のみ</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
+          <t>9. ログ・メトリクス</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>名称・項目</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>通知依頼</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>appId / env / 検知件数 / severity 別内訳 / invoke 結果</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="n"/>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>想定件数 / 所要時間</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>検知があったアプリのみ 1 回（大量時は分割）。正常時はゼロ</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>上限・制約</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>非同期ペイロード上限 1 MB。1 件あたり数百バイトのため数千件までは 1 回に収まる</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-25</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>検知が大量（1 アプリで数千 endpoint が CRITICAL 等）のときの分割単位。そもそもその状態は『アプリ全体で認証が外れている』ことを意味するため、**件数を送って詳細は上位 N 件に絞る**方が通知として有用な可能性がある</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-15-3</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>同一問題が解消するまでの再通知を抑制するか（dedup）</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>受信チーム</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>ヒアリング待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n"/>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="B54:E54"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="A37:E41"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B67:E67"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/doc/excel/apipf-process-design.xlsx
+++ b/doc/excel/apipf-process-design.xlsx
@@ -12084,9 +12084,9 @@
           <t>認証実装チェック-03_正常系確認用トークン取得</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -12396,9 +12396,9 @@
           <t>通知-01_通知先解決</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -12448,9 +12448,9 @@
           <t>通知-02_重要度別通知送信</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -12500,9 +12500,9 @@
           <t>通知-03_メトリクス閾値通知</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -12552,9 +12552,9 @@
           <t>運用-01_監視機構稼働監視通知</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -12604,9 +12604,9 @@
           <t>運用-02_処理失敗退避・再処理</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -12656,9 +12656,9 @@
           <t>運用-03_監視設定手動更新</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -12708,9 +12708,9 @@
           <t>連携-01_認証構成情報配置</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>記入待ち</t>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>○ 記入済</t>
         </is>
       </c>
     </row>
@@ -16397,6 +16397,1103 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E82"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>認証実装チェック-02  API 仕様取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>0. 概要</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>概要</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>確認対象の endpoint 一覧と公開明示（MON-1）を取得する。</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>1. 基本情報</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>系統</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック（1 アプリの確認・共通）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>実行契機</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>共通（対象検索・全量とも）</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>フロー内の位置</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-01 の直後。ここで「何を検査するか」= endpoint のリストが確定する。**本処理の抽出漏れはそのまま検査漏れになる**ため、解釈規則を厳密に定める。</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>起動元</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック Lambda</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>起動先</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>認証構成情報配置バケット（openapi/）</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>呼び出し方式</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>同期</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>実行主体</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック Lambda</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>頻度・タイミング</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>アプリごとに 1 回</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>前提条件・事前状態</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-01 で openApiS3Key を取得済み
+配置バケットへの s3:GetObject 権限</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2. 入力（I）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>取得元</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>説明・例</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>openApiS3Key</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-01</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>openapi/{accountId}/{appId}/openapi.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>endpoint 列挙（代替）</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>台帳（monitoring.yaml 由来）</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>API 仕様が無いモノリス等で使う。17 §17.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>3. 出力（O）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>出力先</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>説明・例</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>endpoint 記述子リスト</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>[{method, path, rawPath, skipAuthCheck, positiveTest, pathParams, authMode, expectedRedirect}]</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-04〜06（メモリ内）</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>1 endpoint = 1 記述子。**認証実装チェック-04 の入力そのもの**</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>4. 処理手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>補足・参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>openApiS3Key で API 仕様を GetObject する</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>中央に複写された「デプロイされた版の写し」（対象検索-10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>paths 配下を走査し、**HTTP メソッドのキーだけ**を endpoint として抽出する</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>【重要】paths 配下には `parameters` / `summary` / `description` / `servers` / `$ref` など**メソッドではないキーが同居しうる**。これらをメソッドと誤認すると存在しない endpoint を検査してしまう。抽出は get / put / post / delete / options / head / patch / trace の**許可リスト方式**にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>**公開明示（x-synthetics-skip-auth-check）を解釈する。未記載は false（＝認証必須）**</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>MON-1 の default-deny（13 §13.3.0）。ここを「未記載＝スキップ」にすると、うっかり公開した endpoint を永久に検知できなくなる。本機構の安全性の根幹</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>path parameter を x-canary-path-params の dummy 値で解決し、path と rawPath の 2 つを作る</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>path = 実際に叩く URL（/api/users/1）、rawPath = テンプレート（/api/users/{id}）。**rawPath はログ・アラートの識別子**に使う。dummy 値が無い場合の扱いは下記の例外参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>x-canary-positive-test を解釈し、正常系確認の対象かを決める</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>既定 false。pre-prod-only は本番では対象外（11 §11.5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>x-canary-auth-mode / x-canary-expected-redirect を解釈する（Cookie モノリス用）</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>302 が期待値になるケースの判定材料（認証実装チェック-06 へ渡す）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>**検査先のホストは台帳の baseUrl に固定する**（仕様側 servers のホストは使わない）</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>servers には開発用 URL や API GW の直 URL が書かれていることがあり、これに従うとCloudFront を経由しない検査になってしまう（実 UX と条件がずれ、Origin Protection も破る）。宛先を台帳の baseUrl に固定することが宛先 allowlist の担保にもなる（10 §10.1.6）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>【注意】**servers の「パス部分」（/v1 等）は完全に無視してはならない**</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI の servers は相対参照が可能で、`/v1` のようなパスプレフィックスだけが書かれていることがある。これを無視すると全 endpoint が 404 になり、**WARN（構成）が全件出るだけで認証漏れを検知できない**。暫定は baseUrl のみを使い、全件 404 になる場合は servers のパス欠落を疑う運用とする（M-Q-PD-28）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>**webhooks は endpoint として抽出しない**（OpenAPI 3.1）</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>3.1 で追加された webhooks は Path Item Object を値に持つが URL パスではない。paths と同じ構造のため取り違えやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Path Item レベルの parameters を Operation にマージする</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 仕様上、Path Item の parameters は配下の全 Operation に適用される（Operation 側で上書きは可能だが削除は不可）。マージしないと path parameter を取りこぼす</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>API 仕様が無い場合は台帳の endpoint 列挙を使う</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>ALB 直モノリス等（17 §17.4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック Lambda -&gt; 配置バケット : GetObject(openApiS3Key)
+配置バケット --&gt; 認証実装チェック Lambda : API 仕様
+【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>6. 例外・異常系</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>ケース</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>検知方法</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>動作</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>API 仕様が存在しない</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>NoSuchKey</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>台帳の endpoint 列挙にフォールバック。それも無ければ検査対象なしとして終了し記録する</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>列挙も無い場合はメタ不足として P2</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>17 §17.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>paths が空 / 0 endpoint</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>解析結果</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>検査対象なしとして終了し記録する</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>メタ不足アラート → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>paths フィールド自体が無い（OpenAPI 3.1）</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>解析結果</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>3.1 では paths は必須でなく、components / webhooks だけの文書がありうる。検査対象なしとして終了し記録する</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>メタ不足アラート → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 仕様</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>path parameter があるのに x-canary-path-params が無い</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>解析結果</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>**その endpoint をスキップせず、既定の dummy 値（例 1）で解決して検査する**。スキップすると認証漏れを見逃すため。404 になっても認証レイヤーの手前で弾かれるかは観測できる</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>メソッド以外のキー（parameters / summary 等）</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>解析</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>endpoint として抽出しない（許可リスト方式）</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.x 仕様</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>$ref による外部参照</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>解析</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>**解決せず、その endpoint をスキップして記録する**。外部ファイルは中央に複写されていないため解決できない</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>メタ不足アラート → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>仕様が巨大（数千 endpoint）</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>件数に上限を設け、超過分は検査せず記録する（Lambda の 15 分制限に当たらないため）</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>メタ不足アラート → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>7. 冪等性・リトライ</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>再実行時の振る舞い</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>読み取りと解析のみ。同じ仕様なら常に同じ endpoint リストが得られる。</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>状態更新のタイミング</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>8. 権限・エンドポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>s3:GetObject</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>認証方式・補足</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>s3:GetObject（配置バケット）。共通基盤アカウント内</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>9. ログ・メトリクス</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>名称・項目</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>endpoint 抽出</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>appId / env / 抽出件数 / 公開明示件数 / スキップ件数と理由</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>**パス一覧の全件出力はしない**（件数と代表値のみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="n"/>
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="10" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>10. 性能・上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>想定件数 / 所要時間</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>1 アプリにつき 1 回の GetObject と解析。数十〜数百 endpoint</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="4" t="n"/>
+      <c r="E73" s="4" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>上限・制約</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>仕様サイズは 対象検索-07 のサイズ上限で制御済み（M-Q-PD-6）。endpoint 件数上限は M-Q-PD-22</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n"/>
+      <c r="D74" s="4" t="n"/>
+      <c r="E74" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>11. 未決事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>確認先</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-20</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>path parameter の dummy 値が未指定のときの既定値。案: 数値パラメータは 1、文字列は canary-test。実在しない ID になるため 404 が返りやすいが、**認証が効いていれば 404 より先に 401/403 が返る**ため検査は成立する</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-21</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>$ref による外部ファイル参照を解決するか。解決するなら参照先も認証構成情報として連携バケットに置いてもらう必要があり、アプリ側の作業が増える。案: 単一ファイルに bundle してからアップロードすることを規約にする（vendor-guide に追記）</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-22</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>1 アプリあたりの endpoint 件数上限（Lambda 15 分制限との兼ね合い）。W3-5 の性能実測で 1 endpoint あたりの所要時間を確定してから決める</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>設計担当（W3-5 と連動）</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-28</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI の servers に書かれたパスプレフィックス（/v1 等）を baseUrl に結合するか。結合しないと全件 404 になり認証漏れを検知できない。結合すると baseUrl が既にプレフィックスを含む場合に二重になる。案: 結合せず、アプリ側に『baseUrl はプレフィックスまで含めて書く』ことを規約化する（vendor-guide に追記）</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="n"/>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A42:E46"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="A67:E67"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C6E0B4"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -16410,7 +17507,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>認証実装チェック-02  API 仕様取得</t>
+          <t>認証実装チェック-03  正常系確認用トークン取得</t>
         </is>
       </c>
     </row>
@@ -16429,7 +17526,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>確認対象の endpoint 一覧と公開明示（MON-1）を取得する。</t>
+          <t>正常系アクセス確認で使う短命トークンを取得する。</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -16481,7 +17578,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック-01 の直後。ここで「何を検査するか」= endpoint のリストが確定する。**本処理の抽出漏れはそのまま検査漏れになる**ため、解釈規則を厳密に定める。</t>
+          <t>認証実装チェック-05（正常系アクセス確認）の直前に、**必要になった時点で初めて**実行する（遅延取得）。正常系確認の対象 endpoint が 1 つも無いアプリではトークンを発行しない。</t>
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -16511,7 +17608,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>認証構成情報配置バケット（openapi/）</t>
+          <t>Secrets Manager → 認証基盤 /token</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -16556,7 +17653,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>アプリごとに 1 回</t>
+          <t>確認ごとに 1 回</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -16571,8 +17668,9 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック-01 で openApiS3Key を取得済み
-配置バケットへの s3:GetObject 権限</t>
+          <t>Secrets Manager に canary 専用クライアントの client_id / client_secret が登録済み（WBS A10-i / W1-4）
+認証基盤（Keycloak）側に service account 有効のクライアントが発行済み（W1-4）
+Lambda ロールに secretsmanager:GetSecretValue（+ CMK 利用時は kms:Decrypt）があること</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
@@ -16616,7 +17714,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>openApiS3Key</t>
+          <t>testTokenSecret</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -16631,39 +17729,39 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック-01</t>
+          <t>認証実装チェック-01（台帳）</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>openapi/{accountId}/{appId}/openapi.yaml</t>
+          <t>Secret 名。省略時は共通の既定 Secret（11 §11.3.1）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>endpoint 列挙（代替）</t>
+          <t>token endpoint URL</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>要</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>台帳（monitoring.yaml 由来）</t>
+          <t>Lambda 環境変数</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>API 仕様が無いモノリス等で使う。17 §17.4</t>
+          <t>Keycloak の /realms/{realm}/protocol/openid-connect/token</t>
         </is>
       </c>
     </row>
@@ -16706,393 +17804,413 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>endpoint 記述子リスト</t>
+          <t>access_token</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>[{method, path, rawPath, skipAuthCheck, positiveTest, pathParams, authMode, expectedRedirect}]</t>
+          <t>string（機微）</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック-04〜06（メモリ内）</t>
+          <t>認証実装チェック-05（メモリ内）</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>1 endpoint = 1 記述子。**認証実装チェック-04 の入力そのもの**</t>
+          <t>**ログ・アラート本文・例外メッセージに出さない**（06 章 OBS-3）</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>有効期限</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>epoch 秒</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>内部キャッシュ</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>expires_in から算出。再取得の判断に使う</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>処理内容</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>補足・参照</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>openApiS3Key で API 仕様を GetObject する</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>中央に複写された「デプロイされた版の写し」（対象検索-10）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>paths 配下を走査し、**HTTP メソッドのキーだけ**を endpoint として抽出する</t>
+          <t>**正常系確認の対象 endpoint が 1 つも無ければ、本処理をスキップする（遅延取得）**</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>【重要】paths 配下には `parameters` / `summary` / `description` / `servers` / `$ref` など**メソッドではないキーが同居しうる**。これらをメソッドと誤認すると存在しない endpoint を検査してしまう。抽出は get / put / post / delete / options / head / patch / trace の**許可リスト方式**にする</t>
+          <t>x-canary-positive-test は既定 false のため、対象が無いアプリは珍しくない。不要なトークン発行を避けることで、資格情報の露出機会と認証基盤への負荷を減らす</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>**公開明示（x-synthetics-skip-auth-check）を解釈する。未記載は false（＝認証必須）**</t>
+          <t>キャッシュ済みトークンがあり、**有効期限まで 30 秒以上ある**ならそれを再利用する</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>MON-1 の default-deny（13 §13.3.0）。ここを「未記載＝スキップ」にすると、うっかり公開した endpoint を永久に検知できなくなる。本機構の安全性の根幹</t>
+          <t>Lambda の実行環境は再利用されるため、ハンドラ外にキャッシュして実行をまたいで使い回す（AWS のベストプラクティス）。30 秒という値は Keycloak 公式アダプタの minValidity の例に倣う（規格〔RFC 6749〕には期限前再取得の規範的記述が無い）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>path parameter を x-canary-path-params の dummy 値で解決し、path と rawPath の 2 つを作る</t>
+          <t>Secrets Manager から client_id / client_secret を取得する</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>path = 実際に叩く URL（/api/users/1）、rawPath = テンプレート（/api/users/{id}）。**rawPath はログ・アラートの識別子**に使う。dummy 値が無い場合の扱いは下記の例外参照</t>
+          <t>**Node.js には公式のクライアントサイドキャッシュライブラリが無い**（Java/Python/.NET/Go/Rust のみ）ため、**AWS Parameters and Secrets Lambda Extension** の利用を推奨する（既定 TTL 300 秒・キャッシュ 1000 件・東京リージョン提供あり）。【注意】Extension は **INVOKE フェーズでのみ呼べる**（INIT フェーズでは使えない）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>x-canary-positive-test を解釈し、正常系確認の対象かを決める</t>
+          <t>token endpoint へ grant_type=client_credentials で POST する</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>既定 false。pre-prod-only は本番では対象外（11 §11.5）</t>
+          <t>クライアント認証は Basic ヘッダ（base64(client_id:client_secret)）または POST パラメータ。Keycloak 側はクライアント認証 ON（confidential）+ サービスアカウント有効が前提</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>x-canary-auth-mode / x-canary-expected-redirect を解釈する（Cookie モノリス用）</t>
+          <t>応答から access_token と expires_in を取り出し、期限を算出してキャッシュする</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>302 が期待値になるケースの判定材料（認証実装チェック-06 へ渡す）</t>
+          <t>**client_credentials では refresh token が返らない**（RFC 6749 が SHOULD NOT、Keycloak も明記）。失効したら再取得するしかないため、期限管理はこちら側の責務。Keycloak の Access Token Lifespan の既定は **5 分**</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>**仕様側の servers は無視し、検査先は台帳の baseUrl を使う**</t>
+          <t>取得に失敗した場合は正常系確認をスキップし、未認証確認は継続する</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>servers には開発用 URL や API GW の直 URL が書かれていることがあり、これに従うとCloudFront を経由しない検査になってしまう（実 UX と条件がずれ、Origin Protection も破る）。宛先を台帳の baseUrl に固定することが宛先 allowlist の担保にもなる（10 §10.1.6）</t>
+          <t>**トークンが取れなくても未認証確認（認証実装チェック-04）は成立する**。本機構の主目的は『認証が効いているか』であり、トークン取得の失敗で検査全体を諦めない</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>API 仕様が無い場合は台帳の endpoint 列挙を使う</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>ALB 直モノリス等（17 §17.4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>認証実装チェック Lambda -&gt; 配置バケット : GetObject(openApiS3Key)
-配置バケット --&gt; 認証実装チェック Lambda : API 仕様
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック Lambda -&gt; Secrets Manager : GetSecretValue
+認証実装チェック Lambda -&gt; 認証基盤 /token : client_credentials
+認証基盤 --&gt; 認証実装チェック Lambda : access_token（短命）
 【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40"/>
     <row r="41"/>
     <row r="42"/>
-    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>6. 例外・異常系</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>6. 例外・異常系</t>
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>ケース</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>検知方法</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>動作</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>参照</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>ケース</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>検知方法</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>動作</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>通知</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>参照</t>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>正常系確認の対象が無い</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>endpoint 記述子</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>スキップ（正常系）</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>通知なし</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>遅延取得</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>API 仕様が存在しない</t>
+          <t>Secrets Manager の取得失敗（権限・存在しない）</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>NoSuchKey</t>
+          <t>API 例外</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>台帳の endpoint 列挙にフォールバック。それも無ければ検査対象なしとして終了し記録する</t>
+          <t>正常系確認をスキップし、未認証確認は継続。posStatus は null</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>列挙も無い場合はメタ不足として P2</t>
+          <t>メタ不足アラート → P2 Platform</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>17 §17.4</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>paths が空 / 0 endpoint</t>
+          <t>Secrets Manager のスロットリング</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>解析結果</t>
+          <t>ThrottlingException（HTTP 400）</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>検査対象なしとして終了し記録する</t>
+          <t>SDK 標準リトライ。Extension のキャッシュにより通常は発生しない</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>メタ不足アラート → P2 Platform</t>
+          <t>継続失敗なら P2</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>上限 10,000 TPS のため実質発生しない</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>path parameter があるのに x-canary-path-params が無い</t>
+          <t>token endpoint が 4xx（クライアント設定不備）</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>解析結果</t>
+          <t>HTTP ステータス</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>**その endpoint をスキップせず、既定の dummy 値（例 1）で解決して検査する**。スキップすると認証漏れを見逃すため。404 になっても認証レイヤーの手前で弾かれるかは観測できる</t>
+          <t>正常系確認をスキップして継続</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>メタ不足アラート → P2 Platform</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>M-Q-PD-20</t>
+          <t>W1-4 の設定不備を疑う</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>メソッド以外のキー（parameters / summary 等）</t>
+          <t>token endpoint が 5xx / 接続不能</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>解析</t>
+          <t>例外</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>endpoint として抽出しない（許可リスト方式）</t>
+          <t>同上。認証基盤側の障害の可能性</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
+          <t>P2 Platform</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>OpenAPI 3.x 仕様</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>$ref による外部参照</t>
+          <t>**検査中にトークンが失効した（API が 401 を返した）**</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>解析</t>
+          <t>認証実装チェック-05 の posStatus</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>**解決せず、その endpoint をスキップして記録する**。外部ファイルは中央に複写されていないため解決できない</t>
+          <t>**トークンを再取得して当該 endpoint を 1 回だけ再試行する**。それでも 401 ならスコープ不足として観測値を返す</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>メタ不足アラート → P2 Platform</t>
+          <t>認証実装チェック-06 で WARN → P2 Platform</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>M-Q-PD-21</t>
+          <t>RFC 6750（invalid_token は 401 が標準）/ M-Q-PD-29</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>仕様が巨大（数千 endpoint）</t>
+          <t>ローテーション直後に古い資格情報を使った</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>件数</t>
+          <t>Extension のキャッシュ</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>件数に上限を設け、超過分は検査せず記録する（Lambda の 15 分制限に当たらないため）</t>
+          <t>**キャッシュ TTL の分だけ古い値を使いうる**（AWS 公式が明記）。認証失敗したら再取得することで自然に回復する。TTL を短くする（例 60 秒）ことでも緩和できる</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>メタ不足アラート → P2 Platform</t>
+          <t>一時的な WARN として現れる</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>M-Q-PD-22</t>
+          <t>M-Q-PD-30</t>
         </is>
       </c>
     </row>
@@ -17118,7 +18236,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>読み取りと解析のみ。同じ仕様なら常に同じ endpoint リストが得られる。</t>
+          <t>同じ資格情報で何度呼んでも新しいトークンが発行されるだけで副作用はない。ただし短時間に大量発行すると認証基盤に無駄な負荷をかけるため、キャッシュして再利用する。</t>
         </is>
       </c>
       <c r="C56" s="4" t="n"/>
@@ -17133,7 +18251,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>状態を更新しない。</t>
+          <t>状態を更新しない。トークンのキャッシュは Lambda 実行環境のメモリ上のみで、永続化しない。</t>
         </is>
       </c>
       <c r="C57" s="4" t="n"/>
@@ -17155,7 +18273,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>s3:GetObject</t>
+          <t>secretsmanager:GetSecretValue / 認証基盤の公開 /token（インターネット経由・OAuth client_credentials）</t>
         </is>
       </c>
       <c r="C60" s="4" t="n"/>
@@ -17170,7 +18288,10 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>s3:GetObject（配置バケット）。共通基盤アカウント内</t>
+          <t>secretsmanager:GetSecretValue（対象 Secret に限定）+ kms:Decrypt（CMK 利用時）
+**client_secret と access_token をログ・アラート本文・例外メッセージに出さない**（OBS-3）。HTTP クライアントのデバッグログがヘッダを出力しないことも確認する
+token endpoint への通信はインターネット経由（10 §10.1.6 経路 B）。宛先は設定済みの 1 本に固定
+資格情報は Secrets Manager の自動ローテーション対象（30/90 日、11 §11.3.1）</t>
         </is>
       </c>
       <c r="C61" s="4" t="n"/>
@@ -17214,17 +18335,17 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>endpoint 抽出</t>
+          <t>トークン取得</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>appId / env / 抽出件数 / 公開明示件数 / スキップ件数と理由</t>
+          <t>appId / env / 取得元（キャッシュ or 新規発行）/ 有効期限までの秒数 / 所要 ms</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>**パス一覧の全件出力はしない**（件数と代表値のみ）</t>
+          <t>**トークンと client_secret は出力しない**。有効期限は秒数のみ（トークン本体は出さない）</t>
         </is>
       </c>
     </row>
@@ -17249,7 +18370,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>1 アプリにつき 1 回の GetObject と解析。数十〜数百 endpoint</t>
+          <t>1 検査につき最大 1 回（キャッシュヒット時はゼロ）。Keycloak の Access Token Lifespan 既定 5 分に対し、検査 1 回は数分のため実行内での再取得は通常発生しない</t>
         </is>
       </c>
       <c r="C69" s="4" t="n"/>
@@ -17264,7 +18385,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>仕様サイズは 対象検索-07 のサイズ上限で制御済み（M-Q-PD-6）。endpoint 件数上限は M-Q-PD-22</t>
+          <t>Secrets Manager は 10,000 TPS（GetSecretValue）で上限には当たらない。Extension のキャッシュ TTL は最大 300 秒（既定 300 秒）。料金は Secret 1 個 $0.40/月 + API $0.05/1 万回（RC-6）</t>
         </is>
       </c>
       <c r="C70" s="4" t="n"/>
@@ -17303,12 +18424,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>M-Q-PD-20</t>
+          <t>M-Q-PD-29</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>path parameter の dummy 値が未指定のときの既定値。案: 数値パラメータは 1、文字列は canary-test。実在しない ID になるため 404 が返りやすいが、**認証が効いていれば 404 より先に 401/403 が返る**ため検査は成立する</t>
+          <t>検査中の 401 に対する再試行を 1 回に限るか（案: 1 回）。無制限に再試行するとトークン発行が増え、スコープ不足の場合は永久にループする</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -17321,12 +18442,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>M-Q-PD-21</t>
+          <t>M-Q-PD-30</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>$ref による外部ファイル参照を解決するか。解決するなら参照先も認証構成情報として連携バケットに置いてもらう必要があり、アプリ側の作業が増える。案: 単一ファイルに bundle してからアップロードすることを規約にする（vendor-guide に追記）</t>
+          <t>Secrets Manager Extension のキャッシュ TTL（既定 300 秒 / 最大 300 秒）。ローテーション直後に古い資格情報を使う窓を短くするなら 60 秒程度に下げる。下げると GetSecretValue の呼び出しが増えるが、費用は $0.05/1 万回で誤差</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -17339,20 +18460,24 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>M-Q-PD-22</t>
+          <t>M-Q-11-4</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>1 アプリあたりの endpoint 件数上限（Lambda 15 分制限との兼ね合い）。W3-5 の性能実測で 1 endpoint あたりの所要時間を確定してから決める</t>
+          <t>Positive のスコープを B（canary 専用テナント / 合成データのみ）へ移行する時期</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>設計担当（W3-5 と連動）</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr"/>
+          <t>認証基盤チーム</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>調整中</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="n"/>
@@ -17363,19 +18488,19 @@
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A38:E42"/>
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A39:E43"/>
     <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A37:E37"/>
     <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A27:E27"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="B56:E56"/>
-    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B70:E70"/>
@@ -17385,631 +18510,13 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B57:E57"/>
-    <mergeCell ref="A38:E38"/>
     <mergeCell ref="A72:E72"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B69:E69"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="B10:E10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00C6E0B4"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E67"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>認証実装チェック-03  正常系確認用トークン取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>0. 概要</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>概要</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>正常系アクセス確認で使う短命トークンを取得する。</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>1. 基本情報</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>系統</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>認証実装チェック（1 アプリの確認・共通）</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>実行契機</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>共通（対象検索・全量とも）</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>フロー内の位置</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>起動元</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>認証実装チェック Lambda</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>起動先</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Secrets Manager → 認証基盤 /token</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>呼び出し方式</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>同期</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>実行主体</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>認証実装チェック Lambda</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>頻度・タイミング</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>確認ごとに 1 回</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>前提条件・事前状態</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>2. 入力（I）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>取得元</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>説明・例</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>3. 出力（O）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>出力先</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>説明・例</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>4. 処理手順</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>処理内容</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>補足・参照</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】トークンのキャッシュ有無・失効時の再取得・ログへのマスク（トークンを出力しない）を明記する</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>認証実装チェック Lambda -&gt; Secrets Manager : GetSecretValue
-認証実装チェック Lambda -&gt; 認証基盤 /token : client_credentials
-認証基盤 --&gt; 認証実装チェック Lambda : access_token（短命）
-【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>6. 例外・異常系</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>ケース</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>検知方法</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>動作</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>通知</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>参照</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>7. 冪等性・リトライ</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>再実行時の振る舞い</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>状態更新のタイミング</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>8. 権限・エンドポイント</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>権限 / エンドポイント</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>secretsmanager:GetSecretValue / 認証基盤の公開 /token（インターネット経由・OAuth client_credentials）</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>認証方式・補足</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>9. ログ・メトリクス</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>名称・項目</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>10. 性能・上限</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>想定件数 / 所要時間</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>上限・制約</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>11. 未決事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>確認先</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>期限</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18022,7 +18529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18639,7 +19146,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>alb-cookie-monolith / bff-cookie-session は 302 そのものが期待値のため、追従すると観測できない（11 §11.3）</t>
+          <t>alb-cookie-monolith / bff-cookie-session は 302 そのものが期待値のため、追従すると観測できない（11 §11.3）。【実装注意】Node.js の `https` モジュールは**既定で追従しない**ため追加設定は不要だが、グローバル `fetch`（undici）は**既定で追従する**ため `redirect: 'manual'` の指定が必須。ここを取り違えると Cookie 系アプリの検査が丸ごと誤判定になる</t>
         </is>
       </c>
     </row>
@@ -18867,137 +19374,164 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>§10 上限・制約</t>
+          <t>§10 上限・制約 / M-Q-PD-31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>5xx が返る</t>
+          <t>アイドル接続の再利用による接続エラー</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>ステータス</t>
+          <t>例外</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>そのまま観測値として返す（本処理では異常扱いしない）</t>
+          <t>**AWS 公式が「Lambda はアイドル接続を破棄するため、再利用しようとすると接続エラーになる」と明記**。1 回だけ再接続してリトライする</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>認証実装チェック-06 の判定に委ねる</t>
+          <t>リトライ成功なら通知なし</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>11 §11.2.2</t>
+          <t>Lambda ベストプラクティス / M-Q-PD-32</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
+          <t>5xx が返る</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>そのまま観測値として返す（本処理では異常扱いしない）</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-06 の判定に委ねる</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>11 §11.2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
           <t>2xx が返る</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>そのまま観測値として返す</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>認証実装チェック-06 で CRITICAL（認証実装漏れ）→ P1 Security 即時</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>11 §11.2.2 / README §2.5</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="10" t="n"/>
-      <c r="B61" s="10" t="n"/>
-      <c r="C61" s="10" t="n"/>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="10" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="10" t="n"/>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>再実行時の振る舞い</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>参照系の読み取り検査であり状態を持たないため、何度実行しても結果は変わらず安全（冪等）。対象検索 → 検査の invoke は at-least-once（18 §18.5.2）で重複起動しうるが、重複しても無害。※ 更新系メソッドを probe する場合の副作用は M-Q-11-6（§11 未決）を参照</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>状態更新のタイミング</t>
+          <t>再実行時の振る舞い</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>本処理は台帳・S3・メトリクスのいずれも更新しない。観測値はメモリ上で認証実装チェック-06 へ渡すのみで、メトリクス送信は認証実装チェック-07、通知は認証実装チェック-08 以降に集約する</t>
+          <t>参照系の読み取り検査であり状態を持たないため、何度実行しても結果は変わらず安全（冪等）。対象検索 → 検査の invoke は at-least-once（18 §18.5.2）で重複起動しうるが、重複しても無害。※ 更新系メソッドを probe する場合の副作用は M-Q-11-6（§11 未決）を参照</t>
         </is>
       </c>
       <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
       <c r="E65" s="4" t="n"/>
     </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>状態更新のタイミング</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>本処理は台帳・S3・メトリクスのいずれも更新しない。観測値はメモリ上で認証実装チェック-06 へ渡すのみで、メトリクス送信は認証実装チェック-07、通知は認証実装チェック-08 以降に集約する</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>8. 権限・エンドポイント</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>権限 / エンドポイント</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>認証不要（Public 経路）/ HTTPS 443 / X-Auth-Probe ヘッダ付与（WAF 誤検知回避）</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>認証不要（Public 経路）/ HTTPS 443 / X-Auth-Probe ヘッダ付与（WAF 誤検知回避）</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
           <t>認証方式・補足</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>認証情報は付与しない（付与しないことが検査の本体）。Authorization / Cookie とも送らない
 X-Auth-Probe の識別値は Secrets Manager 管理。ログ・アラート本文・例外メッセージに出さない（OBS-3 機微情報のマスク）
@@ -19005,58 +19539,36 @@
 AWS API の呼び出しは伴わない（Secrets の取得は認証実装チェック-03 / 起動時に済ませる）。本処理の通信はインターネット向け HTTPS 443 のみ</t>
         </is>
       </c>
-      <c r="C69" s="4" t="n"/>
-      <c r="D69" s="4" t="n"/>
-      <c r="E69" s="4" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" s="4" t="n"/>
+      <c r="E70" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="7" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>ログ</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>probe 実行ログ</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>appId / env / authPattern / method / rawPath / negStatus / wafBlocked / 所要 ms / 相関 ID（実行 ID）</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>1 endpoint 1 行。識別ヘッダ値・トークンはマスク（06 章 OBS-2 相関 ID / OBS-3 マスク）</t>
         </is>
       </c>
     </row>
@@ -19068,218 +19580,276 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>スキップログ</t>
+          <t>probe 実行ログ</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>公開印により probe しなかった endpoint（appId / rawPath）</t>
+          <t>appId / env / authPattern / method / rawPath / negStatus / wafBlocked / 所要 ms / 相関 ID（実行 ID）</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>公開印の濫用レビュー（月次棚卸し）の入力になる</t>
+          <t>1 endpoint 1 行。識別ヘッダ値・トークンはマスク（06 章 OBS-2 相関 ID / OBS-3 マスク）</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
+          <t>ログ</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>スキップログ</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>公開印により probe しなかった endpoint（appId / rawPath）</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>公開印の濫用レビュー（月次棚卸し）の入力になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
           <t>メトリクス</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>（本処理では送信しない）</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>EndpointsProbed ほかの集計送信は認証実装チェック-07 に集約</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>endpoint ごとに PutMetricData すると呼び出し回数と費用が endpoint 数に比例するため</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="10" t="n"/>
-      <c r="B76" s="10" t="n"/>
-      <c r="C76" s="10" t="n"/>
-      <c r="D76" s="10" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="10" t="n"/>
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="10" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>想定件数 / 所要時間</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>1 アプリ 30 endpoint 想定（費用見積 P-3）で Negative 30 回。1 回あたり 0.1〜1 秒、1 アプリ分で 30 秒以内が目安。閾値の本決めは W3-5（性能実測）</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="n"/>
-      <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>上限・制約</t>
+          <t>想定件数 / 所要時間</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Lambda 15 分（1 実行 = 1 アプリ、18 §18.5.3）/ タイムアウト 接続 3 秒・応答 10 秒（暫定、W3-5 で確定）/ endpoint は直列実行を前提（並列化は WAF レートルール誤爆と表裏。並列化する場合は M-Q-11-5 の許可ルールと併せて判断）</t>
+          <t>1 アプリ 30 endpoint 想定（費用見積 P-3）で Negative 30 回。1 回あたり 0.1〜1 秒、1 アプリ分で 30 秒以内が目安。閾値の本決めは W3-5（性能実測）</t>
         </is>
       </c>
       <c r="C80" s="4" t="n"/>
       <c r="D80" s="4" t="n"/>
       <c r="E80" s="4" t="n"/>
     </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>上限・制約</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Lambda 15 分（1 実行 = 1 アプリ、18 §18.5.3）/ タイムアウト 接続 3 秒・応答 10 秒（暫定、W3-5 で確定）/ endpoint は直列実行を前提（並列化は WAF レートルール誤爆と表裏。並列化する場合は M-Q-11-5 の許可ルールと併せて判断）</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n"/>
+      <c r="E81" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="7" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>期限</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>M-Q-11-5</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>probe 識別ヘッダ（X-Auth-Probe）の WAF 許可ルール。未設定だと WAF ブロックによる WARN が多発し、偽陰性のリスクも残る</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>境界管理チーム（ネットワーク監査アカウント）</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>調整中</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>M-Q-11-6</t>
+          <t>M-Q-11-5</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>【新規】更新系メソッド（POST / PUT / PATCH / DELETE）に対する未認証確認の可否。現行 11 §11.5 は Positive のみ本番 POST をスキップと定めており、Negative は全メソッドが対象。認証が正しく効いていれば 401/403 で副作用はないが、まさに検知したい『認証漏れ』のときだけ本番データを更新してしまう。案: ① 本番の Negative も GET 限定（更新系の認証漏れを検知できない穴が残る）② 更新系は空ボディ・不正 Content-Type で送り、401/403 以外はすべて認証漏れ疑いとする（副作用を最小化しつつ検知は維持。推奨）③ 更新系は stg のみで検査（本番との構成差の分だけ保証が落ちる）</t>
+          <t>probe 識別ヘッダ（X-Auth-Probe）の WAF 許可ルール。未設定だと WAF ブロックによる WARN が多発し、偽陰性のリスクも残る</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>共通基盤チーム + アプリ（顧客合意）</t>
+          <t>境界管理チーム（ネットワーク監査アカウント）</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>調整中</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
+          <t>M-Q-11-6</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>【新規】更新系メソッド（POST / PUT / PATCH / DELETE）に対する未認証確認の可否。現行 11 §11.5 は Positive のみ本番 POST をスキップと定めており、Negative は全メソッドが対象。認証が正しく効いていれば 401/403 で副作用はないが、まさに検知したい『認証漏れ』のときだけ本番データを更新してしまう。案: ① 本番の Negative も GET 限定（更新系の認証漏れを検知できない穴が残る）② 更新系は空ボディ・不正 Content-Type で送り、401/403 以外はすべて認証漏れ疑いとする（副作用を最小化しつつ検知は維持。推奨）③ 更新系は stg のみで検査（本番との構成差の分だけ保証が落ちる）</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>共通基盤チーム + アプリ（顧客合意）</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>タイムアウト値（接続 3 秒 / 応答 10 秒）と直列 / 並列の本決め</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>W3-5 性能実測で確定</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="10" t="n"/>
-      <c r="B87" s="10" t="n"/>
-      <c r="C87" s="10" t="n"/>
-      <c r="D87" s="10" t="n"/>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-31</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>タイムアウトの実装方式。【注意】Node.js の `http`/`https` の `timeout` は**ソケットのアイドルタイムアウトであり、応答全体の上限ではない**。さらに `timeout` イベントは**自動で abort せず `req.destroy()` が必要**。応答全体のデッドラインを設けるには `AbortSignal.timeout()` を使う。undici（グローバル fetch）なら connectTimeout 10 秒 / headersTimeout 300 秒 / bodyTimeout 300 秒が既定</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>設計担当（W3-5 と連動）</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-32</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>HTTP クライアントの Keep-Alive 方針。Node.js 19 以降は `globalAgent` が**既定で keepAlive 有効・timeout 5 秒**（Node 18 では無効）でランタイムにより挙動が変わる。AWS 公式は「Lambda がアイドル接続を破棄するため再利用時に接続エラーになりうる」と警告しており、**接続エラー時の 1 回リトライを実装に含める**必要がある</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="n"/>
+      <c r="B90" s="10" t="n"/>
+      <c r="C90" s="10" t="n"/>
+      <c r="D90" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A83:E83"/>
     <mergeCell ref="B65:E65"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B64:E64"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B80:E80"/>
-    <mergeCell ref="B79:E79"/>
-    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A79:E79"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B66:E66"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="B70:E70"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A72:E72"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B69:E69"/>
     <mergeCell ref="A47:E51"/>
-    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A68:E68"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23623,7 +24193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -23705,7 +24275,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>アラート検知 Lambda の入口。検査側（認証実装チェック-08）から受け取ったイベントに**通知先 ARN は含まれていない**ため、ここで解決する。解決を 1 か所に閉じることで、フォールバック規則の二重管理を防いでいる（15 §15.2）。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -23791,7 +24365,13 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-08 から検知イベントを受領していること（README §2.7 形式）
+環境変数 DEFAULT_P1/P2/P3_TOPIC_ARN が設定済みであること（全社デフォルト）
+配置バケットへの s3:GetObject 権限があること</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -23831,66 +24411,143 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>検知イベント</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>object / array</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-08</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>appId / env / severity / 判定根拠。**ARN は含まれない**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>台帳の alertRouting</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>{p1,p2,p3}</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>配置バケット registry/{appId}/{env}.json</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>**中央管理項目**。アプリ側からは設定できない（12 章）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>DEFAULT_P1/P2/P3_TOPIC_ARN</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Lambda 環境変数</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>全社デフォルトの通知先</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>3. 出力（O）</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>出力先</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>説明・例</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-    </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>解決済み通知先 ARN</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>通知-02（メモリ内）</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>severity に対応する 1 本</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n"/>
@@ -23923,40 +24580,94 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】2 段解決（アプリ個別 → 全社デフォルト）の順序と、未解決時に throw する仕様を明記する</t>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>severity から routingKey（p1 / p2 / p3）を決める</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL→p1 / WARN→p2 / INFO→p3。OK は 認証実装チェック-08 で除外済み</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>**① 台帳の alertRouting[routingKey] を引く**</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>registry/{appId}/{env}.json を GetObject。アプリ個別の通知先が設定されていればそれを使う</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>**② 無ければ環境変数の全社デフォルトに fallback する**</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>台帳の alertRouting は未設定でも正常。新規アプリは自動的に全社デフォルトへ流れる（15 §15.2）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="A32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>**③ どちらも解決できなければ throw する**</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>【重要】握り潰して正常終了すると**通知が消える**。throw すれば Lambda のリトライとOn-failure Destination に乗り、MM-5 で気づける。設定不備を可視化するための意図的な設計（D-M-15-4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>台帳が取得できない場合も全社デフォルトに fallback する</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>台帳の一時的な読み取り失敗で P1 通知を落とさない。**通知が届かないより、宛先が粗くても届く方が安全**</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>アラート検知 Lambda -&gt; 配置バケット : GetObject（alertRouting 参照）
 未設定 -&gt; 全社デフォルト ARN
@@ -23964,270 +24675,462 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38"/>
     <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40"/>
+    <row r="41"/>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
     <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>alertRouting 未設定</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>台帳値</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>全社デフォルトへ fallback（正常系）</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>15 §15.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>台帳が存在しない / 取得失敗</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>API 例外</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>**全社デフォルトへ fallback して通知を続行する**</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>通知の欠落を防ぐことを優先</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>全社デフォルトも未設定</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>環境変数なし</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>**throw する**（握り潰さない）</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>リトライ → On-failure Destination → MM-5 → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>D-M-15-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>ARN の形式が不正</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>検証</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>同上（throw）</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>設定不備の可視化</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>severity が未知の値</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>イベント</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>P2（Platform）へ寄せて通知する。**捨てない**</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>P2 Platform</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>再実行時の振る舞い</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>状態更新のタイミング</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>8. 権限・エンドポイント</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>権限 / エンドポイント</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>s3:GetObject</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>認証方式・補足</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
+          <t>再実行時の振る舞い</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>読み取りと解決のみで副作用なし。同じイベントなら常に同じ ARN に解決される。</t>
+        </is>
+      </c>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
     </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>9. ログ・メトリクス</t>
-        </is>
-      </c>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>状態更新のタイミング</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>名称・項目</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>8. 権限・エンドポイント</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>s3:GetObject</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>認証方式・補足</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>s3:GetObject（配置バケットの registry/*）。共通基盤アカウント内
+**解決した ARN をログに出さない**（通知先の構成情報のため。出すならハッシュ化する）</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
+          <t>9. ログ・メトリクス</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>名称・項目</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>通知先解決</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>appId / env / severity / 解決元（台帳 or デフォルト）/ 相関 ID</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>**ARN そのものは出力しない**</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="n"/>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>想定件数 / 所要時間</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>検知イベントごとに 1 回の GetObject。正常時はゼロ</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>上限・制約</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>S3 GET は 5,500 req/s。通知は正常時ほぼ発生しない</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-26</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>未知の severity が来た場合の既定の寄せ先（案: P2 Platform）。検査側と通知側で enum がずれた場合に通知を落とさないための保険</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>A-6</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>alertRouting の運用方式（誰がいつ台帳に設定するか。アプリ追加時の手順）</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>運用 / 設計担当</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n"/>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="B54:E54"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="B66:E66"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="A37:E41"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B67:E67"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24240,7 +25143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -24322,7 +25225,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>アラート検知 Lambda の出口。**人が最初に目にする成果物**であり、ここでの文面の質がインシデント対応の初動速度を決める。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -24408,7 +25315,12 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>通知-01 で通知先 ARN を解決済み
+SNS トピック（P1/P2/P3）が作成済み・宛先 DL が確定済み（WBS A4 / W1-5）</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -24448,18 +25360,58 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>解決済み ARN</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>通知-01</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>検知イベント</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>object / array</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-08</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>appId / env / method / rawPath / negStatus / posStatus / severity / 判定根拠</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n"/>
@@ -24498,10 +25450,26 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>通知メッセージ</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>SNS Publish</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>SNS（P1 Security / P2 Platform / P3 App）</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>件名 + 本文</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n"/>
@@ -24509,341 +25477,615 @@
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>4. 処理手順</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>4. 処理手順</t>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>補足・参照</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>処理内容</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>補足・参照</t>
+      <c r="A28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>severity ごとの SLA 文言を付けた件名を組み立てる</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>P1 は即時 / P2 は 24h / P3 は通常（15 §15.1）。**件名だけで緊急度が分かる**ようにする</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】通知本文のテンプレートと、1 件でも失敗したら throw（DLQ 発火）する仕様を明記する</t>
+      <c r="A29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>本文に appId / env / method / rawPath / 観測ステータス / 判定根拠を含める</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>**rawPath（テンプレートのパス）を使う**。dummy 値で解決した実パス（/api/users/1）では「どの endpoint の話か」が伝わりにくい（認証実装チェック-02）</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>対応の起点となる情報を添える</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Runbook へのリンク（W4-1 ①）と、確認すべき対象（該当アプリの認証設定）。受け手はベンダーや別チームの可能性があり、設計書を読んでいない前提で書く</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>**トークン・応答本文・機微データを含めない**</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>通知はメールで広く配られるため（06 章 OBS-3）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="A32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>配列で受け取った場合は 1 通にまとめる</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>endpoint ごとに 1 通にすると、1 アプリで大量の認証漏れがあったときに受信箱が埋まる（認証実装チェック-08）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>SNS へ Publish する</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>宛先は 通知-01 が解決した ARN</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>**1 件でも Publish に失敗したら throw する**</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>【重要】部分的に成功しても throw する。握り潰すと**一部の通知だけが消える**という最も気づきにくい障害になる。throw すればリトライと On-failure Destination に乗り MM-5 で気づける（D-M-15-4）。リトライによる重複通知は許容する（通知が届かないより安全）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>アラート検知 Lambda -&gt; SNS(P1|P2|P3) : Publish（件名・本文・appId・endpoint・判定根拠）
 【シーケンス図の所在】15 §15.1 振り分けフロー / 10 §10.1.7 F3</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>SNS Publish 失敗（一部）</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>API 例外</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>**throw する**（部分成功でも）</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>リトライ → On-failure Destination → MM-5 → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>D-M-15-4</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>SNS スロットリング</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>API 例外</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>同上（リトライで吸収される）</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>メッセージサイズ超過</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>SNS の上限</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>件数を要約し詳細は上位 N 件に絞る</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>リトライにより重複通知</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>**許容する**。at-least-once（通知が届かないより安全）</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>同一問題が解消するまで毎回通知される</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>現状は抑制しない。dedup の要否は受信チームへのヒアリング待ち</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-15-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>再実行時の振る舞い</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>**at-least-once**。リトライにより同じ通知が複数回届きうるが、通知が届かないリスクの方が重大という判断（15 §15.4）。</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>状態更新のタイミング</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。通知の送信記録はログに残る。</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>8. 権限・エンドポイント</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>権限 / エンドポイント</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>sns:Publish / sns.{region}.amazonaws.com</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>認証方式・補足</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>sns:Publish（P1/P2/P3 トピックに限定）。共通基盤アカウント内
+**本文に機微データを含めない**（OBS-3）。メールで広く配られる前提で書く</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>通知送信</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>appId / env / severity / 件数 / Publish 結果 / 相関 ID</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>**ARN と本文は出力しない**</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>想定件数 / 所要時間</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>検知があったときのみ。正常時はゼロ</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>上限・制約</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>SNS の無料枠 1,000 通/月（RC-11）。正常時は枠内に収まる</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-15-1</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>P1/P2/P3 の宛先 DL（受信チームのヒアリングで確定）</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>各受信チーム</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>調整中</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-15-3</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>同一問題が解消するまでの再通知を抑制するか（dedup）</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>受信チーム</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>ヒアリング待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="n"/>
+      <c r="B74" s="10" t="n"/>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A38:E42"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="B68:E68"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B55:E55"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="B54:E54"/>
     <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A37:E37"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="A66:E66"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B58:E58"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B53:E53"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24856,7 +26098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -24938,7 +26180,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>**発報 2 系統のうち「保険系」**。認証実装チェック-07 が送ったメトリクスの閾値超過で発報する。アラート検知 Lambda（即時系）を経由しないため、**即時系が壊れていても検知が届く**。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -25024,7 +26270,12 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-07 が AuthCheckCritical を送信していること
+CloudWatch アラームが作成済み（WBS B2-i）</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -25064,18 +26315,58 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>AuthCheckCritical</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>メトリクス</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-07</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>severity=CRITICAL の件数</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>閾値</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>アラーム定義</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>&gt; 0（1 データポイントで発報）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n"/>
@@ -25114,10 +26405,26 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>アラーム通知</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>SNS メッセージ</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>SNS（P1 Security）</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch の定型フォーマット</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n"/>
@@ -25125,56 +26432,89 @@
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>4. 処理手順</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>4. 処理手順</t>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>補足・参照</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>処理内容</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>補足・参照</t>
+      <c r="A28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>AuthCheckCritical &gt; 0 を 1 データポイントで判定する</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>認証漏れは 1 件でも重大なため、複数データポイントの確認は待たない</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】即時系（アラート検知 Lambda）と保険系の重複通知の扱いを明記する</t>
+      <c r="A29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>アラームアクションから SNS へ通知する</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch → SNS の直結。Lambda を経由しない</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>**即時系（通知-02）と重複して届くことを許容する**</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>【設計意図】同じ事象で 2 通届くのは冗長だが、**片方が壊れても気づける**ことの方が重要。本機構は『認証漏れに気づけない』ことが最大のリスクであり、通知の重複はその対価として受け入れる（18 §18.5.1）</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>通知先は P1（Security）に固定する</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>保険系はアプリ個別の alertRouting を解決できない（CloudWatch から台帳を読めないため）。**宛先が粗くなる代わりに、経路が単純で壊れにくい**</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n"/>
@@ -25235,228 +26575,370 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>即時系と重複して届く</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>**許容する**（設計意図）</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>メトリクスが送られてこない（認証実装チェック-07 の失敗）</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>欠損</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>保険系は発報しない。**即時系（通知-02）が独立して動くため通知は届く**</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>発報 2 系統の利点</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>両系統とも壊れている</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>MM-4 / MM-5（Destination 滞留）と MM-1 / MM-6（ハートビート欠損）が検知する</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>MM 各種 → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>アラームが INSUFFICIENT_DATA になる</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>データなし</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>**TreatMissingData は notBreaching とする**。AuthCheckCritical は異常時のみ非ゼロになる性質ではなく常時 0 が送られるため、欠損＝検査が動いていないことを意味するが、それは MM-1 / MM-6 の役割</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-27</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="10" t="n"/>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>再実行時の振る舞い</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch アラームの標準動作。状態遷移時にのみ通知する（ALARM 状態が続く間は再通知しない）。</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>状態更新のタイミング</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>8. 権限・エンドポイント</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>権限 / エンドポイント</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>CloudWatch Alarm → SNS（アラームアクション）</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>認証方式・補足</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch アラームアクション → SNS。Lambda や IAM ロールを経由しない単純な経路</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch アラーム履歴</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>状態遷移の記録</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>アラーム自体が履歴を持つ</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="10" t="n"/>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>想定件数 / 所要時間</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>閾値超過時のみ。正常時はゼロ</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>上限・制約</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch アラームは 1 本 $0.10/月（RC-8）</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-27</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>AuthCheckCritical アラームの TreatMissingData（案: notBreaching）。検査が動いていないことの検知は MM-1 / MM-6 の役割であり、本アラームで二重に見る必要はない</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="n"/>
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="B64:E64"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B55:E55"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B50:E50"/>
     <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B54:E54"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A66:E66"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="A62:E62"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="A35:E39"/>
@@ -25472,7 +26954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -25554,7 +27036,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>被監視系（AuthCheck 系）とは**別系統**で、監視機構そのものの停止・失敗を検知する。「検知した結果」を知らせる通知-02 / 通知-03 に対し、本処理は**「検知できていない状態」**を知らせる（18 §18.5.1）。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -25640,7 +27126,12 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>各 Lambda がメトリクスを emit していること（対象検索-14 / 全量-05 / 認証実装チェック-07）
+CloudWatch アラーム 6 本が作成済み（WBS B3-i〜B8-i / B10-i）</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -25680,402 +27171,747 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>DiscoveryLastSuccess</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>メトリクス</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>対象検索-14</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>MM-1。**6 時間欠損**で発報（2026-09-14 緩和）</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>FullScanLastSuccess</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>メトリクス</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>全量-05</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>MM-6。**48 時間欠損**で発報（2026-09-15 確定）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Lambda Errors（標準）</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>メトリクス</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>AWS/Lambda</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>MM-2（対象検索）/ MM-4（検査）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>DiscoveryAccountErrors</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>メトリクス</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>対象検索-14</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>MM-3。1 件以上で発報</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Destination 滞留</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>SQS メトリクス</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>On-failure Destination</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>MM-4 / MM-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>3. 出力（O）</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>出力先</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>説明・例</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>メタ監視アラート</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>SNS メッセージ</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>SNS（P2 Platform）</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>監視系の障害はアプリの障害ではないため P2 に固定</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>処理内容</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>補足・参照</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
+    <row r="31">
+      <c r="A31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】MM-1〜5 の各アラーム定義（対象メトリクス・閾値・評価期間）を一覧化する</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>ハートビートの欠損を検知する（MM-1 / MM-6）</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>`TreatMissingData=breaching` を設定する。【注意】AWS 公式は「メトリクスは best-effort 配信で欠落しうる」「メトリクス停止後もアラームが直近データ点を再評価し続ける」と警告しており、短い閾値は誤発報を招く。**検知の遅れを許容して閾値を長めに取る**</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="A32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Lambda の標準 Errors を検知する（MM-2 / MM-4）</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>コード例外・タイムアウトの両方が Errors に計上される</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>部分失敗を検知する（MM-3）</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>1 アカウントでも巡回に失敗したら発報。**消滅検知の誤判定を防ぐ安全弁**でもある（対象検索-13）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>On-failure Destination の滞留を検知する（MM-4 / MM-5）</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>リトライを使い切った呼び出しが溜まっている状態。運用-02 の再処理対象</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>通知先は P2（Platform）に固定する</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>監視系の障害はアプリチームに投げても対処できない（18 §18.5.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Alarm(DiscoveryLastSuccess 2h 欠損 / Lambda Errors / DLQ 滞留) -&gt; SNS(P2)
 【シーケンス図の所在】18 §18.5 運用設計 / 10 §10.1.7 F3</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-    </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>メトリクス配信の遅延・欠落による誤発報</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch 側</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>閾値を長めに取ることで緩和済み（MM-1 は 6 時間、MM-6 は 48 時間）</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>誤発報時は Runbook ③ で切り分け</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-2 / WBS W4-1 ③</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>巡回と全量の両方が止まった</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>MM-1 + MM-6</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>2 本とも発報する。**監視機構が全面停止している状態**で最も重大</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>P2 Platform（内容は重大）</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-33</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>アラーム自体が削除・無効化された</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>**本設計では検知できない**。IaC 管理と手動変更検知（Config Rules）で担保する</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-34</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA へ遷移</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>データなし</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>MM-1 / MM-6 は breaching 設定のため ALARM になる。Errors 系は notBreaching が適切</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>WBS B0-d で個別に定義</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>再実行時の振る舞い</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch アラームの標準動作。状態遷移時のみ通知し、ALARM が続く間は再通知しない。</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>状態更新のタイミング</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>8. 権限・エンドポイント</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>権限 / エンドポイント</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>CloudWatch Alarm → SNS</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>認証方式・補足</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch アラームアクション → SNS。Lambda を経由しない単純な経路で、監視系が壊れても動く</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch アラーム履歴</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>状態遷移の記録</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>アラーム自体が履歴を持つ</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>想定件数 / 所要時間</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>閾値超過時のみ</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>上限・制約</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>アラーム 1 本 $0.10/月 × 9 本（RC-8）</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-33</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>MM-1 と MM-6 が同時発報した場合に、個別通知ではなく『監視機構の全面停止』としてまとめて通知するか。個別に 2 通届いても対応は同じため、優先度は低い</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-34</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>アラーム自体の削除・無効化をどう検知するか。IaC（CloudFormation ドリフト検出）または Config Rules で担保する案</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="n"/>
+      <c r="B74" s="10" t="n"/>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="B68:E68"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="B55:E55"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A39:E43"/>
+    <mergeCell ref="B54:E54"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B58:E58"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="A38:E38"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26088,7 +27924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -26170,7 +28006,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>非同期呼び出しがリトライ後も失敗したときの退避と、その後の人手による再処理。**失敗を握り潰さないための最後の受け皿**（18 §18.5.2）。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -26256,7 +28096,13 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>各 Lambda に On-failure Destination（送信先 SQS）が設定済み（WBS A5。2026-09-14 に DLQ から変更）
+滞留アラーム（MM-4 / MM-5）が設定済み
+再処理手順が Runbook 化されていること（WBS W4-1）</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -26296,11 +28142,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>失敗した呼び出しの記録</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>SQS メッセージ（JSON）</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Lambda の On-failure Destination</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>**requestContext（試行回数・エラー種別）/ requestPayload / responsePayload を含む**。DLQ ではイベント本文とエラーメッセージ先頭 1KB しか残らないため Destination を選択した（2026-09-14 確定）</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n"/>
@@ -26309,47 +28175,78 @@
       <c r="D18" s="10" t="n"/>
       <c r="E18" s="10" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>3. 出力（O）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>3. 出力（O）</t>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>出力先</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>説明・例</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>出力先</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>説明・例</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>滞留アラート</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>SNS メッセージ</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>SNS（P2 Platform）</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>MM-4 / MM-5</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>再処理結果</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>運用者</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>原因を除去したうえで再実行</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n"/>
@@ -26357,71 +28254,134 @@
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>4. 処理手順</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>4. 処理手順</t>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>補足・参照</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>処理内容</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>補足・参照</t>
+      <c r="A28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>【自動】リトライを使い切った呼び出しが Destination へ送られる</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>**関数エラー（コード例外・タイムアウト）は既定 2 回リトライ（1 分後・2 分後）**。スロットル（429）やシステムエラー（5xx）は扱いが異なり、最大 6 時間・指数バックオフでキューに保持される</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】DLQ の保持期間・再処理手順（Runbook 化）・滞留アラーム（MM-4/5）を明記する</t>
+      <c r="A29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>【自動】滞留を検知して通知する（MM-4 / MM-5）</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>運用-01 の一部として動く</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>【人手】メッセージの requestContext と responsePayload から原因を特定する</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>**Destination なら応答内容まで残る**ため、DLQ より原因特定が速い</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>【人手】原因を除去する</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>権限不足・設定不備・アプリ側の一時障害など</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="A32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>【人手】再処理する</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>検査は読み取り専用で冪等のため、**同じ payload をそのまま再 invoke してよい**（18 §18.5.2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>【人手】処理済みメッセージを削除する</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>滞留アラームを解消するため</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Lambda(失敗) -&gt; 自動リトライ(2 回) -&gt; SQS DLQ
 運用者 -&gt; DLQ : 内容確認 -&gt; 再実行
@@ -26429,110 +28389,175 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38"/>
     <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40"/>
+    <row r="41"/>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
     <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>保持期間を超えて滞留</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>SQS の保持期間</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>メッセージが失われる。**保持期間は再処理の猶予を見て設定する**（既定 4 日 / 最大 14 日）</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>同じ原因で大量に滞留</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>個別再処理ではなく原因の恒久対処を優先する</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>MM-4 / MM-5 → P2</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Runbook</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>7. 冪等性・リトライ</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>再処理しても再び失敗</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>原因が除去できていない。**無限に再処理しない**（回数上限を Runbook に定める）</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>WBS W4-1</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>再実行時の振る舞い</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Destination への送信自体が失敗</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>DestinationDeliveryFailures メトリクス</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>**失敗の記録すら残らない**最悪ケース。当該メトリクスの監視が必要</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>P2 Platform</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-36</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>状態更新のタイミング</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
+      <c r="A49" s="10" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>8. 権限・エンドポイント</t>
+          <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>権限 / エンドポイント</t>
+          <t>再実行時の振る舞い</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Lambda 非同期呼び出しの DLQ 設定 / sqs:ReceiveMessage・DeleteMessage（運用者）</t>
+          <t>検査・通知とも読み取り専用または冪等な処理のため、**同じメッセージを何度再処理しても安全**。通知の再処理は重複通知になるが、届かないより安全という判断（18 §18.5.2）。</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
@@ -26542,10 +28567,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>認証方式・補足</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
+          <t>状態更新のタイミング</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>再処理そのものは状態を持たない。処理済みメッセージの削除で滞留が解消する。</t>
+        </is>
+      </c>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
@@ -26553,146 +28582,237 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
+          <t>8. 権限・エンドポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Lambda 非同期呼び出しの DLQ 設定 / sqs:ReceiveMessage・DeleteMessage（運用者）</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>認証方式・補足</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>運用者に sqs:ReceiveMessage / DeleteMessage / lambda:InvokeFunction。**メッセージ本文に検査対象の情報が含まれる**ため、閲覧権限は運用担当に限定する</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>10. 性能・上限</t>
-        </is>
-      </c>
-    </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>想定件数 / 所要時間</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>監査ログ</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>CloudTrail</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>再処理の実行記録</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>誰がいつ再処理したか</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>上限・制約</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
+      <c r="A62" s="10" t="n"/>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
+          <t>10. 性能・上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>想定件数 / 所要時間</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>失敗時のみ。正常時はゼロ</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>上限・制約</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>SQS の無料枠内（月 100 万リクエスト）</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-35</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Destination 用 SQS の保持期間（既定 4 日 / 最大 14 日）。休日を挟んでも再処理できるよう長めが望ましい（案: 14 日）</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>運用 / 設計担当</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-36</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>DestinationDeliveryFailures の監視を追加するか。失敗の記録すら残らない状態を検知する最後の砦になる</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="n"/>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="B65:E65"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B66:E66"/>
     <mergeCell ref="A55:E55"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A37:E41"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B57:E57"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A68:E68"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26705,7 +28825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -26787,7 +28907,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>台帳の**中央管理項目**（enabled / alertRouting）を運用者が変更する。アプリ側からは設定できない項目であり、**巡回（対象検索-09）はこれらを上書きしない**（12 章）。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -26873,7 +28997,12 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>運用者に配置バケットへの読み書き権限があること
+変更手順が Runbook 化されていること（WBS W4-1 ④）</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -26913,18 +29042,58 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>対象レコード</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>registry/{appId}/{env}.json</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>配置バケット</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>変更内容</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>enabled / alertRouting</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>運用者</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>**中央管理項目のみ**。baseUrl 等のアプリ由来項目は変更しない</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n"/>
@@ -26963,16 +29132,48 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>更新後レコード</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>S3 オブジェクト</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>配置バケット</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>変更履歴</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>S3 バージョニング</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>配置バケット</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>旧版が保全され、誤更新時に戻せる</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n"/>
@@ -27005,40 +29206,94 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】巡回（対象検索-09）との競合手順、変更履歴の追跡（Versioning）、承認フローの要否を明記する</t>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>対象レコードを GetObject し、**ETag を控える**</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>楽観ロックの基準</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>**中央管理項目のみを変更する**</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>baseUrl / authPattern / openApiS3Key は巡回が同期する項目であり、手で変えても次の巡回で上書きされる。変更したいなら認証構成情報（アプリ側）を直すのが正しい経路</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>**If-Match（控えた ETag）付きで PutObject する**</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>巡回（対象検索-09）と同じ楽観ロック方式。**双方が If-Match を使うことで相互に上書きしない**</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="A32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>**412 が返ったら再取得してやり直す**</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>巡回が先に更新した。手元の内容で上書きすると巡回の同期結果を消してしまう</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>変更の理由と実施者を記録する</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Runbook の実施記録（W4-1 ④）。CloudTrail にも API 呼び出しが残る</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>運用者 -&gt; 配置バケット : GetObject -&gt; 編集 -&gt; PutObject（If-Match）
 巡回と競合した場合は 412 -&gt; 再取得
@@ -27046,270 +29301,463 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38"/>
     <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40"/>
+    <row r="41"/>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-    </row>
     <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>412 Precondition Failed</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>S3 応答</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>再取得してやり直す</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>対象検索-09 と同じ方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>誤ってアプリ由来項目を変更した</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>次の巡回で上書きされる（変更が消える）。**実害は小さいが混乱の元**</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Runbook で注意喚起</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>enabled=false にしたまま戻し忘れた</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>**そのアプリが監視されない状態が続く**。月次棚卸し（対象検索-13）で検出する</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>棚卸しアラート → P2</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>17 §17.2.3 / WBS W4-1 ⑤</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>誤更新・削除</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>**バージョニングから旧版を復元する**</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>JSON を壊した</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>パース例外</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>検査側（認証実装チェック-01）と巡回側（対象検索-05）の両方が当該アプリで失敗する</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>MM-3 / MM-4 → P2</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>再実行時の振る舞い</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>状態更新のタイミング</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>8. 権限・エンドポイント</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>権限 / エンドポイント</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>s3:GetObject / s3:PutObject（ETag 条件付き）</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>認証方式・補足</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
+          <t>再実行時の振る舞い</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>同じ変更を何度適用しても結果は同じ。条件付き書き込みにより、競合時はどちらか一方だけが成功する。</t>
+        </is>
+      </c>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
     </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>9. ログ・メトリクス</t>
-        </is>
-      </c>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>状態更新のタイミング</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>**enabled を true に戻せるのは本処理だけ**（対象検索-09 は認証構成情報が再び置かれた場合に戻す）。false に落とすのは 対象検索-13 の消滅検知と本処理の 2 経路。</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>名称・項目</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>8. 権限・エンドポイント</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>s3:GetObject / s3:PutObject（ETag 条件付き）</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>認証方式・補足</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>運用者に s3:GetObject / s3:PutObject（If-Match のため GetObject が必須）
+**alertRouting には SNS ARN が入る**ため、閲覧・変更権限は運用担当に限定する
+変更の記録は CloudTrail に依存する（共通基盤アカウントで有効であることが前提）</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
+          <t>9. ログ・メトリクス</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>名称・項目</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>監査ログ</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>CloudTrail PutObject</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>実行者 / 時刻 / 対象キー</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>手動操作の追跡</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="n"/>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>想定件数 / 所要時間</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>随時（アプリ追加時・監視の一時停止時）</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>上限・制約</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>A-6</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>alertRouting の運用方式（誰がいつ設定するか。アプリ追加時の手順）</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>運用 / 設計担当</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-37</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>enabled=false にする際の承認フローの要否。**監視を止める操作**であり、無断で止められると検知の空白が生まれる。案: 理由の記録を必須とし、棚卸しで定期確認する（承認フローまでは求めない）</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>運用 / セキュリティ</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n"/>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="B54:E54"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="B66:E66"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="A37:E41"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B67:E67"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27322,7 +29770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -27404,7 +29852,11 @@
           <t>フロー内の位置</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>**本機構の入口**であり、唯一アプリ（ベンダー）側が実施する処理。ここが実行されないと以降の全処理が古い情報で動く（17 §17.2.2）。</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -27490,7 +29942,13 @@
           <t>前提条件・事前状態</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>連携バケットと ArtifactUploadRole-{appId} が StackSets で配布済み（16 §16.2.2 / WBS S2）
+ベンダー CI から AWS への接続方式が確定していること（方式はアプリごとに既存のもので可。W1-7）
+配布資料が渡っていること（vendor-guide-artifact-upload.md）</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -27530,66 +29988,143 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>monitoring.yaml</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>YAML</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>ベンダーのリポジトリ</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>監視宣言。appId / environments / baseUrl / authPattern</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>openapi.yaml</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>YAML/JSON</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>**デプロイした版**の API 仕様。公開明示（MON-1）を含む</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>deploy-info.json</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>CI が生成</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>commitId / deployedAt / pipelineRunId。追跡用の参考値</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>3. 出力（O）</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>出力先</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>説明・例</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-    </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>認証構成情報</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>S3 オブジェクト</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>連携バケット {appId}/</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>**新しい VersionId が発行され、これが検知シグナルになる**</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n"/>
@@ -27622,40 +30157,79 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【設計時の要記載】デプロイ成功後に実行すること（順序逆転の禁止）、配置漏れは原則アプリ責任（M-Q-17-7）である旨を明記する</t>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>**デプロイが成功したことを確認してから実行する**</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>【重要】順序が逆転すると、実際には反映されていない内容で検査され誤判定になる。デプロイ失敗時はアップロードしない（前回の内容が残り、実態と一致した状態が保たれる）</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>ArtifactUploadRole-{appId} を Assume する</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>権限は `{appId}/` 配下への **PutObject のみ**（読み取り・削除は不可）。デプロイロールとは分離されている</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>monitoring.yaml / openapi.yaml を `{appId}/` 配下へ**同名で上書き**アップロードする</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>バージョニングにより旧版は自動で保全される。**同じ内容でも再アップロードすれば新しい VersionId が発行され、デプロイされたことが中央に伝わる**（17 §17.2.1 差分判定の原則②）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>deploy-info.json を任意でアップロードする</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>監視の動作には影響しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>ベンダー CI -&gt; STS : AssumeRole(ArtifactUploadRole-{appId})
 ベンダー CI -&gt; 連携バケット : PutObject(monitoring.yaml, openapi.yaml, deploy-info.json)
@@ -27663,110 +30237,202 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37"/>
     <row r="38"/>
     <row r="39"/>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40"/>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-    </row>
     <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>アップロードを忘れた</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>古い情報のまま検査が継続し、**新設 endpoint は検査対象に入らない**。**原則アプリ責任**（顧客合意 M-Q-17-7）。中央は staleness 検知と月次棚卸しで補助する</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>鮮度低下アラート → P2（対象検索-13）</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>17 §17.2.2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>デプロイ前にアップロードした（順序逆転）</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>未反映の内容で検査され誤判定になる。次回巡回・日次全量が実態基準で再検査する</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>17 §17.2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>権限不足（ロール未払い出し・信頼設定不備）</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>AccessDenied</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>アップロードできない。CI が失敗する</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>W1-7 で受入確認する</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>7. 冪等性・リトライ</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>他アプリのプレフィックスへ書こうとした</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>AccessDenied</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>**ロールが `{appId}/` に限定されているため拒否される**。仮に書けても appId 検証で弾かれる（対象検索-08）</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>16 §16.2.2</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>再実行時の振る舞い</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>内容に不備がある</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>対象検索-08 の検証</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>取り込みを拒否され、監視対象にならない。**同じ版では再通知されない**（拒否レコード）</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>メタ不足アラート → P2</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>対象検索-12</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>状態更新のタイミング</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
+      <c r="A49" s="10" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>8. 権限・エンドポイント</t>
+          <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>権限 / エンドポイント</t>
+          <t>再実行時の振る舞い</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>ArtifactUploadRole-{appId} を Assume / s3:PutObject（{appId}/* 限定）/ s3.{region}.amazonaws.com</t>
+          <t>同じ内容を何度アップロードしても、中央側は「新しい版がデプロイされた」として検査を起動するだけで害はない。ただし不要な再検査が走るため、デプロイのたびに 1 回とする。</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
@@ -27776,10 +30442,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>認証方式・補足</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
+          <t>状態更新のタイミング</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>**アップロードが唯一の状態変更**。以降の処理はすべてこれを読むだけで、アプリ側へ書き戻すことはない。</t>
+        </is>
+      </c>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
@@ -27787,146 +30457,261 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
+          <t>8. 権限・エンドポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>ArtifactUploadRole-{appId} を Assume / s3:PutObject（{appId}/* 限定）/ s3.{region}.amazonaws.com</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>認証方式・補足</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>ArtifactUploadRole-{appId}（`{appId}/*` 限定の s3:PutObject のみ）。**デプロイロールとは分離**
+信頼ポリシーはベンダー CI の接続方式（OIDC フェデレーション / IAM ロール / アクセスキー）に合わせて設定する
+1 ベンダーが複数アプリを担当する場合も**ロールはアプリ単位**（他アプリの領域には書けない）</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>10. 性能・上限</t>
-        </is>
-      </c>
-    </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>想定件数 / 所要時間</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>監査ログ</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>CloudTrail PutObject（App アカウント）</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>実行者 / 時刻 / キー / VersionId</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>**アプリ側の資産として自然に残る**（中央へ書かせない設計の利点）</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>上限・制約</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
+      <c r="A62" s="10" t="n"/>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
+          <t>10. 性能・上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>想定件数 / 所要時間</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>デプロイのたびに 2〜3 オブジェクト</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>上限・制約</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>S3 PUT は 3,500 req/s（プレフィックス単位）。サイズ上限は M-Q-PD-6</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="10" t="n"/>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-17-7</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>**配置漏れ・内容誤りは原則アプリ責任**とする責任分界の顧客・ベンダー合意</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>顧客 / 法務</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>合意待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-21</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>$ref の外部参照を使う場合、単一ファイルに bundle してからアップロードする規約の追加</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-28</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>baseUrl にパスプレフィックス（/v1 等）まで含めて書く規約の明文化</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n"/>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="B65:E65"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B62:E62"/>
     <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A36:E40"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B66:E66"/>
     <mergeCell ref="A55:E55"/>
+    <mergeCell ref="B56:E56"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A42:E42"/>
     <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A47:E47"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B57:E57"/>
     <mergeCell ref="B53:E53"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A68:E68"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/doc/excel/apipf-process-design.xlsx
+++ b/doc/excel/apipf-process-design.xlsx
@@ -4942,7 +4942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>payload = {mode:'delta', appId, env}</t>
+          <t>payload = {mode:'delta', appId, env, origin:'delta'}</t>
         </is>
       </c>
     </row>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>payload は {mode:'delta', appId, env} のみとする</t>
+          <t>payload は {mode:'delta', appId, env, origin:'delta'} とする</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>検査側は台帳と仕様を自分で読む。**対象検索側は差分の中身を渡さない**（17 §17.2.1 差分判定の原則③）。これにより検査 Lambda はモード1/モード2 で同一実装になる</t>
+          <t>検査側は台帳と仕様を自分で読む。**対象検索側は差分の中身を渡さない**（17 §17.2.1 差分判定の原則③）。これにより検査 Lambda はモード1/モード2 で同一実装になる。**origin は巡回起点でも必ず付ける**（付けたり付けなかったりすると「origin が無い＝巡回起点」という暗黙のルールになり読みにくい）。検査側は判定に使わずログにのみ出す（README §2.6）</t>
         </is>
       </c>
     </row>
@@ -5905,26 +5905,44 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
+          <t>M-Q-PD-19</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>【解決・2026-09-16】origin は**巡回起点・全量起点の両方で必ず付ける**（付けない経路があると暗黙ルールになるため）。README §2.6 に定義済み</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>—（解決済み）</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
           <t>M-Q-PD-11</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>【解決・2026-09-14】失敗の受け皿は **On-failure Destination（送信先は SQS）** を採用。DLQ はイベント本文とエラーメッセージ先頭 1KB しか残らないのに対し、Destination は**呼び出し記録（requestContext の試行回数・requestPayload・responsePayload）を JSON で残せる**ため障害調査が容易。18 §18.5.1/§18.5.2・WBS A5 を改訂済み。※ EventBridge Scheduler 側は Destination 非対応のため**従来どおり DLQ（SQS 標準キュー）**（対象検索-01）</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>—（解決済み）</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="n"/>
-      <c r="B77" s="10" t="n"/>
-      <c r="C77" s="10" t="n"/>
-      <c r="D77" s="10" t="n"/>
+      <c r="D77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="n"/>
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -21945,7 +21963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -22295,497 +22313,541 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>AuthCheckPassed</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Count=N</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch（共通基盤）</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>OK 判定の件数（README §2.4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>EndpointsProbed</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Count=N</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>CloudWatch（共通基盤）</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>検査した endpoint 数（README §2.4）。**0 件なら「検査したのに対象が無い」状態**で、仕様の取り込み漏れを疑える</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>処理内容</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>補足・参照</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>endpoint ごとの判定を severity 別に集計する</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>1 アプリ 1 回の送信にまとめ、endpoint 単位では送らない</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>AuthCheckCritical を PutMetricData する。**0 件でも 0 を送る**</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>値を送らないと「検査していない」と「異常なし」が区別できない。アラームは &gt; 0 で発報するため、0 の送信はアラーム動作に影響しない</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>ディメンションは appId / env に限定する</t>
+          <t>endpoint ごとの判定を severity 別に集計する</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>【注意】**メトリクスはディメンションの組合せごとに課金される**（RC-7 が最大費目）。endpoint 単位のディメンションを付けると endpoint 数 × アプリ数で急増するため付けない。endpoint 単位の情報は 認証実装チェック-06 のログ（CloudWatch Logs Insights）で追う</t>
+          <t>1 アプリ 1 回の送信にまとめ、endpoint 単位では送らない</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>**この送信は即時系（認証実装チェック-08）と独立して行う**</t>
+          <t>AuthCheckCritical を PutMetricData する。**0 件でも 0 を送る**</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>アラート検知 Lambda が壊れていても保険系アラームが鳴るようにするため。両方そろって初めて検知網が閉じる（18 §18.5.1）</t>
+          <t>値を送らないと「検査していない」と「異常なし」が区別できない。アラームは &gt; 0 で発報するため、0 の送信はアラーム動作に影響しない</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>ディメンションは appId / env に限定する</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>【注意】**メトリクスはディメンションの組合せごとに課金される**（RC-7 が最大費目）。endpoint 単位のディメンションを付けると endpoint 数 × アプリ数で急増するため付けない。endpoint 単位の情報は 認証実装チェック-06 のログ（CloudWatch Logs Insights）で追う</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>**この送信は即時系（認証実装チェック-08）と独立して行う**</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>アラート検知 Lambda が壊れていても保険系アラームが鳴るようにするため。両方そろって初めて検知網が閉じる（18 §18.5.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>PutMetricData の失敗は記録して握り潰す</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>メトリクス送信の失敗で検査結果を覆さない</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-    </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>認証実装チェック Lambda -&gt; CloudWatch : PutMetricData(AuthCheckCritical ほか, ディメンション=appId/env)
 【シーケンス図の所在】11 §11.1 検査実行シーケンス / 10 §10.1.7 F2</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40"/>
     <row r="41"/>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="42"/>
+    <row r="43"/>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>6. 例外・異常系</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>検知方法</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>参照</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL が 1 件以上</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>集計</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>AuthCheckCritical = N を送信</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>保険系アラーム &gt; 0 → P1 Security</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>18 §18.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>全 endpoint が観測不能</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>集計</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL は 0 だが WARN が全件になる。**アプリ全面ダウンの可能性**</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>WARN 経由で P2 Platform</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>認証実装チェック-06</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
+          <t>CRITICAL が 1 件以上</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>集計</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>AuthCheckCritical = N を送信</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>保険系アラーム &gt; 0 → P1 Security</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>全 endpoint が観測不能</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>集計</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL は 0 だが WARN が全件になる。**アプリ全面ダウンの可能性**</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>WARN 経由で P2 Platform</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>認証実装チェック-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
           <t>PutMetricData 失敗</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>API 例外</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>記録して継続。**即時系（認証実装チェック-08）は独立して動くため通知は届く**</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>発報 2 系統の利点</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="10" t="n"/>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
-    </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="10" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>7. 冪等性・リトライ</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>再実行時の振る舞い</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>同じ検査で複数回送っても CloudWatch 側は同一タイムスタンプの値として扱う。1 回に留める。</t>
         </is>
       </c>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>状態更新のタイミング</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>状態を更新しない。</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>8. 権限・エンドポイント</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>権限 / エンドポイント</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>cloudwatch:PutMetricData / monitoring.{region}.amazonaws.com</t>
         </is>
       </c>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>認証方式・補足</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>cloudwatch:PutMetricData。共通基盤アカウント内</t>
         </is>
       </c>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>9. ログ・メトリクス</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>名称・項目</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>メトリクス</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>AuthCheckCritical / AuthCheckWarn / AuthCheckInfo</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>severity 別件数</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>ディメンションは appId / env のみ</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="10" t="n"/>
-      <c r="B61" s="10" t="n"/>
-      <c r="C61" s="10" t="n"/>
-      <c r="D61" s="10" t="n"/>
-    </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="A63" s="10" t="n"/>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>10. 性能・上限</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>想定件数 / 所要時間</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>1 アプリにつき 1 回。カスタムメトリクスはアプリ数 × env 数 × 種類数で増える</t>
         </is>
       </c>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>上限・制約</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>**PutMetricData は 1 リクエスト 1 MB / 1,000 メトリクス / 30 ディメンションまで**。アプリ数比例でメトリクス課金が増える点は費用見積 RC-7 に織り込み済み</t>
         </is>
       </c>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>11. 未決事項</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="7" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="10" t="n"/>
-      <c r="B69" s="10" t="n"/>
-      <c r="C69" s="10" t="n"/>
-      <c r="D69" s="10" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="n"/>
-      <c r="B70" s="10" t="n"/>
-      <c r="C70" s="10" t="n"/>
-      <c r="D70" s="10" t="n"/>
+    <row r="71">
+      <c r="A71" s="10" t="n"/>
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="10" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="n"/>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="B65:E65"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="A45:E45"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A39:E43"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="B54:E54"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="B66:E66"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="B56:E56"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="A37:E41"/>
+    <mergeCell ref="B58:E58"/>
     <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="A63:E63"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27129,7 +27191,7 @@
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>各 Lambda がメトリクスを emit していること（対象検索-14 / 全量-05 / 認証実装チェック-07）
-CloudWatch アラーム 6 本が作成済み（WBS B3-i〜B8-i / B10-i）</t>
+**メタ監視アラーム 6 本**（MM-1〜MM-6）が作成済み（WBS B3-i〜B7-i / B10-i）。これとは別に被監視系のアラーム（AuthCheckCritical = B2-i、Duration = B8-i）がある</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
@@ -27802,7 +27864,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>アラーム 1 本 $0.10/月 × 9 本（RC-8）</t>
+          <t>本処理が扱うメタ監視アラームは 6 本（MM-1〜6）。ブック全体のアラームは 8 本（B2-i〜B8-i + B10-i）で、費用見積 RC-8 は余裕を見て 10 本で計上している（1 本 $0.10/月）</t>
         </is>
       </c>
       <c r="C68" s="4" t="n"/>

--- a/doc/excel/apipf-process-design.xlsx
+++ b/doc/excel/apipf-process-design.xlsx
@@ -6918,12 +6918,12 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>不備が解消されたときに「解消しました」の通知を出すか。出さない場合、受け手は自分で直したことを自覚しているはずという前提に依存する</t>
+          <t>【解決・2026-09-16】**解消通知は出さない**。直した側は自覚しているのが通常であり、通知を増やすとアラート全体の重みが下がるため。解消の事実は台帳の拒否フィールドがクリアされることで確認できる</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>運用設計（WBS W4-1）</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr"/>
@@ -11044,7 +11044,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>AWS Organizations</t>
+          <t>SSM Parameter Store（監視対象アカウント一覧）</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>巡回対象となる App アカウントの一覧を取得する。</t>
+          <t>巡回対象となる App アカウントの一覧を、中央が管理する登録リストから取得する。</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -27908,12 +27908,12 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>MM-1 と MM-6 が同時発報した場合に、個別通知ではなく『監視機構の全面停止』としてまとめて通知するか。個別に 2 通届いても対応は同じため、優先度は低い</t>
+          <t>【解決・2026-09-16】**まとめて通知する**。MM-1（巡回停止）と MM-6（全量確認停止）が同時に発報している場合は、個別の 2 通ではなく『**監視機構の全面停止**』として 1 通で通知する。2 つが同時に止まっている状態は個別の障害とは重大度が異なり、それが件名で伝わるようにするため</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr"/>
@@ -31870,7 +31870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -31902,7 +31902,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>巡回対象となる App アカウントの一覧を取得する。</t>
+          <t>巡回対象となる App アカウントの一覧を、中央が管理する登録リストから取得する。</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -31984,7 +31984,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>AWS Organizations</t>
+          <t>SSM Parameter Store（監視対象アカウント一覧）</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -32044,9 +32044,9 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>列挙方式が確定していること（**M-Q-17-2**。案 c = Organizations のリソースベース委任ポリシーが推奨）
-【注意】ListAccounts は**管理アカウントか委任管理者からしか呼べない**。共通基盤アカウントから直接呼ぶには、管理アカウントで PutResourcePolicy による委任が必要（organizations:ListAccounts は公式に委任可能アクションとして列挙されている）
-委任先（共通基盤アカウント）の Lambda ロール側にも organizations:ListAccounts の IAM 権限が要る（**両方揃わないと拒否される**）</t>
+          <t>監視対象アカウントの登録リストが SSM Parameter Store に存在すること
+リストへの登録は**申請ベース**（案件側が連携バケットと読み取りロールを作成し、中央へアカウント ID の登録を依頼する）。オンボーディング手順は vendor-guide に記載
+Lambda ロールに ssm:GetParameter（対象パラメータに限定）があること</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
@@ -32090,54 +32090,54 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>対象範囲</t>
+          <t>パラメータ名</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>OU / 明示リスト / 組織全体</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>要</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Lambda 環境変数 or SSM</t>
+          <t>Lambda 環境変数</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>組織全体だと管理アカウント・監査アカウント等も返るため、**App アカウントに絞る条件が必要**（M-Q-17-2）</t>
+          <t>例 /auth-monitoring/target-accounts</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MaxResults</t>
+          <t>登録リスト</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>JSON 配列</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>要</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>実装定数</t>
+          <t>SSM Parameter Store</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>**最大 20**（ListAccounts の上限。1000 ではない）。ページングは必須</t>
+          <t>[{accountId, appOwner, registeredAt}] 形式。**中央が管理する**（アプリ側からは書き換えられない）</t>
         </is>
       </c>
     </row>
@@ -32185,7 +32185,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>[{accountId, name, state}]</t>
+          <t>[{accountId, …}]</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -32195,7 +32195,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>State=ACTIVE のみを対象とする。SUSPENDED / PENDING_CLOSURE / CLOSED は除外</t>
+          <t>登録されているアカウントのみ</t>
         </is>
       </c>
     </row>
@@ -32217,7 +32217,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>取得件数・除外件数・ページ数。アカウント ID は出すがメールアドレスは出さない</t>
+          <t>取得件数。アカウント ID は出すが担当者情報は出さない</t>
         </is>
       </c>
     </row>
@@ -32257,12 +32257,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>委任ポリシー経由で organizations:ListAccounts を呼ぶ（エンドポイントは organizations.us-east-1.amazonaws.com）</t>
+          <t>SSM Parameter Store から監視対象アカウントの登録リストを取得する</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Organizations は us-east-1 にホストされるグローバルサービス</t>
+          <t>**Organizations の ListAccounts は使わない**（2026-09-16 確定）。連携バケットと読み取りロールを**案件側が作成する**方式にしたため、組織全体を列挙しても『どのアカウントが監視対象か』を判別できず、判別のために全アカウントへ AssumeRole を試すと対象外アカウントで必ず失敗してDiscoveryAccountErrors（MM-3）が常時発報し、本物の障害が埋もれるため</t>
         </is>
       </c>
     </row>
@@ -32272,12 +32272,12 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>NextToken が null になるまでページングする。**空の結果が返っても打ち切らない**</t>
+          <t>JSON をパースして accountId の配列を得る</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>【注意】AWS 公式の警告: 「結果が空でも、まだ続きがある場合がある。NextToken が null になるまで繰り返すこと」</t>
+          <t>形式不正は巡回を中断（黙って 0 件で進めない）</t>
         </is>
       </c>
     </row>
@@ -32287,118 +32287,142 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>各アカウントの **State** を見て ACTIVE 以外を除外する</t>
+          <t>リストが空なら異常として扱い、巡回を中断してアラートする</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>【注意】旧 `Status` パラメータは **2026-09-09 に廃止**。新規実装は **State** を使う（PENDING_ACTIVATION / ACTIVE / SUSPENDED / PENDING_CLOSURE / CLOSED）</t>
+          <t>「対象が消えた」のか「パラメータを壊した」のかを区別できないため、0 件で正常終了しない（誤って全アプリが消滅検知されるのを防ぐ、対象検索-13）</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>対象範囲の条件（OU / 明示リスト）で絞り込む</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>組織全体を返すため、監視対象でないアカウント（管理・監査・ネットワーク等）を除外する</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>結果が 0 件なら異常として扱い、巡回を中断してアラートする</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>「対象が消えた」のか「権限を失った」のかを区別できないため、黙って 0 件で正常終了しない（誤って全アプリが消滅検知されるのを防ぐ、対象検索-13）</t>
-        </is>
-      </c>
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>5. シーケンス（矢印記法。必要に応じて図を貼付）</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>対象検索 Lambda -&gt; Organizations : ListAccounts
-Organizations --&gt; 対象検索 Lambda : アカウント一覧
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>対象検索 Lambda -&gt; SSM Parameter Store : GetParameter（監視対象アカウント一覧）
+SSM --&gt; 対象検索 Lambda : アカウント ID の配列
 【シーケンス図の所在】17 §17.2.1 巡回シーケンス図（対象検索-01〜14 を通した図）/ 10 §10.1.7 F1</t>
         </is>
       </c>
     </row>
+    <row r="36"/>
+    <row r="37"/>
     <row r="38"/>
     <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>6. 例外・異常系</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>ケース</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>検知方法</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>動作</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>参照</t>
+        </is>
+      </c>
+    </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>6. 例外・異常系</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>パラメータが存在しない</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>ParameterNotFound</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>巡回を中断</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>MM-2 → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>18 §18.5.1</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>ケース</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>検知方法</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>動作</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>通知</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>参照</t>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>JSON の形式不正</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>パース例外</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>巡回を中断</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>MM-2 → P2 Platform</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>AccessDeniedException（委任ポリシー未設定・IAM 権限不足）</t>
+          <t>リストが空</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>API 例外</t>
+          <t>件数</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>巡回を中断（アカウント単位の継続はしない）</t>
+          <t>巡回を中断し、消滅検知（対象検索-13）を実行しない</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -32408,14 +32432,14 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>16 §16.3</t>
+          <t>対象検索-13 の前提</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TooManyRequestsException（HTTP 400）</t>
+          <t>AccessDenied</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -32425,7 +32449,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>SDK 標準リトライ（指数バックオフ）で吸収。それでも失敗なら中断</t>
+          <t>巡回を中断</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -32435,393 +32459,335 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>§10 上限・制約</t>
+          <t>16 §16.3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>空ページが返る（NextToken は非 null）</t>
+          <t>**アカウントの登録漏れ**</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>応答</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>**打ち切らず次ページへ進む**</t>
+          <t>**そのアカウントのアプリは一切監視されない**（巡回対象に入らないため、アプリ単位の自動発見も働かない）</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>月次棚卸しで検出（M-Q-17-3）</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>AWS 公式の明示警告</t>
+          <t>本方式の受容したリスク。§11 未決参照</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>State=SUSPENDED / CLOSED のアカウント</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>応答フィールド</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>対象から除外。台帳に該当アプリがあれば 対象検索-13 で棚卸し対象</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>棚卸しアラート → P2</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>対象検索-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>対象 0 件</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>巡回を中断し、消滅検知（対象検索-13）を実行しない</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>MM-2 → P2 Platform</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>対象検索-13 の前提</t>
-        </is>
-      </c>
+      <c r="A48" s="10" t="n"/>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="n"/>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>7. 冪等性・リトライ</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>再実行時の振る舞い</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>読み取りのみで副作用なし。</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>7. 冪等性・リトライ</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>再実行時の振る舞い</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>読み取りのみで副作用なし。何度実行しても同じ結果が得られる。</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>状態更新のタイミング</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>状態を更新しない。</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>状態更新のタイミング</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>状態を更新しない。</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>8. 権限・エンドポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>権限 / エンドポイント</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>ssm:GetParameter（対象パラメータに限定）/ ssm.{region}.amazonaws.com</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>8. 権限・エンドポイント</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>権限 / エンドポイント</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>organizations:ListAccounts（委任ポリシー方式が推奨。M-Q-17-2）/ organizations.us-east-1.amazonaws.com</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="n"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>認証方式・補足</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>ssm:GetParameter（対象パラメータ 1 本に限定）。共通基盤アカウント内のため AssumeRole は不要
+**Organizations の委任ポリシーは不要になった**（2026-09-16）。組織の管理アカウントへの依頼（旧 W1-3 / M-Q-17-2）が外部調整から落ちる
+登録リストは**中央管理**。アプリ側が書き換えられる場所に置かない（勝手に監視対象から外れないようにするため）</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>認証方式・補足</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>**委任方式（推奨）**: 管理アカウントで organizations:PutResourcePolicy によりリソースベース委任ポリシーを設定し、共通基盤アカウントに organizations:ListAccounts を委任する。管理アカウントへの AssumeRole が不要になる
-【注意】委任ポリシーは最大 40,000 文字。**2026-06-30 以降 NotAction / NotResource は使用不可**
-代替案: 管理アカウントに列挙専用の読み取りロールを置き AssumeRole（案 a）/ SSM Parameter に静的リスト（案 b）。案 b はアカウント追加時の登録漏れ = 監視漏れに直結するため非推奨</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>9. ログ・メトリクス</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>名称・項目</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>9. ログ・メトリクス</t>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>アプリログ</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>アカウント列挙結果</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>取得件数 / 所要 ms</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>担当者情報（連絡先等）は出力しない</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>名称・項目</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="A61" s="10" t="n"/>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>10. 性能・上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>想定件数 / 所要時間</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>巡回ごとに 1 回の GetParameter。Phase 1 は約 3 アカウント</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>上限・制約</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>SSM Parameter Store の Standard パラメータは 4KB 上限。アカウント数が増えて超える場合は Advanced（8KB）または S3 上の台帳へ移す（M-Q-PD-38）</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>11. 未決事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>アプリログ</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>アカウント列挙結果</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>取得件数 / State 別内訳 / 除外件数 / ページ数 / 所要 ms</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>メールアドレスは出力しない（個人情報）</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>メトリクス</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>本処理単体ではメトリクスを出さない</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>巡回全体の結果は 対象検索-14 で集約</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="n"/>
-      <c r="B64" s="10" t="n"/>
-      <c r="C64" s="10" t="n"/>
-      <c r="D64" s="10" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>10. 性能・上限</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>想定件数 / 所要時間</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Phase 1 は約 3 アカウント（1 ページで完了）。将来 100 アカウントでも MaxResults=20 なら 5 ページ・1 秒未満</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>上限・制約</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>**ListAccounts のスロットリング: アカウント単位 8 req/s（バースト 12）/ 組織単位 9 req/s（バースト 15）**。1 時間に 1 回・数ページの呼び出しなので余裕は大きい</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>確認先</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-4</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>【解決・2026-09-16】対象アカウントは **SSM Parameter Store の登録リスト（申請ベース）** とする。連携バケットと読み取りロールを**案件側が作成する**方針に変更したため、Organizations での全アカウント列挙では監視対象を判別できず、判別のための AssumeRole 試行は MM-3 の常時発報を招くため。**代償: アカウント単位では登録漏れが起きうる**（アプリ単位の自動発見は従来どおり）。月次棚卸しで補完する</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>—（解決済み）</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>11. 未決事項</t>
-        </is>
-      </c>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-PD-38</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>登録リストの置き場（SSM Standard 4KB / Advanced 8KB / S3）。アカウント数が数十を超えるなら S3 上の台帳に移すことを検討</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>設計担当</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>確認先</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>期限</t>
-        </is>
-      </c>
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>M-Q-17-3</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>アカウント単位の登録漏れを検出する棚卸しの方法（API 提供契約 / Service Catalog の払い出し実績との突合）。**本方式では重要度が上がる**（アプリ単位の自動発見が効かない層のため）</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>設計担当 + 運用</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>M-Q-17-2</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>列挙方式（委任ポリシー / AssumeRole / 静的リスト）と対象範囲（組織全体 / OU / 明示リスト）の確定</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>管理アカウント管理者</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>M-Q-PD-4</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>App アカウントを識別する条件。OU 単位で括るのか、タグやアカウント名の規約で判定するのか。組織全体を返す API なので、何らかの絞り込み条件が必ず要る</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>設計担当</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="n"/>
-      <c r="B74" s="10" t="n"/>
-      <c r="C74" s="10" t="n"/>
-      <c r="D74" s="10" t="n"/>
+      <c r="A72" s="10" t="n"/>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A34:E34"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="B65:E65"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B64:E64"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B55:E55"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A41:E41"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="B56:E56"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="A37:E41"/>
+    <mergeCell ref="B52:E52"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B67:E67"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="A52:E52"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A63:E63"/>
     <mergeCell ref="B10:E10"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A35:E39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33008,7 +32974,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>各 App アカウントに DiscoveryReadRole が StackSets で配布済み（16 §16.2 / WBS S0・S1）
+          <t>各 App アカウントに DiscoveryReadRole が作成済み（**案件側が中央提供のテンプレートで作成する**。2026-09-16 変更。16 §16.2 / WBS S0・S1）
 信頼ポリシーの Principal が対象検索 Lambda のロール 1 本に限定され、sts:ExternalId 条件が設定済み
 共通基盤側の Lambda ロールに sts:AssumeRole（各 App の DiscoveryReadRole ARN）が付与済み</t>
         </is>
@@ -33433,27 +33399,27 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>ロールが存在しない（新規アカウントで StackSets 未反映）</t>
+          <t>ロールが存在しない（案件側が未作成）</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>NoSuchEntity / AccessDenied</t>
+          <t>AccessDenied</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>同上。StackSets の自動デプロイ待ちとして扱う</t>
+          <t>当該アカウントをスキップし継続。**登録リストに載っているのにロールが無い = オンボーディング未完了**であり、MM-3 で気づいて案件側へ督促する</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>DiscoveryAccountErrors ≥ 1 → MM-3 → P2 Platform</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>16 §16.4</t>
+          <t>16 §16.4 / vendor-guide</t>
         </is>
       </c>
     </row>
@@ -33970,7 +33936,7 @@
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>対象検索-03 で当該アカウントの一時クレデンシャルを取得済み
-連携バケット auth-monitoring-artifacts-{accountId} が StackSets で配布済み、**バージョニング有効**（16 §16.4 / WBS S2）
+連携バケット auth-monitoring-artifacts-{accountId} が作成済み、**バージョニング有効**（**案件側が中央提供のテンプレートで作成する**。2026-09-16 変更。16 §16.4 / WBS S2）
 DiscoveryReadRole に s3:ListBucket **および s3:ListBucketVersions** が付与済み（【注意】権限名が別。16 §16.2）</t>
         </is>
       </c>
@@ -34343,7 +34309,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>バケットが存在しない（StackSets 未反映の新規アカウント）</t>
+          <t>バケットが存在しない（案件側が未作成）</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -34353,7 +34319,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>当該アカウントをスキップして継続</t>
+          <t>当該アカウントをスキップして継続。**登録リストに載っているのにバケットが無い = オンボーディング未完了**</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -34363,7 +34329,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>18 §18.5.2</t>
+          <t>18 §18.5.2 / vendor-guide</t>
         </is>
       </c>
     </row>

--- a/doc/excel/apipf-process-design.xlsx
+++ b/doc/excel/apipf-process-design.xlsx
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>認証構成情報のサイズ上限（openapi.yaml が巨大なアプリの扱い）。旧 CodeCommit 方式には GetFile の 6MB 制約があったが、S3 には該当する API 制約がないため、**Lambda のメモリと処理時間から上限を決める必要がある**（案: 1 ファイル 5MB）</t>
+          <t>【解決・2026-09-18】**1 ファイル 5MB** を上限とする。S3 側に API 制約は無いため、Lambda のメモリと処理時間から決めた値。超過は取り込み拒否とし不備通知する</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr"/>
@@ -2953,12 +2953,12 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>monitoring.yaml から環境が削除された場合の扱い（台帳レコードを enabled=false にするか、誤削除の可能性を考えて棚卸し通知にとどめるか）</t>
+          <t>【解決・2026-09-18】**棚卸し通知にとどめる**（enabled は自動で変えない）。monitoring.yaml からの env 削除は誤記の可能性があり、消滅検知（対象検索-13）と同じく人の確認を挟む</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr"/>
@@ -4028,12 +4028,12 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>412 競合時のリトライ回数と待ち方（案: 3 回・短いジッタ付き）。競合相手は運用者の手動更新（運用-03）か多重起動した巡回で、いずれも頻度は低い</t>
+          <t>【解決・2026-09-18】**3 回・短いジッタ付き**で確定。競合相手は運用者の手動更新（運用-03）か多重起動した巡回で頻度は低く、3 回で収束しなければ MM-3 で気づく</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr"/>
@@ -5892,12 +5892,12 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>巡回の相関 ID を検査依頼の payload に含め、検査側ログまで追跡できるようにするか。含めると「どの巡回が起こした検査か」を追えるが、payload に検査側が使わない項目が増える</t>
+          <t>【解決・2026-09-18】**巡回の相関 ID を payload に含める**。「どの巡回が起こした検査か」をログで追えるようにする。検査側は判定に使わずログにのみ出す（origin と同じ扱い）</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr"/>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>1 アカウントで大量の消滅判定が出た場合に自動で enabled=false にしてよいか。安全弁として『N 件以上 / 全体の X% 以上なら自動更新せず通知のみ』の閾値を設けるか</t>
+          <t>【解決・2026-09-16】**閾値を超えたら自動更新せず通知のみ**。同一アカウントで **5 件以上または対象の半数以上**が消滅判定になった場合は enabled を変更せず P2 通知に留める</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr"/>
@@ -8902,12 +8902,12 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>巡回メトリクスにアプリ単位のディメンションを持たせないこと（コスト起因）の確認。アプリ別の巡回状況を見たい要望が出た場合はログ（CloudWatch Logs Insights）で代替する</t>
+          <t>【解決・2026-09-18】**アプリ単位のディメンションは持たせない**。メトリクスはディメンションの組合せごとに課金され RC-7 が費用の最大費目のため。アプリ別の巡回状況はログ（CloudWatch Logs Insights）で追う</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr"/>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>payload に origin を追加することの確認（検査側は判定に使わずログ出力のみ）。code-samples/README §2 のイベント形式に追記が必要</t>
+          <t>【解決・2026-09-16】origin は**巡回起点・全量起点の両方で必ず付ける**（付けない経路があると暗黙ルールになるため）。README §2.6 に定義済み</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr"/>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>OpenAPI の servers は相対参照が可能で、`/v1` のようなパスプレフィックスだけが書かれていることがある。これを無視すると全 endpoint が 404 になり、**WARN（構成）が全件出るだけで認証漏れを検知できない**。暫定は baseUrl のみを使い、全件 404 になる場合は servers のパス欠落を疑う運用とする（M-Q-PD-28）</t>
+          <t>OpenAPI の servers は相対参照が可能で、`/v1` のようなパスプレフィックスだけが書かれていることがある。これを無視すると全 endpoint が 404 になり、**WARN（構成）が全件出るだけで認証漏れを検知できない**。**servers は無視し baseUrl のみを使う**（2026-09-18 確定）。アプリ側に「baseUrl はパスプレフィックス（/v1 等）まで含めて書く」ことを規約化した（ベンダー配布資料 §2.2）。全件 404 になる場合はこの記載漏れを疑う</t>
         </is>
       </c>
     </row>
@@ -17398,12 +17398,12 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>path parameter の dummy 値が未指定のときの既定値。案: 数値パラメータは 1、文字列は canary-test。実在しない ID になるため 404 が返りやすいが、**認証が効いていれば 404 より先に 401/403 が返る**ため検査は成立する</t>
+          <t>【解決・2026-09-18】**数値パラメータは 1、文字列は canary-test** を既定の dummy 値とする。実在しない ID で 404 が返りやすいが、認証が効いていれば 404 より先に 401/403 が返るため検査は成立する</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr"/>
@@ -17416,12 +17416,12 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>$ref による外部ファイル参照を解決するか。解決するなら参照先も認証構成情報として連携バケットに置いてもらう必要があり、アプリ側の作業が増える。案: 単一ファイルに bundle してからアップロードすることを規約にする（vendor-guide に追記）</t>
+          <t>【解決・2026-09-18】**外部 $ref は解決しない**（スキップして不備通知）。アプリ側に「**単一ファイルに bundle してからアップロードする**」ことを規約化し、ベンダー配布資料へ明記する</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr"/>
@@ -17452,12 +17452,12 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>OpenAPI の servers に書かれたパスプレフィックス（/v1 等）を baseUrl に結合するか。結合しないと全件 404 になり認証漏れを検知できない。結合すると baseUrl が既にプレフィックスを含む場合に二重になる。案: 結合せず、アプリ側に『baseUrl はプレフィックスまで含めて書く』ことを規約化する（vendor-guide に追記）</t>
+          <t>【解決・2026-09-18】**servers は無視し、baseUrl のみを使う**。アプリ側に「**baseUrl はパスプレフィックス（/v1 等）まで含めて書く**」ことを規約化し、ベンダー配布資料へ明記する。全件 404 になる場合はこの記載漏れを疑う</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr"/>
@@ -18447,12 +18447,12 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>検査中の 401 に対する再試行を 1 回に限るか（案: 1 回）。無制限に再試行するとトークン発行が増え、スコープ不足の場合は永久にループする</t>
+          <t>【解決・2026-09-18】**1 回まで**。無制限に再試行するとトークン発行が増え、スコープ不足の場合は永久にループするため</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr"/>
@@ -18465,12 +18465,12 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Secrets Manager Extension のキャッシュ TTL（既定 300 秒 / 最大 300 秒）。ローテーション直後に古い資格情報を使う窓を短くするなら 60 秒程度に下げる。下げると GetSecretValue の呼び出しが増えるが、費用は $0.05/1 万回で誤差</t>
+          <t>【解決・2026-09-18】**60 秒**に下げる。AWS 既定は 300 秒だが、ローテーション直後に古い資格情報を使う窓を短くする。GetSecretValue の呼び出しは増えるが費用は $0.05/1 万回で誤差</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr"/>
@@ -21605,12 +21605,12 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>WARN（構成）→ P2 Platform</t>
+          <t>**OK とする**（リダイレクト先は検証しない。2026-09-18 確定）</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>通知なし</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -21885,12 +21885,12 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Cookie 系でリダイレクト先が期待値と異なる場合の扱い（WARN にするか、リダイレクト先は見ないか）。厳密に見ると誤検知が増える可能性がある</t>
+          <t>【解決・2026-09-18】**リダイレクト先は検証しない**。302 が返れば期待どおりとして OK 判定にする。リダイレクト先まで厳密に見ると、ログイン画面の URL 変更などで誤検知が増えるため</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr"/>
@@ -21903,12 +21903,12 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>4×4 表に無い組合せ（例: negStatus=500）の既定分類。案: WARN（未分類）として通知し、頻出するものは表に追加していく</t>
+          <t>【解決・2026-09-18】**WARN（未分類）として通知する**。判定できなかったものを OK に倒さないことを原則とし、頻出する組合せは 4×4 表へ追加していく</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr"/>
@@ -24173,12 +24173,12 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>検知が大量（1 アプリで数千 endpoint が CRITICAL 等）のときの分割単位。そもそもその状態は『アプリ全体で認証が外れている』ことを意味するため、**件数を送って詳細は上位 N 件に絞る**方が通知として有用な可能性がある</t>
+          <t>【解決・2026-09-18】**件数を送り、詳細は上位 20 件に絞る**。1 アプリで数千件が CRITICAL になる状態は「アプリ全体で認証が外れている」ことを意味し、全件列挙より件数と代表例の方が通知として有用</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr"/>
@@ -25123,12 +25123,12 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>未知の severity が来た場合の既定の寄せ先（案: P2 Platform）。検査側と通知側で enum がずれた場合に通知を落とさないための保険</t>
+          <t>【解決・2026-09-18】**P2（Platform）へ寄せる**。検査側と通知側で enum がずれても通知を落とさないための保険</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr"/>
@@ -26956,12 +26956,12 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>AuthCheckCritical アラームの TreatMissingData（案: notBreaching）。検査が動いていないことの検知は MM-1 / MM-6 の役割であり、本アラームで二重に見る必要はない</t>
+          <t>【解決・2026-09-18】**notBreaching** とする。検査が動いていないことの検知は MM-1 / MM-6 の役割であり、本アラームで二重に見る必要はない</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr"/>
@@ -27926,12 +27926,12 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>アラーム自体の削除・無効化をどう検知するか。IaC（CloudFormation ドリフト検出）または Config Rules で担保する案</t>
+          <t>【解決・2026-09-18】**IaC のドリフト検出で担保する**。アラーム自体が削除・無効化されたことに気づけるようにする（W1-6 の Config Rules と併せて整備）</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr"/>
@@ -28809,12 +28809,12 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Destination 用 SQS の保持期間（既定 4 日 / 最大 14 日）。休日を挟んでも再処理できるよう長めが望ましい（案: 14 日）</t>
+          <t>【解決・2026-09-18】**14 日**（最大値）とする。休日や連休を挟んでも再処理できるようにするため。既定は 4 日</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>運用 / 設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr"/>
@@ -28827,12 +28827,12 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>DestinationDeliveryFailures の監視を追加するか。失敗の記録すら残らない状態を検知する最後の砦になる</t>
+          <t>【解決・2026-09-18】**追加する**。`DestinationDeliveryFailures` を監視し、**失敗の記録すら残らない状態**を検知する。これが無いと最後の砦が抜ける</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr"/>
@@ -29772,12 +29772,12 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>enabled=false にする際の承認フローの要否。**監視を止める操作**であり、無断で止められると検知の空白が生まれる。案: 理由の記録を必須とし、棚卸しで定期確認する（承認フローまでは求めない）</t>
+          <t>【解決・2026-09-16】**理由の記録を必須とし、承認フローは求めない**。台帳に停止理由と実施者・実施日時を残すことを必須とし、月次棚卸しで「止めたままのアプリ」を確認する。承認を必須にすると障害対応中の緊急停止ができなくなるため</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>運用 / セキュリティ</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr"/>
@@ -30708,12 +30708,12 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>$ref の外部参照を使う場合、単一ファイルに bundle してからアップロードする規約の追加</t>
+          <t>【解決・2026-09-18】**外部 $ref は解決しない**（スキップして不備通知）。アプリ側に「**単一ファイルに bundle してからアップロードする**」ことを規約化し、ベンダー配布資料へ明記する</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr"/>
@@ -30726,12 +30726,12 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>baseUrl にパスプレフィックス（/v1 等）まで含めて書く規約の明文化</t>
+          <t>【解決・2026-09-18】**servers は無視し、baseUrl のみを使う**。アプリ側に「**baseUrl はパスプレフィックス（/v1 等）まで含めて書く**」ことを規約化し、ベンダー配布資料へ明記する。全件 404 になる場合はこの記載漏れを疑う</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr"/>
@@ -31774,12 +31774,12 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>RetryPolicy（MaximumRetryAttempts / MaximumEventAgeInSeconds）の設定値。**AWS 公式は 185 回・24 時間を「最大値」としか記載しておらず既定値が不明**のため、明示設定する。巡回は 1 時間ごとに再実行されるので、長時間リトライより早く諦めて DLQ + MM-2 で気づく方が望ましい（案: 2 回 / 600 秒）</t>
+          <t>【解決・2026-09-18】**リトライ 2 回 / 最大 600 秒**で確定。AWS 公式は 185 回・24 時間を「最大値」としか記載しておらず既定値が不明なため、明示設定する。巡回は 1 時間ごとに再実行されるため、長時間リトライするより早く諦めて DLQ + MM-2 で気づく方がよい</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr"/>
@@ -31810,12 +31810,12 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>対象検索 Lambda に予約同時実行 1 を設定するか（多重起動の抑止）。設定すると多重起動は防げるが、スロットルされた起動が Scheduler 側のリトライ・DLQ に回る点に注意</t>
+          <t>【解決・2026-09-18】**予約同時実行 1 を設定する**。多重起動を抑止し 412 競合を減らす。スロットルされた起動は Scheduler 側のリトライ（PD-1）で吸収し、枯渇すれば DLQ + MM-2 で気づける</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr"/>
@@ -32722,12 +32722,12 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>登録リストの置き場（SSM Standard 4KB / Advanced 8KB / S3）。アカウント数が数十を超えるなら S3 上の台帳に移すことを検討</t>
+          <t>【解決・2026-09-18】**SSM Standard（4KB）で開始**する。Phase 1 の規模（数アカウント）では十分。数十アカウントに増えて上限に近づいたら S3 上の台帳へ移す</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>設計担当</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr"/>
@@ -35600,12 +35600,12 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>台帳 JSON が破損していた場合の復旧手順（バージョニングからの巻き戻しを Runbook 化するか）。配置バケットはバージョニング有効なので旧版から復元可能</t>
+          <t>【解決・2026-09-18】**Runbook 化する**。配置バケットはバージョニング有効のため、破損時は旧版へ巻き戻す手順を運用手順書（WBS W4-1）に含める</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>運用設計（WBS W4-1）</t>
+          <t>—（解決済み）</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr"/>
